--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH55"/>
+  <dimension ref="A1:DH71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22110,6 +22110,6266 @@
         <v>5.934391687221749e-17</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 9, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8834876543209876</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.793956043956044</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.7893518518518519</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.7307692307692308</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8282828282828283</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.9028571428571428</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.8229166666666666</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.8610354223433241</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.9144593253968254</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.8181829094095475</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.8305059523809524</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.7213114754098361</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.775330396475771</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>0.014668703079223633, 0.012719392776489258, 0.0190122127532959, 0.012093544006347656, 0.0, 0.020070552825927734, 0.003084897994995117</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.01166418620518276</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.01271939277648926</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.007016743756521022</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>0.01783299446105957, 0.015633821487426758, 0.01527714729309082, 0.017386913299560547, 0.016959667205810547, 0.014983415603637695, 0.01750326156616211</t>
+        </is>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.01651103155953543</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.01695966720581055</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.001090617614472017</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7735849056603774, 0.8301886792452831, 0.7735849056603774, 0.8490566037735849, 0.7358490566037735, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7611111111111111, 0.8328173374613003, 0.7770897832817337, 0.8359133126934984, 0.7476780185758514, 0.686532507739938</t>
+        </is>
+      </c>
+      <c r="AI56" t="n">
+        <v>0.7942770090492337</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.7770897832817337</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.06959052271303844</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.8007387441349706</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0.06716123003259146</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.823529411764706, 0.8615384615384616, 0.8125, 0.8823529411764706, 0.7741935483870968, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6842105263157895, 0.7804878048780488, 0.7142857142857143, 0.7894736842105263, 0.6818181818181819, 0.5945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0.7342296211725884</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.0895216357943244</v>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7538699690402477, 0.8210131332082552, 0.7633928571428572, 0.8359133126934984, 0.7280058651026393, 0.6886016451233843</t>
+        </is>
+      </c>
+      <c r="AU56" t="n">
+        <v>0.7870848249702979</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0.7633928571428572</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0.07145152461578382</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0.8399400287680073</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0.823529411764706</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0.0554063234891343</v>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848485, 0.9032258064516129, 0.8666666666666667, 0.8823529411764706, 0.8571428571428571, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.65, 0.7272727272727273, 0.6521739130434783, 0.7894736842105263, 0.6, 0.6111111111111112</t>
+        </is>
+      </c>
+      <c r="BC56" t="n">
+        <v>0.7035383253918724</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0.09947915103007433</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0.8674512620297384</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0.04909885900271642</v>
+      </c>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8235294117647058, 0.7647058823529411, 0.8823529411764706, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7222222222222222, 0.8421052631578947, 0.7894736842105263, 0.7894736842105263, 0.7894736842105263, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="BK56" t="n">
+        <v>0.7723475355054303</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>0.0930755219513667</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>0.8162064825930371</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0.07175719094074301</v>
+      </c>
+      <c r="BQ56" t="inlineStr">
+        <is>
+          <t>0.9548872180451128, 0.8571428571428572, 0.9396284829721362, 0.8715170278637772, 0.9380804953560372, 0.848297213622291, 0.8746130030959752</t>
+        </is>
+      </c>
+      <c r="BR56" t="n">
+        <v>0.8977380425854553</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>0.8746130030959752</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>0.04134009548189208</v>
+      </c>
+      <c r="BU56" t="inlineStr">
+        <is>
+          <t>0.8018867924528302, 0.8338557993730408, 0.8275862068965517, 0.8213166144200627, 0.8244514106583072, 0.8463949843260188, 0.8401253918495298</t>
+        </is>
+      </c>
+      <c r="BV56" t="inlineStr">
+        <is>
+          <t>0.798683358515001, 0.833739837398374, 0.828550562763124, 0.8177034109459576, 0.820130595411977, 0.8511040467394106, 0.8362617063321591</t>
+        </is>
+      </c>
+      <c r="BW56" t="n">
+        <v>0.8265962168722863</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>0.828550562763124</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>0.01534796456100859</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>0.8279453142823344</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>0.01341108811353248</v>
+      </c>
+      <c r="CC56" t="inlineStr">
+        <is>
+          <t>0.8405063291139241, 0.8658227848101266, 0.860759493670886, 0.8571428571428572, 0.86, 0.8753180661577608, 0.8728179551122195</t>
+        </is>
+      </c>
+      <c r="CD56" t="inlineStr">
+        <is>
+          <t>0.7385892116182572, 0.7818930041152263, 0.7736625514403291, 0.7615062761506276, 0.7647058823529412, 0.7999999999999999, 0.7848101265822786</t>
+        </is>
+      </c>
+      <c r="CE56" t="n">
+        <v>0.7721667217513799</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>0.7736625514403291</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0.01823710327303168</v>
+      </c>
+      <c r="CH56" t="inlineStr">
+        <is>
+          <t>0.7895477703660907, 0.8238578944626764, 0.8172110225556075, 0.8093245666467423, 0.8123529411764706, 0.8376590330788803, 0.8288140408472491</t>
+        </is>
+      </c>
+      <c r="CI56" t="n">
+        <v>0.8169667527333883</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>0.8172110225556075</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>0.01438037880959576</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>0.8617667837153965</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>0.860759493670886</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>0.01068871617772289</v>
+      </c>
+      <c r="CO56" t="inlineStr">
+        <is>
+          <t>0.8736842105263158, 0.9, 0.8994708994708994, 0.8860103626943006, 0.8865979381443299, 0.9197860962566845, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="CP56" t="inlineStr">
+        <is>
+          <t>0.6953125, 0.7364341085271318, 0.7230769230769231, 0.7222222222222222, 0.728, 0.7424242424242424, 0.75</t>
+        </is>
+      </c>
+      <c r="CQ56" t="n">
+        <v>0.7282099994643599</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>0.01642722616540448</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>0.8947122006469183</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>0.01347200488828723</v>
+      </c>
+      <c r="CW56" t="inlineStr">
+        <is>
+          <t>0.8097560975609757, 0.8341463414634146, 0.8252427184466019, 0.8300970873786407, 0.8349514563106796, 0.8349514563106796, 0.8495145631067961</t>
+        </is>
+      </c>
+      <c r="CX56" t="inlineStr">
+        <is>
+          <t>0.7876106194690266, 0.8333333333333334, 0.831858407079646, 0.8053097345132744, 0.8053097345132744, 0.8672566371681416, 0.8230088495575221</t>
+        </is>
+      </c>
+      <c r="CY56" t="n">
+        <v>0.8219553308048884</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>0.8230088495575221</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>0.02394803621466072</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>0.831237102939684</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>0.8341463414634146</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>0.01114058176147008</v>
+      </c>
+      <c r="DE56" t="inlineStr">
+        <is>
+          <t>0.8993093028275415, 0.9135643988018828, 0.9040080762952144, 0.9125998797147521, 0.9027622647993814, 0.9172179740527536, 0.9106237649282585</t>
+        </is>
+      </c>
+      <c r="DF56" t="n">
+        <v>0.9085836659171121</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>0.9106237649282585</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>0.006100228290493955</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'estimator': LogisticRegression(fit_intercept=False), 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 6, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7083333333333333</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7855392156862745</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.8417508417508418</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.6454545454545455</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.8987341772151899</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.7513227513227514</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.9445476715828591</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.817636684303351</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.8599175473231913</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.9572192513368984</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.8839506172839506</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>0.011822223663330078, 0.010028839111328125, 0.010276556015014648, 0.01536250114440918, 0.015703678131103516, 0.009590387344360352, 0.010011434555053711</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.01182794570922852</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.01027655601501465</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.002433820964641582</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>0.016391754150390625, 0.010257959365844727, 0.014030933380126953, 0.012598514556884766, 0.015532493591308594, 0.013977766036987305, 0.016004085540771484</t>
+        </is>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.01411335808890206</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.01403093338012695</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.001998710790265128</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7358490566037735, 0.8490566037735849, 0.8113207547169812, 0.8490566037735849, 0.8490566037735849, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>0.8692307692307693, 0.7518315018315018, 0.8745421245421245, 0.848901098901099, 0.8745421245421245, 0.8287545787545787, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.8529827315541602</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.8692307692307693</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.04919646278398139</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.8359289208345813</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.04615480407647387</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>0.7878787878787877, 0.6111111111111112, 0.7647058823529412, 0.7222222222222223, 0.7647058823529412, 0.7333333333333334, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>0.9066666666666667, 0.8, 0.8888888888888888, 0.8571428571428572, 0.8888888888888888, 0.8947368421052632, 0.9166666666666666</t>
+        </is>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0.8789986871941758</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0.0365399690171014</v>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>0.8472727272727272, 0.7055555555555556, 0.826797385620915, 0.7896825396825398, 0.826797385620915, 0.8140350877192983, 0.8700980392156863</t>
+        </is>
+      </c>
+      <c r="AU57" t="n">
+        <v>0.8114626743839481</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0.826797385620915</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0.04911805317047191</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0.7439266615737203</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0.7647058823529412</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0.06251309692781594</v>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>0.7222222222222222, 0.5, 0.65, 0.5909090909090909, 0.65, 0.6875, 0.7</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9032258064516129, 0.9696969696969697, 0.967741935483871, 0.9696969696969697, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC57" t="n">
+        <v>0.9533892920989696</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0.03092624724237868</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0.6429473304473304</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0.07047375791757227</v>
+      </c>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7857142857142857, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ57" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.717948717948718, 0.8205128205128205, 0.7692307692307693, 0.8205128205128205, 0.8717948717948718, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK57" t="n">
+        <v>0.8168498168498168</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0.05206106374927434</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>0.8891156462585034</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>0.07450144350274553</v>
+      </c>
+      <c r="BQ57" t="inlineStr">
+        <is>
+          <t>0.9521367521367521, 0.9010989010989011, 0.9688644688644688, 0.9340659340659341, 0.8992673992673993, 0.9468864468864469, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="BR57" t="n">
+        <v>0.9426652712366999</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>0.9468864468864469</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>0.03242500429245387</v>
+      </c>
+      <c r="BU57" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.8495297805642633, 0.8244514106583072, 0.8369905956112853, 0.8589341692789969, 0.8338557993730408, 0.8338557993730408</t>
+        </is>
+      </c>
+      <c r="BV57" t="inlineStr">
+        <is>
+          <t>0.8562271062271063, 0.8712166918049271, 0.842885872297637, 0.8589240824534943, 0.8663901458019105, 0.8530417295123178, 0.8492961287078934</t>
+        </is>
+      </c>
+      <c r="BW57" t="n">
+        <v>0.8568545366864695</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>0.8562271062271063</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>0.009013217627763364</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>0.8387072697417525</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>0.8338557993730408</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>0.01074631774588803</v>
+      </c>
+      <c r="CC57" t="inlineStr">
+        <is>
+          <t>0.7414634146341463, 0.7647058823529411, 0.7281553398058254, 0.7475728155339805, 0.7692307692307693, 0.7414634146341464, 0.7389162561576355</t>
+        </is>
+      </c>
+      <c r="CD57" t="inlineStr">
+        <is>
+          <t>0.8770301624129929, 0.8894009216589861, 0.8703703703703703, 0.8796296296296297, 0.8984198645598194, 0.8775981524249422, 0.8781609195402298</t>
+        </is>
+      </c>
+      <c r="CE57" t="n">
+        <v>0.8815157172281386</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0.8781609195402298</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0.008638988965732697</v>
+      </c>
+      <c r="CH57" t="inlineStr">
+        <is>
+          <t>0.8092467885235697, 0.8270534020059637, 0.7992628550880978, 0.813601222581805, 0.8338253168952943, 0.8095307835295443, 0.8085385878489326</t>
+        </is>
+      </c>
+      <c r="CI57" t="n">
+        <v>0.8144369937818867</v>
+      </c>
+      <c r="CJ57" t="n">
+        <v>0.8095307835295443</v>
+      </c>
+      <c r="CK57" t="n">
+        <v>0.01103134592511745</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>0.7473582703356348</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>0.7414634146341464</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>0.01356945452140712</v>
+      </c>
+      <c r="CO57" t="inlineStr">
+        <is>
+          <t>0.628099173553719, 0.6554621848739496, 0.6198347107438017, 0.6363636363636364, 0.6818181818181818, 0.6333333333333333, 0.635593220338983</t>
+        </is>
+      </c>
+      <c r="CP57" t="inlineStr">
+        <is>
+          <t>0.9593908629441624, 0.965, 0.9494949494949495, 0.9595959595959596, 0.9521531100478469, 0.9547738693467337, 0.9502487562189055</t>
+        </is>
+      </c>
+      <c r="CQ57" t="n">
+        <v>0.9558082153783654</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>0.9547738693467337</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>0.00530317766357237</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>0.6415006344322292</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>0.635593220338983</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>0.01926296230954283</v>
+      </c>
+      <c r="CW57" t="inlineStr">
+        <is>
+          <t>0.9047619047619048, 0.9176470588235294, 0.8823529411764706, 0.9058823529411765, 0.8823529411764706, 0.8941176470588236, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="CX57" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.8247863247863247, 0.8034188034188035, 0.811965811965812, 0.8504273504273504, 0.811965811965812, 0.8162393162393162</t>
+        </is>
+      </c>
+      <c r="CY57" t="n">
+        <v>0.8180708180708179</v>
+      </c>
+      <c r="CZ57" t="n">
+        <v>0.811965811965812</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>0.01460105096837776</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>0.8956382553021209</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>0.01311695147525128</v>
+      </c>
+      <c r="DE57" t="inlineStr">
+        <is>
+          <t>0.9461233211233212, 0.9543489190548015, 0.9431875314228256, 0.9482654600301659, 0.9460030165912519, 0.9483660130718954, 0.9361990950226244</t>
+        </is>
+      </c>
+      <c r="DF57" t="n">
+        <v>0.9460704794738409</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>0.9461233211233212</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>0.005132291885239604</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8659793814432989</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8742283950617284</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8103481812876872</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.8078703703703703</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.7547169811320754</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.8956228956228957</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.9351351351351351</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.9010416666666666</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.9177718832891245</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.9738839285714285</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.8874573702159909</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.8933779761904761</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.8303571428571429</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>0.011620044708251953, 0.0, 0.00901651382446289, 0.0030808448791503906, 0.0, 0.009159326553344727, 0.0</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.004696675709315709</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.003080844879150391</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.00471011813044708</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>0.020097732543945312, 0.027334928512573242, 0.018164873123168945, 0.02330303192138672, 0.02862691879272461, 0.015540838241577148, 0.015600204467773438</t>
+        </is>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.0212383610861642</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0.02009773254394531</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0.004942811856970245</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.8301886792452831, 0.8301886792452831, 0.8867924528301887, 0.8301886792452831, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>0.8661654135338346, 0.8452380952380952, 0.8444272445820433, 0.8444272445820433, 0.8769349845201238, 0.8444272445820433, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.8510762199616687</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.8444272445820433</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.01359087690356831</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.852051512428871</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0.02395178080039795</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.8823529411764706, 0.8571428571428571, 0.8571428571428571, 0.9117647058823528, 0.8571428571428571, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.7894736842105262, 0.7906976744186046, 0.7906976744186046, 0.8421052631578947, 0.7906976744186046, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0.8037827125954421</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0.02159698499630696</v>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>0.875, 0.8359133126934983, 0.8239202657807309, 0.8239202657807309, 0.8769349845201238, 0.8239202657807309, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AU58" t="n">
+        <v>0.8422174867499018</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0.8359133126934983</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0.02192144394706144</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0.8806522609043616</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0.02369111490279092</v>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9090909090909091, 0.9310344827586207, 0.9310344827586207, 0.9117647058823529, 0.9310344827586207, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.75, 0.7083333333333334, 0.7083333333333334, 0.8421052631578947, 0.7083333333333334, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BC58" t="n">
+        <v>0.7698474126492704</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0.06547600116055621</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>0.9126005566167839</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0.01842441007284814</v>
+      </c>
+      <c r="BI58" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8571428571428571, 0.7941176470588235, 0.7941176470588235, 0.9117647058823529, 0.7941176470588235, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ58" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.8333333333333334, 0.8947368421052632, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK58" t="n">
+        <v>0.8483709273182958</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0.04416293279876214</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>0.853781512605042</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0.05707573205951751</v>
+      </c>
+      <c r="BQ58" t="inlineStr">
+        <is>
+          <t>0.9255639097744361, 0.8952380952380952, 0.9326625386996905, 0.9504643962848297, 0.869969040247678, 0.9040247678018576, 0.9187306501547987</t>
+        </is>
+      </c>
+      <c r="BR58" t="n">
+        <v>0.9138076283144836</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0.9187306501547987</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>0.02456485963917759</v>
+      </c>
+      <c r="BU58" t="inlineStr">
+        <is>
+          <t>0.8773584905660378, 0.9122257053291536, 0.9059561128526645, 0.890282131661442, 0.9059561128526645, 0.8871473354231975, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="BV58" t="inlineStr">
+        <is>
+          <t>0.8810489963306712, 0.9122379118528028, 0.9092061173640347, 0.8970701950339376, 0.9072085230689921, 0.8866526333877481, 0.8939341867858064</t>
+        </is>
+      </c>
+      <c r="BW58" t="n">
+        <v>0.8981940805462847</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>0.8970701950339376</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>0.01099560337723226</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0.8964968018318701</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>0.01145592895294708</v>
+      </c>
+      <c r="CC58" t="inlineStr">
+        <is>
+          <t>0.90126582278481, 0.9303482587064676, 0.9250000000000002, 0.9113924050632911, 0.9253731343283583, 0.9104477611940298, 0.9185185185185186</t>
+        </is>
+      </c>
+      <c r="CD58" t="inlineStr">
+        <is>
+          <t>0.8381742738589212, 0.8813559322033898, 0.8739495798319328, 0.8559670781893004, 0.8728813559322035, 0.8474576271186441, 0.8583690987124464</t>
+        </is>
+      </c>
+      <c r="CE58" t="n">
+        <v>0.861164992263834</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>0.8583690987124464</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>0.01444048493454186</v>
+      </c>
+      <c r="CH58" t="inlineStr">
+        <is>
+          <t>0.8697200483218657, 0.9058520954549287, 0.8994747899159665, 0.8836797416262958, 0.899127245130281, 0.878952694156337, 0.8884438086154824</t>
+        </is>
+      </c>
+      <c r="CI58" t="n">
+        <v>0.8893214890315939</v>
+      </c>
+      <c r="CJ58" t="n">
+        <v>0.8884438086154824</v>
+      </c>
+      <c r="CK58" t="n">
+        <v>0.01193333471534314</v>
+      </c>
+      <c r="CL58" t="n">
+        <v>0.9174779857993538</v>
+      </c>
+      <c r="CM58" t="n">
+        <v>0.9185185185185186</v>
+      </c>
+      <c r="CN58" t="n">
+        <v>0.00952390437252938</v>
+      </c>
+      <c r="CO58" t="inlineStr">
+        <is>
+          <t>0.9368421052631579, 0.949238578680203, 0.9536082474226805, 0.9523809523809523, 0.9489795918367347, 0.9336734693877551, 0.9346733668341709</t>
+        </is>
+      </c>
+      <c r="CP58" t="inlineStr">
+        <is>
+          <t>0.7890625, 0.8524590163934426, 0.832, 0.8, 0.8373983739837398, 0.8130081300813008, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="CQ58" t="n">
+        <v>0.8224659076845452</v>
+      </c>
+      <c r="CR58" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>0.02084472933222052</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>0.9441994731150934</v>
+      </c>
+      <c r="CU58" t="n">
+        <v>0.9489795918367347</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>0.008100952976481572</v>
+      </c>
+      <c r="CW58" t="inlineStr">
+        <is>
+          <t>0.8682926829268293, 0.9121951219512195, 0.8980582524271845, 0.8737864077669902, 0.9029126213592233, 0.8883495145631068, 0.9029126213592233</t>
+        </is>
+      </c>
+      <c r="CX58" t="inlineStr">
+        <is>
+          <t>0.8938053097345132, 0.9122807017543859, 0.9203539823008849, 0.9203539823008849, 0.911504424778761, 0.8849557522123894, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY58" t="n">
+        <v>0.9040299864706015</v>
+      </c>
+      <c r="CZ58" t="n">
+        <v>0.911504424778761</v>
+      </c>
+      <c r="DA58" t="n">
+        <v>0.01458513945220852</v>
+      </c>
+      <c r="DB58" t="n">
+        <v>0.8923581746219681</v>
+      </c>
+      <c r="DC58" t="n">
+        <v>0.8980582524271845</v>
+      </c>
+      <c r="DD58" t="n">
+        <v>0.01506612012003893</v>
+      </c>
+      <c r="DE58" t="inlineStr">
+        <is>
+          <t>0.9688322900928125, 0.9769790329482242, 0.977919065211788, 0.9740527536729959, 0.9727639831600654, 0.972957298737005, 0.9711100610018043</t>
+        </is>
+      </c>
+      <c r="DF58" t="n">
+        <v>0.9735163549749564</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>0.972957298737005</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>0.002934305502395285</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'estimator': KNeighborsClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.8}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9372727272727273</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.7805183946488294</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.8090909090909091</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.9191919191919192</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.7835051546391752</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.9620253164556962</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.9792707002671002</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.9031100478468899</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.9328475206131692</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.9036697247706422</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.9425837320574162</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>0.01562809944152832, 0.0, 0.0, 0.015625476837158203, 0.015625953674316406, 0.0, 0.0</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.006697075707571847</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.007733116961152996</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>0.015892744064331055, 0.016904592514038086, 0.015624284744262695, 0.01565718650817871, 0.009342193603515625, 0.015624284744262695, 0.015623807907104492</t>
+        </is>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.01495272772652762</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.0156242847442627</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.002330545259605557</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7358490566037735, 0.9056603773584906, 0.8113207547169812, 0.9433962264150944, 0.8867924528301887, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>0.9025641025641026, 0.7060439560439561, 0.8901098901098901, 0.826007326007326, 0.9386446886446886, 0.8543956043956045, 0.8974358974358974</t>
+        </is>
+      </c>
+      <c r="AI59" t="n">
+        <v>0.8593144950287809</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0.070903180429137</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.8601377657981431</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0.06380209893910745</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.5625000000000001, 0.8275862068965518, 0.7058823529411764, 0.896551724137931, 0.7857142857142857, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8108108108108107, 0.935064935064935, 0.8611111111111112, 0.9610389610389611, 0.9230769230769231, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0.8993908493908496</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.9189189189189189</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0.04707792269391669</v>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>0.8712241653418124, 0.6866554054054055, 0.8813255709807435, 0.7834967320261438, 0.9287953425884461, 0.8543956043956045, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU59" t="n">
+        <v>0.833948407497741</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0.07299075986710456</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0.7685059656046328</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>0.09975401053627557</v>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.5, 0.8, 0.6, 0.8666666666666667, 0.7857142857142857, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8571428571428571, 0.9473684210526315, 0.9393939393939394, 0.9736842105263158, 0.9230769230769231, 1.0</t>
+        </is>
+      </c>
+      <c r="BC59" t="n">
+        <v>0.9445849889458913</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>0.04273102564488179</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>0.7036552420011067</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>0.1197844006608555</v>
+      </c>
+      <c r="BI59" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.6428571428571429, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ59" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7692307692307693, 0.9230769230769231, 0.7948717948717948, 0.9487179487179487, 0.9230769230769231, 0.7948717948717948</t>
+        </is>
+      </c>
+      <c r="BK59" t="n">
+        <v>0.8608058608058607</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>0.06833244727537595</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>0.8578231292517007</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0.1084516755558075</v>
+      </c>
+      <c r="BQ59" t="inlineStr">
+        <is>
+          <t>0.9598290598290599, 0.8214285714285714, 0.9194139194139195, 0.9285714285714286, 0.966117216117216, 0.891025641025641, 0.9532967032967032</t>
+        </is>
+      </c>
+      <c r="BR59" t="n">
+        <v>0.9199546485260772</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>0.04698245959808522</v>
+      </c>
+      <c r="BU59" t="inlineStr">
+        <is>
+          <t>0.8930817610062893, 0.9184952978056427, 0.8871473354231975, 0.8934169278996865, 0.890282131661442, 0.9059561128526645, 0.8996865203761756</t>
+        </is>
+      </c>
+      <c r="BV59" t="inlineStr">
+        <is>
+          <t>0.9120879120879121, 0.9294620412267471, 0.9043489190548014, 0.91236802413273, 0.8989944695827048, 0.9171694318753143, 0.9091503267973856</t>
+        </is>
+      </c>
+      <c r="BW59" t="n">
+        <v>0.9119401606796566</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>0.9120879120879121</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>0.009004502946801204</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>0.8982951552892998</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>0.8934169278996865</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>0.01005791048390546</v>
+      </c>
+      <c r="CC59" t="inlineStr">
+        <is>
+          <t>0.8247422680412371, 0.8617021276595745, 0.8163265306122449, 0.826530612244898, 0.8167539267015705, 0.8421052631578947, 0.8315789473684211</t>
+        </is>
+      </c>
+      <c r="CD59" t="inlineStr">
+        <is>
+          <t>0.9230769230769229, 0.9422222222222223, 0.9185520361990951, 0.9230769230769229, 0.9217002237136465, 0.9330357142857143, 0.9285714285714285</t>
+        </is>
+      </c>
+      <c r="CE59" t="n">
+        <v>0.9271764958779932</v>
+      </c>
+      <c r="CF59" t="n">
+        <v>0.9230769230769229</v>
+      </c>
+      <c r="CG59" t="n">
+        <v>0.007565277963616885</v>
+      </c>
+      <c r="CH59" t="inlineStr">
+        <is>
+          <t>0.87390959555908, 0.9019621749408984, 0.86743928340567, 0.8748037676609104, 0.8692270752076086, 0.8875704887218046, 0.8800751879699248</t>
+        </is>
+      </c>
+      <c r="CI59" t="n">
+        <v>0.8792839390665567</v>
+      </c>
+      <c r="CJ59" t="n">
+        <v>0.8748037676609104</v>
+      </c>
+      <c r="CK59" t="n">
+        <v>0.01117386775824332</v>
+      </c>
+      <c r="CL59" t="n">
+        <v>0.8313913822551201</v>
+      </c>
+      <c r="CM59" t="n">
+        <v>0.826530612244898</v>
+      </c>
+      <c r="CN59" t="n">
+        <v>0.01484494323075194</v>
+      </c>
+      <c r="CO59" t="inlineStr">
+        <is>
+          <t>0.7272727272727273, 0.7864077669902912, 0.7207207207207207, 0.7297297297297297, 0.7358490566037735, 0.7619047619047619, 0.7523809523809524</t>
+        </is>
+      </c>
+      <c r="CP59" t="inlineStr">
+        <is>
+          <t>0.9807692307692307, 0.9814814814814815, 0.9759615384615384, 0.9807692307692307, 0.9671361502347418, 0.9766355140186916, 0.9719626168224299</t>
+        </is>
+      </c>
+      <c r="CQ59" t="n">
+        <v>0.9763879660796206</v>
+      </c>
+      <c r="CR59" t="n">
+        <v>0.9766355140186916</v>
+      </c>
+      <c r="CS59" t="n">
+        <v>0.004924541932013494</v>
+      </c>
+      <c r="CT59" t="n">
+        <v>0.7448951022289938</v>
+      </c>
+      <c r="CU59" t="n">
+        <v>0.7358490566037735</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>0.02163144567940942</v>
+      </c>
+      <c r="CW59" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9529411764705882, 0.9411764705882353, 0.9529411764705882, 0.9176470588235294, 0.9411764705882353, 0.9294117647058824</t>
+        </is>
+      </c>
+      <c r="CX59" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.905982905982906, 0.8675213675213675, 0.8717948717948718, 0.8803418803418803, 0.8931623931623932, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="CY59" t="n">
+        <v>0.882783882783883</v>
+      </c>
+      <c r="CZ59" t="n">
+        <v>0.8803418803418803</v>
+      </c>
+      <c r="DA59" t="n">
+        <v>0.01289298661901274</v>
+      </c>
+      <c r="DB59" t="n">
+        <v>0.9410964385754302</v>
+      </c>
+      <c r="DC59" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="DD59" t="n">
+        <v>0.0125034492833532</v>
+      </c>
+      <c r="DE59" t="inlineStr">
+        <is>
+          <t>0.9801587301587301, 0.9868024132730016, 0.9796882855706386, 0.9729009552538964, 0.9785822021116138, 0.9811965811965812, 0.9818250377073906</t>
+        </is>
+      </c>
+      <c r="DF59" t="n">
+        <v>0.9801648864674075</v>
+      </c>
+      <c r="DG59" t="n">
+        <v>0.9801587301587301</v>
+      </c>
+      <c r="DH59" t="n">
+        <v>0.003842878961857964</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8935185185185185</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.793956043956044</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.7893518518518519</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.7307692307692308</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.9441340782122905</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.8802083333333334</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.9110512129380053</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.9442708333333334</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.8815345750788681</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.8924851190476191</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.8050847457627118</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.8520179372197308</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>0.03433680534362793, 0.01859283447265625, 0.015628576278686523, 0.015626907348632812, 0.016400575637817383, 0.03128385543823242, 0.015625</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.02107065064566476</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.01640057563781738</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.007532360772272542</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>0.01595616340637207, 0.0164492130279541, 0.015617132186889648, 0.015623807907104492, 0.015953540802001953, 0.015622138977050781, 0.015624284744262695</t>
+        </is>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.01583518300737654</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0.0156242847442627</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0.000289770628559924</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.9056603773584906, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.788888888888889, 0.914860681114551, 0.8854489164086687, 0.8885448916408669, 0.8707430340557275, 0.794891640866873</t>
+        </is>
+      </c>
+      <c r="AI60" t="n">
+        <v>0.8643064243241155</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.8854489164086687</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0.04772058760655016</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.8627333532993909</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0.04505786739163111</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8358208955223881, 0.923076923076923, 0.888888888888889, 0.9090909090909091, 0.8709677419354839, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.717948717948718, 0.8780487804878049, 0.8372093023255814, 0.8500000000000001, 0.8181818181818181, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0.8181599447279956</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0.0616682423498862</v>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.776884806735553, 0.900562851782364, 0.8630490956072352, 0.8795454545454546, 0.8445747800586509, 0.794891640866873</t>
+        </is>
+      </c>
+      <c r="AU60" t="n">
+        <v>0.8537393280375426</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0.8630490956072352</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0.04834190274924574</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0.8893187113470893</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0.03603904089363921</v>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.875, 0.967741935483871, 0.9655172413793104, 0.9375, 0.9642857142857143, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6666666666666666, 0.8181818181818182, 0.75, 0.8095238095238095, 0.72, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BC60" t="n">
+        <v>0.7774844100319553</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0.08234952702795686</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>0.9259864266483433</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>0.04291316743921902</v>
+      </c>
+      <c r="BI60" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.8823529411764706, 0.8235294117647058, 0.8823529411764706, 0.7941176470588235, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ60" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7777777777777778, 0.9473684210526315, 0.9473684210526315, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK60" t="n">
+        <v>0.8705096073517125</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>0.08069500846144192</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>0.8581032412965186</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>0.056959717418727</v>
+      </c>
+      <c r="BQ60" t="inlineStr">
+        <is>
+          <t>0.9774436090225564, 0.8777777777777777, 0.9442724458204335, 0.9226006191950464, 0.9287925696594428, 0.9195046439628483, 0.8761609907120743</t>
+        </is>
+      </c>
+      <c r="BR60" t="n">
+        <v>0.92093609373574</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>0.9226006191950464</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>0.03310519727650558</v>
+      </c>
+      <c r="BU60" t="inlineStr">
+        <is>
+          <t>0.8647798742138365, 0.8934169278996865, 0.8620689655172413, 0.8808777429467085, 0.8808777429467085, 0.8714733542319749, 0.8746081504702194</t>
+        </is>
+      </c>
+      <c r="BV60" t="inlineStr">
+        <is>
+          <t>0.8712928987696956, 0.8956568249893025, 0.8672351576595927, 0.8817982644557093, 0.8837958587507517, 0.8725191167626085, 0.8769438955236704</t>
+        </is>
+      </c>
+      <c r="BW60" t="n">
+        <v>0.8784631452730471</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>0.8769438955236704</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>0.008866495608941287</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>0.8754432511751966</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>0.8746081504702194</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>0.009936635364963042</v>
+      </c>
+      <c r="CC60" t="inlineStr">
+        <is>
+          <t>0.8900255754475703, 0.914572864321608, 0.8883248730964467, 0.905, 0.9045226130653266, 0.8972431077694234, 0.8994974874371858</t>
+        </is>
+      </c>
+      <c r="CD60" t="inlineStr">
+        <is>
+          <t>0.8244897959183674, 0.8583333333333333, 0.819672131147541, 0.8403361344537816, 0.8416666666666667, 0.8284518828451883, 0.8333333333333335</t>
+        </is>
+      </c>
+      <c r="CE60" t="n">
+        <v>0.8351833253854587</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>0.01200114001647768</v>
+      </c>
+      <c r="CH60" t="inlineStr">
+        <is>
+          <t>0.8572576856829688, 0.8864530988274706, 0.8539985021219938, 0.8726680672268908, 0.8730946398659967, 0.8628474953073059, 0.8664154103852597</t>
+        </is>
+      </c>
+      <c r="CI60" t="n">
+        <v>0.867533557059698</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>0.8664154103852597</v>
+      </c>
+      <c r="CK60" t="n">
+        <v>0.01019270445527831</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>0.8998837887339372</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>0.8994974874371858</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>0.008463185613324879</v>
+      </c>
+      <c r="CO60" t="inlineStr">
+        <is>
+          <t>0.9354838709677419, 0.9430051813471503, 0.9308510638297872, 0.9329896907216495, 0.9375, 0.927461139896373, 0.9322916666666666</t>
+        </is>
+      </c>
+      <c r="CP60" t="inlineStr">
+        <is>
+          <t>0.7651515151515151, 0.8174603174603174, 0.7633587786259542, 0.8, 0.7952755905511811, 0.7857142857142857, 0.7874015748031497</t>
+        </is>
+      </c>
+      <c r="CQ60" t="n">
+        <v>0.7877660089009149</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>0.7874015748031497</v>
+      </c>
+      <c r="CS60" t="n">
+        <v>0.01772523186662077</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>0.9342260876327669</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>0.9329896907216495</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>0.004656776519910335</v>
+      </c>
+      <c r="CW60" t="inlineStr">
+        <is>
+          <t>0.848780487804878, 0.8878048780487805, 0.8495145631067961, 0.8786407766990292, 0.8737864077669902, 0.8689320388349514, 0.8689320388349514</t>
+        </is>
+      </c>
+      <c r="CX60" t="inlineStr">
+        <is>
+          <t>0.8938053097345132, 0.9035087719298246, 0.8849557522123894, 0.8849557522123894, 0.8938053097345132, 0.8761061946902655, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY60" t="n">
+        <v>0.888870406103755</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>0.008210506683715773</v>
+      </c>
+      <c r="DB60" t="n">
+        <v>0.8680558844423395</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>0.8689320388349514</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>0.0133724578121604</v>
+      </c>
+      <c r="DE60" t="inlineStr">
+        <is>
+          <t>0.9492553421109432, 0.9536585365853659, 0.9474396425809777, 0.9469670933929031, 0.9322321505283959, 0.9509408024744395, 0.9538405361285334</t>
+        </is>
+      </c>
+      <c r="DF60" t="n">
+        <v>0.9477620148287941</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>0.9492553421109432</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>0.006823955874386418</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'estimator': SVC(probability=True), 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 9, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.9142857142857144</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.7473684210526316</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.8987341772151899</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.8160919540229885</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.9611543374753222</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.8699507389162562</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.894321217047962</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.9603960396039604</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.8899082568807339</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.9238095238095239</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>0.015657424926757812, 0.015627145767211914, 0.03125357627868652, 0.01628565788269043, 0.021266460418701172, 0.01564311981201172, 0.031931400299072266</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.02109496934073312</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.01628565788269043</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.006896904729078499</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>0.01793813705444336, 0.015626907348632812, 0.015623092651367188, 0.015621185302734375, 0.015627145767211914, 0.015625953674316406, 0.015622854232788086</t>
+        </is>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.01595503943307059</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.01562595367431641</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0.0008095989118930963</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7358490566037735, 0.9056603773584906, 0.8490566037735849, 0.8867924528301887, 0.8490566037735849, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>0.8897435897435897, 0.728937728937729, 0.8901098901098901, 0.8516483516483516, 0.8772893772893773, 0.8287545787545787, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI61" t="n">
+        <v>0.8538199895342753</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.8772893772893773</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.05678520119296428</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.8521014275731258</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0.05097521636335406</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>0.8, 0.588235294117647, 0.8275862068965518, 0.75, 0.7999999999999999, 0.7333333333333334, 0.8</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>0.9041095890410958, 0.8055555555555556, 0.935064935064935, 0.8918918918918919, 0.9210526315789475, 0.8947368421052632, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0.8934028422774162</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0.9014084507042254</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0.03854528566208262</v>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>0.8520547945205479, 0.6968954248366013, 0.8813255709807435, 0.8209459459459459, 0.8605263157894737, 0.8140350877192983, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU61" t="n">
+        <v>0.8252124807349605</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>0.8507042253521127</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0.05653632077110618</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0.7570221191925046</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0.07523301539873144</v>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>0.7, 0.5, 0.8, 0.6666666666666666, 0.75, 0.6875, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>0.9705882352941176, 0.8787878787878788, 0.9473684210526315, 0.9428571428571428, 0.9459459459459459, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC61" t="n">
+        <v>0.9434952204080908</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0.03533365677699621</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>0.681547619047619</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>0.08659844908091573</v>
+      </c>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7142857142857143, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.7435897435897436, 0.9230769230769231, 0.8461538461538461, 0.8974358974358975, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK61" t="n">
+        <v>0.8498168498168497</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>0.0538349394018281</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>0.8578231292517007</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>0.08595689668837832</v>
+      </c>
+      <c r="BQ61" t="inlineStr">
+        <is>
+          <t>0.9606837606837607, 0.836996336996337, 0.9560439560439561, 0.9304029304029304, 0.9478021978021978, 0.924908424908425, 0.9871794871794872</t>
+        </is>
+      </c>
+      <c r="BR61" t="n">
+        <v>0.934859584859585</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>0.9478021978021978</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>0.04426648471584126</v>
+      </c>
+      <c r="BU61" t="inlineStr">
+        <is>
+          <t>0.8962264150943396, 0.8934169278996865, 0.8840125391849529, 0.8808777429467085, 0.8808777429467085, 0.8996865203761756, 0.8808777429467085</t>
+        </is>
+      </c>
+      <c r="BV61" t="inlineStr">
+        <is>
+          <t>0.9027777777777777, 0.9048768225238814, 0.9097033685268979, 0.8925842131724484, 0.8850930115635998, 0.924132730015083, 0.8925842131724484</t>
+        </is>
+      </c>
+      <c r="BW61" t="n">
+        <v>0.9016788766788767</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>0.9027777777777777</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>0.01207428892037036</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>0.8879965187707544</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>0.8840125391849529</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>0.007575064046837832</v>
+      </c>
+      <c r="CC61" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.8229166666666666, 0.8159203980099502, 0.8041237113402062, 0.8, 0.8383838383838383, 0.8041237113402062</t>
+        </is>
+      </c>
+      <c r="CD61" t="inlineStr">
+        <is>
+          <t>0.9265033407572383, 0.9237668161434976, 0.9153318077803204, 0.9144144144144144, 0.9151785714285714, 0.9272727272727274, 0.9144144144144144</t>
+        </is>
+      </c>
+      <c r="CE61" t="n">
+        <v>0.9195545846015978</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>0.9153318077803204</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>0.005547481635124106</v>
+      </c>
+      <c r="CH61" t="inlineStr">
+        <is>
+          <t>0.8750163762609721, 0.8733417414050821, 0.8656261028951353, 0.8592690628773103, 0.8575892857142857, 0.8828282828282829, 0.8592690628773103</t>
+        </is>
+      </c>
+      <c r="CI61" t="n">
+        <v>0.8675628449797684</v>
+      </c>
+      <c r="CJ61" t="n">
+        <v>0.8656261028951353</v>
+      </c>
+      <c r="CK61" t="n">
+        <v>0.008966452257576855</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>0.815571105357939</v>
+      </c>
+      <c r="CM61" t="n">
+        <v>0.8159203980099502</v>
+      </c>
+      <c r="CN61" t="n">
+        <v>0.01277486196142618</v>
+      </c>
+      <c r="CO61" t="inlineStr">
+        <is>
+          <t>0.7475728155339806, 0.7383177570093458, 0.7068965517241379, 0.7155963302752294, 0.7238095238095238, 0.7345132743362832, 0.7155963302752294</t>
+        </is>
+      </c>
+      <c r="CP61" t="inlineStr">
+        <is>
+          <t>0.9674418604651163, 0.9716981132075472, 0.9852216748768473, 0.9666666666666667, 0.9579439252336449, 0.9902912621359223, 0.9666666666666667</t>
+        </is>
+      </c>
+      <c r="CQ61" t="n">
+        <v>0.9722757384646302</v>
+      </c>
+      <c r="CR61" t="n">
+        <v>0.9674418604651163</v>
+      </c>
+      <c r="CS61" t="n">
+        <v>0.01058422433590352</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>0.7260432261376757</v>
+      </c>
+      <c r="CU61" t="n">
+        <v>0.7238095238095238</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>0.01350020570049746</v>
+      </c>
+      <c r="CW61" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.9294117647058824, 0.9647058823529412, 0.9176470588235294, 0.8941176470588236, 0.9764705882352941, 0.9176470588235294</t>
+        </is>
+      </c>
+      <c r="CX61" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8803418803418803, 0.8547008547008547, 0.8675213675213675, 0.8760683760683761, 0.8717948717948718, 0.8675213675213675</t>
+        </is>
+      </c>
+      <c r="CY61" t="n">
+        <v>0.8724053724053726</v>
+      </c>
+      <c r="CZ61" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>0.01006863400639232</v>
+      </c>
+      <c r="DB61" t="n">
+        <v>0.9309523809523811</v>
+      </c>
+      <c r="DC61" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="DD61" t="n">
+        <v>0.0270674342998427</v>
+      </c>
+      <c r="DE61" t="inlineStr">
+        <is>
+          <t>0.9583842083842083, 0.9621417797888386, 0.9569632981397688, 0.959577677224736, 0.9602815485168426, 0.9619406737053796, 0.9523881347410759</t>
+        </is>
+      </c>
+      <c r="DF61" t="n">
+        <v>0.9588110457858358</v>
+      </c>
+      <c r="DG61" t="n">
+        <v>0.959577677224736</v>
+      </c>
+      <c r="DH61" t="n">
+        <v>0.003127952542991053</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x0000026E41C87050&gt;, 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 0.8}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.9467592592592593</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.9996775793650794</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>1.4758789539337158, 1.4511454105377197, 1.4686856269836426, 1.5177464485168457, 1.4586482048034668, 1.4340603351593018, 1.4502270221710205</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.465198857443673</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.458648204803467</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.02484709006213714</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>0.016666650772094727, 0.01901388168334961, 0.016052961349487305, 0.01895451545715332, 0.011610031127929688, 0.01884150505065918, 0.0033164024353027344</t>
+        </is>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.01492227826799665</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0.01666665077209473</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0.005323118157845596</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.9245283018867925, 0.8679245283018868, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8452380952380952, 0.891640866873065, 0.8212074303405572, 0.9179566563467492, 0.8738390092879257, 0.8506191950464397</t>
+        </is>
+      </c>
+      <c r="AI62" t="n">
+        <v>0.878267096312209</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0.04081289499914347</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0.8868922831186982</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0.04296485003780158</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8823529411764706, 0.9275362318840579, 0.8656716417910447, 0.9411764705882353, 0.8923076923076922, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7894736842105262, 0.8648648648648649, 0.7692307692307692, 0.8947368421052632, 0.8292682926829269, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0.8432613869070865</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0.0572924075874893</v>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8359133126934983, 0.8962005483744614, 0.8174512055109069, 0.9179566563467492, 0.8607879924953096, 0.8546807677242461</t>
+        </is>
+      </c>
+      <c r="AU62" t="n">
+        <v>0.8773319737826436</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0.8607879924953096</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0.04575649920672938</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0.9114025606582007</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0.8985507246376812</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>0.03445658409277488</v>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9090909090909091, 0.9142857142857143, 0.8787878787878788, 0.9411764705882353, 0.9354838709677419, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>1.0, 0.75, 0.8888888888888888, 0.75, 0.8947368421052632, 0.7727272727272727, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="BC62" t="n">
+        <v>0.8413837624363939</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>0.08597583217745321</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>0.9157835821972444</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>0.0246766184552728</v>
+      </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.8529411764705882, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8421052631578947, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK62" t="n">
+        <v>0.8483709273182958</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>0.04416293279876214</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>0.9081632653061223</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>0.05254758374127082</v>
+      </c>
+      <c r="BQ62" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9396825396825397, 0.9814241486068112, 0.9551083591331271, 0.9535603715170279, 0.9504643962848297, 0.9396284829721363</t>
+        </is>
+      </c>
+      <c r="BR62" t="n">
+        <v>0.959766362685425</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>0.9535603715170279</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>0.02044048917000036</v>
+      </c>
+      <c r="BU62" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV62" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 0.9956140350877193, 0.995575221238938, 0.9931480367729186, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW62" t="n">
+        <v>0.9958661366880558</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>0.001885242517235258</v>
+      </c>
+      <c r="BZ62" t="n">
+        <v>0.9968637954974975</v>
+      </c>
+      <c r="CA62" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB62" t="n">
+        <v>0.001675622622249898</v>
+      </c>
+      <c r="CC62" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD62" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 0.9955947136563876, 0.9955555555555555, 0.9911504424778761, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE62" t="n">
+        <v>0.9955667683366408</v>
+      </c>
+      <c r="CF62" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG62" t="n">
+        <v>0.002365186821933608</v>
+      </c>
+      <c r="CH62" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 0.9965808118160284, 0.9965671240247511, 0.9931480367729186, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI62" t="n">
+        <v>0.9965702076326874</v>
+      </c>
+      <c r="CJ62" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK62" t="n">
+        <v>0.001831273974945286</v>
+      </c>
+      <c r="CL62" t="n">
+        <v>0.9975736469287341</v>
+      </c>
+      <c r="CM62" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN62" t="n">
+        <v>0.001297393947929273</v>
+      </c>
+      <c r="CO62" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP62" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9911504424778761, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ62" t="n">
+        <v>0.9987357774968394</v>
+      </c>
+      <c r="CR62" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS62" t="n">
+        <v>0.003096700054087461</v>
+      </c>
+      <c r="CT62" t="n">
+        <v>0.9958491627972421</v>
+      </c>
+      <c r="CU62" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV62" t="n">
+        <v>0.001694606963530478</v>
+      </c>
+      <c r="CW62" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX62" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY62" t="n">
+        <v>0.9924257546521169</v>
+      </c>
+      <c r="CZ62" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA62" t="n">
+        <v>0.003092288713291248</v>
+      </c>
+      <c r="DB62" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="DC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD62" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="DE62" t="inlineStr">
+        <is>
+          <t>0.9993308871141808, 0.9999572100984168, 0.9995918893375719, 0.9995918893375719, 0.9994200532691812, 1.0, 0.9994630122862789</t>
+        </is>
+      </c>
+      <c r="DF62" t="n">
+        <v>0.9996221344918859</v>
+      </c>
+      <c r="DG62" t="n">
+        <v>0.9995918893375719</v>
+      </c>
+      <c r="DH62" t="n">
+        <v>0.0002413856650201297</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'estimator': &lt;catboost.core.CatBoostClassifier object at 0x0000026E43F55B10&gt;, 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 5, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.9854545454545454</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.9338624338624338</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.9477272727272728</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9811320754716981</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9932659932659933</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.9753086419753086</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.9998838694692835</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.9914458525345622</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.9908256880733946</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0.9953917050691244</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>1.434830904006958, 1.415780782699585, 1.403782844543457, 1.3846032619476318, 1.4211301803588867, 1.4777939319610596, 1.4155619144439697</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.421926259994507</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.415780782699585</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.02696246556059037</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>0.013998270034790039, 0.016599416732788086, 0.014160394668579102, 0.018730640411376953, 0.010782241821289062, 0.006818294525146484, 0.01667642593383789</t>
+        </is>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.01396652630397252</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0.0141603946685791</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0.003746387385205371</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9622641509433962, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>0.9076923076923077, 0.8745421245421245, 0.88003663003663, 0.8772893772893773, 0.9285714285714286, 0.9157509157509157, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI63" t="n">
+        <v>0.9032182103610676</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0.9076923076923077</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0.02422193585873737</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0.9193371268842968</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0.03599459928488697</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7647058823529412, 0.8461538461538461, 0.7999999999999999, 0.923076923076923, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8888888888888888, 0.9500000000000001, 0.9210526315789475, 0.975, 0.9620253164556962, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0.9438176780972061</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0.02725037578545481</v>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>0.9076923076923077, 0.826797385620915, 0.8980769230769231, 0.8605263157894737, 0.9490384615384615, 0.9254571026722926, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU63" t="n">
+        <v>0.8994834055684028</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0.9076923076923077</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0.03938782040217161</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0.8551491330395997</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0.05196387147484134</v>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.65, 0.9166666666666666, 0.75, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.9696969696969697, 0.926829268292683, 0.9459459459459459, 0.9512195121951219, 0.95, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC63" t="n">
+        <v>0.9522991221964264</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>0.01448328953848443</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>0.8532967032967035</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>0.1087356945717492</v>
+      </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ63" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8205128205128205, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9743589743589743, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK63" t="n">
+        <v>0.9377289377289377</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>0.8687074829931972</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0.04545113765575531</v>
+      </c>
+      <c r="BQ63" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.9102564102564102, 0.9908424908424908, 0.924908424908425, 0.9981684981684982, 0.9102564102564102, 0.9908424908424908</t>
+        </is>
+      </c>
+      <c r="BR63" t="n">
+        <v>0.9570905285190999</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>0.03719935827652363</v>
+      </c>
+      <c r="BU63" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 0.9937304075235109, 1.0, 0.9937304075235109, 0.9968652037617555, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV63" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 0.9957264957264957, 1.0, 0.9957264957264957, 0.9978632478632479, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="BW63" t="n">
+        <v>0.9972527472527473</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>0.9957264957264957</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>0.001881689256095529</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>0.9959667311651696</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>0.9937304075235109</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>0.002762889579380034</v>
+      </c>
+      <c r="CC63" t="inlineStr">
+        <is>
+          <t>0.988235294117647, 1.0, 0.9883720930232558, 1.0, 0.9883720930232558, 0.9941520467836257, 0.9883720930232558</t>
+        </is>
+      </c>
+      <c r="CD63" t="inlineStr">
+        <is>
+          <t>0.9957081545064378, 1.0, 0.9957081545064378, 1.0, 0.9957081545064378, 0.9978586723768736, 0.9957081545064378</t>
+        </is>
+      </c>
+      <c r="CE63" t="n">
+        <v>0.9972416129146605</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0.9957081545064378</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0.001889978826942549</v>
+      </c>
+      <c r="CH63" t="inlineStr">
+        <is>
+          <t>0.9919717243120424, 1.0, 0.9920401237648468, 1.0, 0.9920401237648468, 0.9960053595802496, 0.9920401237648468</t>
+        </is>
+      </c>
+      <c r="CI63" t="n">
+        <v>0.9948710650266903</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>0.9920401237648468</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0.003512171365790511</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0.99250051713872</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0.9883720930232558</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0.005134419163035145</v>
+      </c>
+      <c r="CO63" t="inlineStr">
+        <is>
+          <t>0.9767441860465116, 1.0, 0.9770114942528736, 1.0, 0.9770114942528736, 0.9883720930232558, 0.9770114942528736</t>
+        </is>
+      </c>
+      <c r="CP63" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>0.9851643945469125</v>
+      </c>
+      <c r="CU63" t="n">
+        <v>0.9770114942528736</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>0.01014740620368671</v>
+      </c>
+      <c r="CW63" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX63" t="inlineStr">
+        <is>
+          <t>0.9914529914529915, 1.0, 0.9914529914529915, 1.0, 0.9914529914529915, 0.9957264957264957, 0.9914529914529915</t>
+        </is>
+      </c>
+      <c r="CY63" t="n">
+        <v>0.9945054945054945</v>
+      </c>
+      <c r="CZ63" t="n">
+        <v>0.9914529914529915</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>0.003763378512191059</v>
+      </c>
+      <c r="DB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE63" t="inlineStr">
+        <is>
+          <t>0.9998982498982499, 1.0, 0.9999999999999999, 1.0, 0.999798893916541, 1.0, 0.9998994469582704</t>
+        </is>
+      </c>
+      <c r="DF63" t="n">
+        <v>0.9999423701104373</v>
+      </c>
+      <c r="DG63" t="n">
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="DH63" t="n">
+        <v>7.334772857949766e-05</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.9471450617283951</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8528257456828885</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>0.04170680046081543, 0.056752920150756836, 0.03728842735290527, 0.039114952087402344, 0.033617496490478516, 0.03336811065673828, 0.035186767578125</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.03957649639674595</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.03728842735290527</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.007543582551340926</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>0.007856607437133789, 0.018970966339111328, 0.016738176345825195, 0.01774120330810547, 0.016413450241088867, 0.02956104278564453, 0.01653122901916504</t>
+        </is>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.0176875250680106</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0.0167381763458252</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0.005893568134832149</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.7924528301886793, 0.9245283018867925, 0.8301886792452831, 0.9056603773584906, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8023809523809524, 0.9295665634674922, 0.8328173374613003, 0.903250773993808, 0.8560371517027863, 0.8390092879256965</t>
+        </is>
+      </c>
+      <c r="AI64" t="n">
+        <v>0.8729186411406668</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0.8560371517027863</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0.05027112793891122</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0.8734151941699111</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0.05605255122691098</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8307692307692307, 0.9393939393939394, 0.8615384615384616, 0.9253731343283583, 0.8524590163934426, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7317073170731708, 0.9, 0.7804878048780488, 0.8717948717948718, 0.7999999999999999, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0.8326334911700766</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0.06929100562647317</v>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.7812382739212007, 0.9196969696969697, 0.8210131332082552, 0.898584003061615, 0.8262295081967213, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU64" t="n">
+        <v>0.8651142066814581</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0.8507042253521127</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0.05792736212327599</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0.89759492219284</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0.9014084507042254</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0.04766783161975097</v>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9, 0.96875, 0.9032258064516129, 0.9393939393939394, 0.9629629629629629, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>1.0, 0.6521739130434783, 0.8571428571428571, 0.7272727272727273, 0.85, 0.6923076923076923, 0.875</t>
+        </is>
+      </c>
+      <c r="BC64" t="n">
+        <v>0.8076995985381078</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>0.1132095154495363</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>0.9264490742313323</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>0.0352578632957699</v>
+      </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>1.0, 0.7714285714285715, 0.9117647058823529, 0.8235294117647058, 0.9117647058823529, 0.7647058823529411, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ64" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK64" t="n">
+        <v>0.8709273182957393</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>0.06870551459585363</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>0.8749099639855943</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>0.08302203697858708</v>
+      </c>
+      <c r="BQ64" t="inlineStr">
+        <is>
+          <t>0.9894736842105264, 0.946031746031746, 0.9752321981424148, 0.9489164086687307, 0.9442724458204335, 0.9303405572755418, 0.93343653250774</t>
+        </is>
+      </c>
+      <c r="BR64" t="n">
+        <v>0.9525290818081619</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0.946031746031746</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>0.02021537609599209</v>
+      </c>
+      <c r="BU64" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV64" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW64" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC64" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD64" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE64" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH64" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI64" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO64" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP64" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU64" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV64" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW64" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX64" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY64" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ64" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA64" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE64" t="inlineStr">
+        <is>
+          <t>0.9999784157133608, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF64" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG64" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH64" t="n">
+        <v>9.712984233443494e-06</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'estimator': XGBClassifier(base_score=None, booster=None, callbacks=None,
+              colsample_bylevel=None, colsample_bynode=None,
+              colsample_bytree=None, device=None, early_stopping_rounds=None,
+              enable_categorical=False, eval_metric=None, feature_types=None,
+              gamma=None, grow_policy=None, importance_type=None,
+              interaction_constraints=None, learning_rate=None, max_bin=None,
+              max_cat_threshold=None, max_cat_to_onehot=None,
+              max_delta_step=None, max_depth=None, max_leaves=None,
+              min_child_weight=None, missing=nan, monotone_constraints=None,
+              multi_strategy=None, n_estimators=None, n_jobs=None,
+              num_parallel_tree=None, random_state=None, ...), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 8, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9818181818181818</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.8825240545983442</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.8886363636363637</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.9357798165137615</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>0.03332328796386719, 0.03335070610046387, 0.03403043746948242, 0.03331947326660156, 0.033356666564941406, 0.0329434871673584, 0.03337812423706055</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.03338602610996792</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.03335070610046387</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.00029800383446348</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>0.01617121696472168, 0.016697168350219727, 0.016052722930908203, 0.016712427139282227, 0.017388105392456055, 0.016673564910888672, 0.016690731048583984</t>
+        </is>
+      </c>
+      <c r="AD65" t="n">
+        <v>0.01662656239100865</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0.01669073104858398</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0.000402716443352365</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.9433962264150944, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>0.8410256410256409, 0.8287545787545787, 0.8672161172161172, 0.8388278388278387, 0.9157509157509157, 0.8672161172161172, 0.9615384615384616</t>
+        </is>
+      </c>
+      <c r="AI65" t="n">
+        <v>0.8743328100470958</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0.04451151604293877</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0.8951781970649896</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0.04010718337465197</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>0.7857142857142856, 0.7333333333333334, 0.8148148148148148, 0.7272727272727273, 0.888888888888889, 0.8148148148148148, 0.9032258064516129</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>0.9249999999999999, 0.8947368421052632, 0.9367088607594937, 0.8767123287671232, 0.9620253164556962, 0.9367088607594937, 0.9600000000000001</t>
+        </is>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0.9274131726924385</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0.02946393194827078</v>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>0.8553571428571427, 0.8140350877192983, 0.8757618377871542, 0.8019925280199253, 0.9254571026722926, 0.8757618377871542, 0.9316129032258065</t>
+        </is>
+      </c>
+      <c r="AU65" t="n">
+        <v>0.8685683485812534</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0.04612899795543637</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0.8097235244700682</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0.06355168081410603</v>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.6875, 0.8461538461538461, 0.631578947368421, 0.9230769230769231, 0.8461538461538461, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.918918918918919, 0.925, 0.9411764705882353, 0.95, 0.925, 1.0</t>
+        </is>
+      </c>
+      <c r="BC65" t="n">
+        <v>0.9375049162710569</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0.02918670159910827</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>0.8005924029530841</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>0.09495227307681021</v>
+      </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ65" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8717948717948718, 0.9487179487179487, 0.8205128205128205, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK65" t="n">
+        <v>0.9194139194139195</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>0.05022457582711388</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>0.8292517006802721</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>0.08070906095218444</v>
+      </c>
+      <c r="BQ65" t="inlineStr">
+        <is>
+          <t>0.976068376068376, 0.9102564102564101, 0.9761904761904762, 0.9340659340659341, 0.9963369963369964, 0.923076923076923, 0.9926739926739927</t>
+        </is>
+      </c>
+      <c r="BR65" t="n">
+        <v>0.9583813012384441</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>0.976068376068376</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>0.0325143136281283</v>
+      </c>
+      <c r="BU65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY65" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ65" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE65" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'estimator': AdaBoostClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8247422680412372</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8545524691358024</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.7519937755300525</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.6792452830188679</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.9764309764309764</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.9895833333333334</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.9819121447028424</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.9970982142857143</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.9740478597910347</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.9709821428571428</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.966183574879227</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>0.051468610763549805, 0.06677556037902832, 0.06499648094177246, 0.06721925735473633, 0.05881047248840332, 0.04910397529602051, 0.06744122505187988</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.06083079746791294</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.06499648094177246</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.00723536857194824</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>0.03287839889526367, 0.016797304153442383, 0.017719030380249023, 0.01660013198852539, 0.016652345657348633, 0.03618192672729492, 0.028240203857421875</t>
+        </is>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.02358133452279227</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0.01771903038024902</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0.007964682280104189</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8113207547169812, 0.8867924528301887, 0.8113207547169812, 0.8867924528301887, 0.7547169811320755, 0.8113207547169812</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7896825396825397, 0.8769349845201238, 0.794891640866873, 0.8769349845201238, 0.7623839009287926, 0.794891640866873</t>
+        </is>
+      </c>
+      <c r="AI66" t="n">
+        <v>0.8196892792204601</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0.794891640866873</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0.04220828358285256</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0.8358790056903265</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0.0483897911592575</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>0.9210526315789475, 0.8571428571428571, 0.9117647058823528, 0.8529411764705882, 0.9117647058823528, 0.7936507936507937, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>0.8125000000000001, 0.7222222222222222, 0.8421052631578947, 0.7368421052631579, 0.8421052631578947, 0.6976744186046512, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0.7700416253812826</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0.05595556089018816</v>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>0.8667763157894738, 0.7896825396825397, 0.8769349845201238, 0.794891640866873, 0.8769349845201238, 0.7456626061277225, 0.794891640866873</t>
+        </is>
+      </c>
+      <c r="AU66" t="n">
+        <v>0.8208249589105329</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0.794891640866873</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0.04836247167788651</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0.8716082924397828</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0.0425161492461217</v>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>0.8536585365853658, 0.8571428571428571, 0.9117647058823529, 0.8529411764705882, 0.9117647058823529, 0.8620689655172413, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>1.0, 0.7222222222222222, 0.8421052631578947, 0.7368421052631579, 0.8421052631578947, 0.625, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BC66" t="n">
+        <v>0.7864452798663325</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0.1114269878550243</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>0.8717545891359065</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>0.02547909229990834</v>
+      </c>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.8529411764705882, 0.9117647058823529, 0.7352941176470589, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ66" t="inlineStr">
+        <is>
+          <t>0.6842105263157895, 0.7222222222222222, 0.8421052631578947, 0.7368421052631579, 0.8421052631578947, 0.7894736842105263, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK66" t="n">
+        <v>0.764828738512949</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>0.05660869509240377</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>0.8745498199279711</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>0.07477266791375879</v>
+      </c>
+      <c r="BQ66" t="inlineStr">
+        <is>
+          <t>0.9398496240601504, 0.8555555555555555, 0.9496904024767803, 0.8885448916408668, 0.9419504643962848, 0.7964396284829721, 0.8916408668730651</t>
+        </is>
+      </c>
+      <c r="BR66" t="n">
+        <v>0.8948102047836678</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>0.8916408668730651</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>0.05144981755245299</v>
+      </c>
+      <c r="BU66" t="inlineStr">
+        <is>
+          <t>0.9182389937106918, 0.9153605015673981, 0.9216300940438872, 0.9404388714733543, 0.9247648902821317, 0.9592476489028213, 0.9278996865203761</t>
+        </is>
+      </c>
+      <c r="BV66" t="inlineStr">
+        <is>
+          <t>0.91474206777466, 0.9107830551989731, 0.9173468511040468, 0.9339075521952058, 0.9237692241601512, 0.9604562247615774, 0.9241988143311282</t>
+        </is>
+      </c>
+      <c r="BW66" t="n">
+        <v>0.9264576842179632</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>0.9237692241601512</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>0.01553654009185822</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.9296543837858088</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>0.9247648902821317</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>0.01423310050294038</v>
+      </c>
+      <c r="CC66" t="inlineStr">
+        <is>
+          <t>0.935960591133005, 0.9336609336609337, 0.9388753056234719, 0.9539951573849879, 0.9408866995073892, 0.9680589680589681, 0.943765281173594</t>
+        </is>
+      </c>
+      <c r="CD66" t="inlineStr">
+        <is>
+          <t>0.8869565217391303, 0.8831168831168831, 0.8908296943231441, 0.9155555555555556, 0.8965517241379309, 0.9437229437229437, 0.8995633187772926</t>
+        </is>
+      </c>
+      <c r="CE66" t="n">
+        <v>0.9023280916246971</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>0.8965517241379309</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>0.01951950967658373</v>
+      </c>
+      <c r="CH66" t="inlineStr">
+        <is>
+          <t>0.9114585564360677, 0.9083889083889084, 0.914852499973308, 0.9347753564702717, 0.9187192118226601, 0.9558909558909559, 0.9216642999754433</t>
+        </is>
+      </c>
+      <c r="CI66" t="n">
+        <v>0.9236785412796592</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>0.9187192118226601</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>0.01535499447742519</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>0.9450289909346214</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>0.9408866995073892</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>0.01120499870491675</v>
+      </c>
+      <c r="CO66" t="inlineStr">
+        <is>
+          <t>0.945273631840796, 0.9405940594059405, 0.9458128078817734, 0.9516908212560387, 0.955, 0.9800995024875622, 0.9507389162561576</t>
+        </is>
+      </c>
+      <c r="CP66" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.8717948717948718, 0.8793103448275862, 0.9196428571428571, 0.8739495798319328, 0.923728813559322, 0.8879310344827587</t>
+        </is>
+      </c>
+      <c r="CQ66" t="n">
+        <v>0.889736053347743</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>0.8793103448275862</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>0.02089040411420355</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>0.9527442484468953</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>0.9507389162561576</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>0.01201196712363182</v>
+      </c>
+      <c r="CW66" t="inlineStr">
+        <is>
+          <t>0.926829268292683, 0.926829268292683, 0.9320388349514563, 0.9563106796116505, 0.9271844660194175, 0.9563106796116505, 0.9368932038834952</t>
+        </is>
+      </c>
+      <c r="CX66" t="inlineStr">
+        <is>
+          <t>0.9026548672566371, 0.8947368421052632, 0.9026548672566371, 0.911504424778761, 0.9203539823008849, 0.9646017699115044, 0.911504424778761</t>
+        </is>
+      </c>
+      <c r="CY66" t="n">
+        <v>0.9154301683412071</v>
+      </c>
+      <c r="CZ66" t="n">
+        <v>0.911504424778761</v>
+      </c>
+      <c r="DA66" t="n">
+        <v>0.02147271909138859</v>
+      </c>
+      <c r="DB66" t="n">
+        <v>0.9374852000947195</v>
+      </c>
+      <c r="DC66" t="n">
+        <v>0.9320388349514563</v>
+      </c>
+      <c r="DD66" t="n">
+        <v>0.01237516867707281</v>
+      </c>
+      <c r="DE66" t="inlineStr">
+        <is>
+          <t>0.9862939779840276, 0.9843816859221224, 0.9824082824984964, 0.9880788727553913, 0.9841481226909529, 0.9948878769653751, 0.9859524014090557</t>
+        </is>
+      </c>
+      <c r="DF66" t="n">
+        <v>0.9865930314607745</v>
+      </c>
+      <c r="DG66" t="n">
+        <v>0.9859524014090557</v>
+      </c>
+      <c r="DH66" t="n">
+        <v>0.00377759897297694</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'estimator': AdaBoostClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 6, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9490909090909091</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.8532927624429472</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8704545454545454</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9423076923076923</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.8909090909090909</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.9158878504672897</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.9730639730639731</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.9958193008942051</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.9663074305161656</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.9776158402043897</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.9952830188679245</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.9678899082568807</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.9813953488372092</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>0.06676530838012695, 0.06592321395874023, 0.05587315559387207, 0.05133795738220215, 0.06651830673217773, 0.0667717456817627, 0.04952597618103027</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.0603879519871303</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.06592321395874023</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.007269428923605925</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>0.016658782958984375, 0.017571687698364258, 0.017281055450439453, 0.01676011085510254, 0.021662473678588867, 0.027605772018432617, 0.03330087661743164</t>
+        </is>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.02154867989676339</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0.01757168769836426</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0.006043721803258766</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.8301886792452831, 0.9245283018867925, 0.8301886792452831, 0.8867924528301887, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>0.7897435897435897, 0.8388278388278387, 0.88003663003663, 0.8388278388278387, 0.8543956043956045, 0.8672161172161172, 0.9029304029304028</t>
+        </is>
+      </c>
+      <c r="AI67" t="n">
+        <v>0.8531397174254316</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.03344720209792343</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.8738145153239492</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0.04410013588092931</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>0.6875, 0.7272727272727273, 0.8461538461538461, 0.7272727272727273, 0.7857142857142857, 0.8148148148148148, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.8767123287671232, 0.9500000000000001, 0.8767123287671232, 0.9230769230769231, 0.9367088607594937, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0.9114784918171701</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0.03362204660054285</v>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>0.7779605263157895, 0.8019925280199253, 0.8980769230769231, 0.8019925280199253, 0.8543956043956045, 0.8757618377871542, 0.9029304029304028</t>
+        </is>
+      </c>
+      <c r="AU67" t="n">
+        <v>0.8447300500779608</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0.0469052625837614</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0.7779816083387512</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0.06054530700835218</v>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>0.6470588235294118, 0.631578947368421, 0.9166666666666666, 0.631578947368421, 0.7857142857142857, 0.8461538461538461, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.9411764705882353, 0.926829268292683, 0.9411764705882353, 0.9230769230769231, 0.925, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BC67" t="n">
+        <v>0.928266996165131</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0.01737969223386602</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0.759413481991987</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0.1119962522792415</v>
+      </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ67" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.8205128205128205, 0.9743589743589743, 0.8205128205128205, 0.9230769230769231, 0.9487179487179487, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK67" t="n">
+        <v>0.8974358974358976</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>0.06129377483766121</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>0.808843537414966</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>0.04520611626077863</v>
+      </c>
+      <c r="BQ67" t="inlineStr">
+        <is>
+          <t>0.8615384615384615, 0.9084249084249084, 0.9816849816849818, 0.9258241758241759, 0.9285714285714286, 0.923992673992674, 0.9780219780219781</t>
+        </is>
+      </c>
+      <c r="BR67" t="n">
+        <v>0.929722658294087</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>0.9258241758241759</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>0.03814435436712547</v>
+      </c>
+      <c r="BU67" t="inlineStr">
+        <is>
+          <t>0.9779874213836478, 0.9655172413793104, 0.9592476489028213, 0.9811912225705329, 0.9623824451410659, 0.9655172413793104, 0.9435736677115988</t>
+        </is>
+      </c>
+      <c r="BV67" t="inlineStr">
+        <is>
+          <t>0.9774114774114774, 0.9652589240824535, 0.9609854198089492, 0.9796882855706385, 0.959376571141277, 0.9652589240824535, 0.9428104575163399</t>
+        </is>
+      </c>
+      <c r="BW67" t="n">
+        <v>0.9643985799447984</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>0.9652589240824535</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>0.01138613346635316</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>0.9650595554954696</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>0.01152864695153742</v>
+      </c>
+      <c r="CC67" t="inlineStr">
+        <is>
+          <t>0.95906432748538, 0.9371428571428572, 0.9265536723163841, 0.9651162790697674, 0.9310344827586207, 0.9371428571428572, 0.898876404494382</t>
+        </is>
+      </c>
+      <c r="CD67" t="inlineStr">
+        <is>
+          <t>0.9849462365591398, 0.9762419006479482, 0.9718004338394794, 0.9871244635193134, 0.9741379310344828, 0.9762419006479482, 0.9608695652173912</t>
+        </is>
+      </c>
+      <c r="CE67" t="n">
+        <v>0.9759089187808146</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0.9762419006479482</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0.008052342267687191</v>
+      </c>
+      <c r="CH67" t="inlineStr">
+        <is>
+          <t>0.9720052820222599, 0.9566923788954027, 0.9491770530779318, 0.9761203712945403, 0.9525862068965517, 0.9566923788954027, 0.9298729848558867</t>
+        </is>
+      </c>
+      <c r="CI67" t="n">
+        <v>0.9561638079911395</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>0.9566923788954027</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0.01415524560871515</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>0.9364186972014641</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0.9371428571428572</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0.02025958966633972</v>
+      </c>
+      <c r="CO67" t="inlineStr">
+        <is>
+          <t>0.9425287356321839, 0.9111111111111111, 0.8913043478260869, 0.9540229885057471, 0.9101123595505618, 0.9111111111111111, 0.8602150537634409</t>
+        </is>
+      </c>
+      <c r="CP67" t="inlineStr">
+        <is>
+          <t>0.9913419913419913, 0.9868995633187773, 0.986784140969163, 0.9913793103448276, 0.9826086956521739, 0.9868995633187773, 0.9778761061946902</t>
+        </is>
+      </c>
+      <c r="CQ67" t="n">
+        <v>0.9862556244486288</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>0.9868995633187773</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>0.004419895690442677</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>0.9114865296428919</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>0.02881275463750477</v>
+      </c>
+      <c r="CW67" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9647058823529412, 0.9647058823529412, 0.9764705882352941, 0.9529411764705882, 0.9647058823529412, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX67" t="inlineStr">
+        <is>
+          <t>0.9786324786324786, 0.9658119658119658, 0.9572649572649573, 0.9829059829059829, 0.9658119658119658, 0.9658119658119658, 0.9444444444444444</t>
+        </is>
+      </c>
+      <c r="CY67" t="n">
+        <v>0.9658119658119658</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>0.9658119658119658</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>0.01186948845862244</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>0.9629851940776311</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>0.01159815469077017</v>
+      </c>
+      <c r="DE67" t="inlineStr">
+        <is>
+          <t>0.9979649979649979, 0.9974358974358974, 0.9936400201106084, 0.9979135243841126, 0.993815987933635, 0.9961287078934138, 0.9934640522875816</t>
+        </is>
+      </c>
+      <c r="DF67" t="n">
+        <v>0.9957661697157495</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>0.9961287078934138</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>0.001926835603890327</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'estimator': RandomForestClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 4, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.9459876543209876</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.8332996564962618</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>0.13564085960388184, 0.12950587272644043, 0.12177205085754395, 0.12537336349487305, 0.12349963188171387, 0.11875104904174805, 0.12027597427368164</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.124974114554269</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.1234996318817139</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.005447175668438657</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>0.01592421531677246, 0.020316600799560547, 0.022830963134765625, 0.02386760711669922, 0.035633087158203125, 0.027849435806274414, 0.034264326095581055</t>
+        </is>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.02581231934683664</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0.02386760711669922</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0.006683472751458865</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8867924528301887, 0.9056603773584906, 0.8113207547169812, 0.9245283018867925, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8873015873015873, 0.891640866873065, 0.8065015479876161, 0.9179566563467492, 0.8560371517027863, 0.8506191950464397</t>
+        </is>
+      </c>
+      <c r="AI68" t="n">
+        <v>0.8721134067662152</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0.8873015873015873</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0.03433196971492287</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.8789058600379356</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0.04163102577854238</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>0.945945945945946, 0.9117647058823529, 0.9275362318840579, 0.8484848484848485, 0.9411764705882353, 0.8524590163934426, 0.8985507246376812</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.8421052631578948, 0.8648648648648649, 0.7500000000000001, 0.8947368421052632, 0.7999999999999999, 0.8108108108108109</t>
+        </is>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0.8349815317307577</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0.0474918049273505</v>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>0.9141494435612083, 0.8769349845201239, 0.8962005483744614, 0.7992424242424243, 0.9179566563467492, 0.8262295081967213, 0.8546807677242461</t>
+        </is>
+      </c>
+      <c r="AU68" t="n">
+        <v>0.869342047566562</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0.8769349845201239</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0.04164083855272224</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0.9037025634023664</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0.03688452555241344</v>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9393939393939394, 0.9142857142857143, 0.875, 0.9411764705882353, 0.9629629629629629, 0.8857142857142857</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.8888888888888888, 0.7142857142857143, 0.8947368421052632, 0.6923076923076923, 0.8333333333333334</t>
+        </is>
+      </c>
+      <c r="BC68" t="n">
+        <v>0.8319360672744132</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0.09985174731428009</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>0.9165670386258622</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0.03007179362222138</v>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8235294117647058, 0.9411764705882353, 0.7647058823529411, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.8888888888888888, 0.8421052631578947, 0.7894736842105263, 0.8947368421052632, 0.9473684210526315, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK68" t="n">
+        <v>0.8487886382623225</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>0.05859875661403568</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>0.895438175270108</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>0.07342641682882577</v>
+      </c>
+      <c r="BQ68" t="inlineStr">
+        <is>
+          <t>0.9917293233082707, 0.9460317460317461, 0.9798761609907121, 0.9280185758513932, 0.955108359133127, 0.9148606811145511, 0.9342105263157895</t>
+        </is>
+      </c>
+      <c r="BR68" t="n">
+        <v>0.9499764818207985</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0.9460317460317461</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>0.02575439529401872</v>
+      </c>
+      <c r="BU68" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV68" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW68" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC68" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD68" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE68" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH68" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI68" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO68" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP68" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW68" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX68" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY68" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE68" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914511, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF68" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>9.712984233463659e-06</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'estimator': RandomForestClassifier(), 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.9763636363636364</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.9160886104273886</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.9227272727272727</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.9541284403669724</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>0.12459063529968262, 0.1246042251586914, 0.11680150032043457, 0.11636209487915039, 0.11678647994995117, 0.11964631080627441, 0.11691546440124512</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.1193866729736328</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.1169154644012451</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.003444883418388293</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>0.020977020263671875, 0.010089397430419922, 0.01904606819152832, 0.02005791664123535, 0.019046545028686523, 0.013752460479736328, 0.03292989730834961</t>
+        </is>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.01941418647766113</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.01904654502868652</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0.006598796216883572</v>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7735849056603774, 0.9245283018867925, 0.8113207547169812, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>0.8076923076923077, 0.7087912087912087, 0.88003663003663, 0.7573260073260073, 0.9157509157509157, 0.9157509157509157, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI69" t="n">
+        <v>0.8462846677132392</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.88003663003663</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0.08248649449301339</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.8871418588399721</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0.06526507708554194</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>0.7407407407407408, 0.5714285714285714, 0.8461538461538461, 0.6428571428571429, 0.888888888888889, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>0.9135802469135802, 0.8461538461538461, 0.9500000000000001, 0.8717948717948718, 0.9620253164556962, 0.9620253164556962, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0.9238026512589502</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0.04445452206824584</v>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>0.8271604938271605, 0.7087912087912087, 0.8980769230769231, 0.7573260073260073, 0.9254571026722926, 0.9254571026722926, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU69" t="n">
+        <v>0.8530091687077616</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0.08357570924821299</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0.7822156861565729</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0.1227607107172277</v>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.5714285714285714, 0.9166666666666666, 0.6428571428571429, 0.9230769230769231, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.8461538461538461, 0.926829268292683, 0.8717948717948718, 0.95, 0.95, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC69" t="n">
+        <v>0.9142020825314425</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0.04439277259849604</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>0.8110151753008896</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0.1339253318386625</v>
+      </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.5714285714285714, 0.7857142857142857, 0.6428571428571429, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ69" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8461538461538461, 0.9743589743589743, 0.8717948717948718, 0.9743589743589743, 0.9743589743589743, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK69" t="n">
+        <v>0.9340659340659341</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>0.04914435115384153</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>0.7585034013605442</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>0.123014566802892</v>
+      </c>
+      <c r="BQ69" t="inlineStr">
+        <is>
+          <t>0.9555555555555555, 0.8562271062271063, 0.967032967032967, 0.9194139194139194, 0.9853479853479854, 0.9368131868131868, 0.9862637362637363</t>
+        </is>
+      </c>
+      <c r="BR69" t="n">
+        <v>0.9438077795220653</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0.9555555555555555</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>0.04229129530917896</v>
+      </c>
+      <c r="BU69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE69" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 0.9999999999999999</t>
+        </is>
+      </c>
+      <c r="DF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'estimator': LGBMClassifier(verbose=-1), 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 7, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.9517746913580247</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>0.017925739288330078, 0.015625715255737305, 0.023902177810668945, 0.031249523162841797, 0.031249523162841797, 0.01562666893005371, 0.031249046325683594</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.02383262770516532</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.02390217781066895</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.006913870953922988</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>0.01562666893005371, 0.015625715255737305, 0.01562643051147461, 0.01562666893005371, 0.01562356948852539, 0.0312502384185791, 0.0156252384185791</t>
+        </is>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.01785778999328613</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0.01562643051147461</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0.005467444268321678</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.9245283018867925, 0.8490566037735849, 0.9056603773584906, 0.9056603773584906, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8595238095238096, 0.9179566563467492, 0.8591331269349844, 0.903250773993808, 0.914860681114551, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI70" t="n">
+        <v>0.8970040647838082</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0.903250773993808</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0.03064824639320071</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0.9003693720674851</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0.03469788342272107</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8985507246376812, 0.9411764705882353, 0.8749999999999999, 0.9253731343283583, 0.923076923076923, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8108108108108109, 0.8947368421052632, 0.8095238095238095, 0.8717948717948718, 0.8780487804878049, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0.8644949746178427</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0.04463918848749161</v>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8546807677242461, 0.9179566563467492, 0.8422619047619047, 0.898584003061615, 0.900562851782364, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU70" t="n">
+        <v>0.8927592145043336</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0.898584003061615</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0.03641046495388324</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0.9210234543908248</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0.02868424330801915</v>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9117647058823529, 0.9411764705882353, 0.9333333333333333, 0.9393939393939394, 0.967741935483871, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>1.0, 0.7894736842105263, 0.8947368421052632, 0.7391304347826086, 0.85, 0.8181818181818182, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC70" t="n">
+        <v>0.8476611489197301</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0.0769910128609483</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>0.9358744337871474</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0.01823061274071979</v>
+      </c>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9411764705882353, 0.8235294117647058, 0.9117647058823529, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ70" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK70" t="n">
+        <v>0.8859649122807018</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>0.03539961627023942</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>0.9080432172869148</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>0.05054378033187065</v>
+      </c>
+      <c r="BQ70" t="inlineStr">
+        <is>
+          <t>0.9939849624060151, 0.9587301587301588, 0.9845201238390092, 0.9442724458204335, 0.9597523219814241, 0.9342105263157895, 0.9442724458204335</t>
+        </is>
+      </c>
+      <c r="BR70" t="n">
+        <v>0.9599632835590376</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>0.9587301587301588</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>0.02041598610767627</v>
+      </c>
+      <c r="BU70" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV70" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW70" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC70" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD70" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE70" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH70" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI70" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO70" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP70" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW70" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX70" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY70" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE70" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914511, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF70" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>9.712984233453664e-06</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_smote_opt-smote_default-model</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'estimator': LGBMClassifier(verbose=-1), 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {'k_neighbors': 3, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.980909090909091</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8858943707889591</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.9045454545454545</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.9345794392523366</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>0.018818140029907227, 0.031249046325683594, 0.03212714195251465, 0.031248807907104492, 0.03125, 0.0312502384185791, 0.031247854232788086</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.02959874698093959</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.03124904632568359</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.004411576841219736</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>0.015626907348632812, 0.015624523162841797, 0.01562643051147461, 0.015625715255737305, 0.009752511978149414, 0.015624523162841797, 0.01562643051147461</t>
+        </is>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.01478672027587891</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0.0156257152557373</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0.002055207114787563</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8679245283018868, 0.9056603773584906, 0.8679245283018868, 0.9433962264150944, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>0.8333333333333333, 0.8644688644688645, 0.8672161172161172, 0.8644688644688645, 0.9157509157509157, 0.9029304029304028, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI71" t="n">
+        <v>0.8819989534275249</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0.03093646373846525</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0.9059099530797645</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0.02669027688607385</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>0.8, 0.7741935483870968, 0.8148148148148148, 0.7741935483870968, 0.888888888888889, 0.8571428571428571, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>0.9397590361445783, 0.9066666666666667, 0.9367088607594937, 0.9066666666666667, 0.9620253164556962, 0.9487179487179487, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0.9354161309233833</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0.9397590361445783</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0.01964484562333443</v>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>0.8698795180722891, 0.8404301075268817, 0.8757618377871542, 0.8404301075268817, 0.9254571026722926, 0.9029304029304028, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU71" t="n">
+        <v>0.8802723743393643</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0.03064431636352031</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0.8251286177553459</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0.04266527150878797</v>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>1.0, 0.7058823529411765, 0.8461538461538461, 0.7058823529411765, 0.9230769230769231, 0.8571428571428571, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>0.8863636363636364, 0.9444444444444444, 0.925, 0.9444444444444444, 0.95, 0.9487179487179487, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC71" t="n">
+        <v>0.938849063849064</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0.02505796900711914</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>0.8358054760365684</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>0.09960041652786275</v>
+      </c>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>1.0, 0.8717948717948718, 0.9487179487179487, 0.8717948717948718, 0.9743589743589743, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK71" t="n">
+        <v>0.9340659340659341</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>0.04516054214629286</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>0.8299319727891156</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>0.07681353599072255</v>
+      </c>
+      <c r="BQ71" t="inlineStr">
+        <is>
+          <t>0.958974358974359, 0.9157509157509158, 0.9835164835164836, 0.9377289377289377, 0.9835164835164836, 0.9065934065934067, 0.9908424908424909</t>
+        </is>
+      </c>
+      <c r="BR71" t="n">
+        <v>0.9538461538461539</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>0.958974358974359</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>0.03184677222556585</v>
+      </c>
+      <c r="BU71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE71" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH71" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH71"/>
+  <dimension ref="A1:DH87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28288,6 +28288,6246 @@
       </c>
       <c r="DH71" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 6, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8757716049382716</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.793956043956044</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.7893518518518519</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.7307692307692308</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.9044943820224719</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.8385416666666666</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.8702702702702703</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.9141617063492063</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.8279922779922779</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.8383184523809524</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0.7394957983193278</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.8380952380952381</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0.02599787712097168, 0.02200007438659668, 0.023999929428100586, 0.022001981735229492, 0.021999359130859375, 0.023030757904052734, 0.021968841552734375</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.02299983160836356</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.02200198173522949</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.001416662754772428</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>0.018001317977905273, 0.01600193977355957, 0.01500082015991211, 0.015000104904174805, 0.016000032424926758, 0.014998197555541992, 0.015001296997070312</t>
+        </is>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.01571481568472726</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0.01500129699707031</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0.001030612379537579</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8490566037735849, 0.7924528301886793, 0.8301886792452831, 0.7358490566037735, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.788888888888889, 0.8475232198142415, 0.791795665634675, 0.8095975232198143, 0.7476780185758514, 0.686532507739938</t>
+        </is>
+      </c>
+      <c r="AI72" t="n">
+        <v>0.798687545193516</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0.791795665634675</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0.06788063679845971</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0.8061295797144854</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0.7924528301886793</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0.06550205976124417</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8358208955223881, 0.8787878787878787, 0.8307692307692308, 0.8695652173913043, 0.7741935483870968, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.717948717948718, 0.8, 0.7317073170731707, 0.7567567567567567, 0.6818181818181819, 0.5945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0.7396517728995265</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0.08693701651622963</v>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.776884806735553, 0.8393939393939394, 0.7812382739212007, 0.8131609870740305, 0.7280058651026393, 0.6886016451233843</t>
+        </is>
+      </c>
+      <c r="AU72" t="n">
+        <v>0.7922975014045642</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0.7812382739212007</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0.06959226509356455</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0.8449432299096022</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0.8358208955223881</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0.05413484183944401</v>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.875, 0.90625, 0.8709677419354839, 0.8571428571428571, 0.8571428571428571, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6666666666666666, 0.7619047619047619, 0.6818181818181818, 0.7777777777777778, 0.6, 0.6111111111111112</t>
+        </is>
+      </c>
+      <c r="BC72" t="n">
+        <v>0.713430763054823</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0.09701564406500213</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>0.8686841672152731</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>0.0488188797698017</v>
+      </c>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.8529411764705882, 0.7941176470588235, 0.8823529411764706, 0.7058823529411765, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ72" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7777777777777778, 0.8421052631578947, 0.7894736842105263, 0.7368421052631579, 0.7894736842105263, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="BK72" t="n">
+        <v>0.7727652464494569</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>0.09190400211651173</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>0.824609843937575</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>0.07038746140524818</v>
+      </c>
+      <c r="BQ72" t="inlineStr">
+        <is>
+          <t>0.9548872180451128, 0.8492063492063493, 0.9396284829721362, 0.8746130030959752, 0.9349845201238391, 0.848297213622291, 0.871517027863777</t>
+        </is>
+      </c>
+      <c r="BR72" t="n">
+        <v>0.8961619735613544</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>0.8746130030959752</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>0.04211002473245857</v>
+      </c>
+      <c r="BU72" t="inlineStr">
+        <is>
+          <t>0.8144654088050315, 0.8275862068965517, 0.8213166144200627, 0.8213166144200627, 0.8275862068965517, 0.8401253918495298, 0.8401253918495298</t>
+        </is>
+      </c>
+      <c r="BV72" t="inlineStr">
+        <is>
+          <t>0.8084394560759767, 0.8249679075738126, 0.8177034109459576, 0.8177034109459576, 0.8265529684680815, 0.8462496778073718, 0.8342641120371166</t>
+        </is>
+      </c>
+      <c r="BW72" t="n">
+        <v>0.8251258491220391</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>0.8249679075738126</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>0.0114667624801676</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>0.8275031193053316</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>0.008985583023744357</v>
+      </c>
+      <c r="CC72" t="inlineStr">
+        <is>
+          <t>0.8521303258145363, 0.8614609571788414, 0.8571428571428572, 0.8571428571428572, 0.8614609571788413, 0.8695652173913043, 0.8734491315136476</t>
+        </is>
+      </c>
+      <c r="CD72" t="inlineStr">
+        <is>
+          <t>0.7510548523206751, 0.7717842323651452, 0.7615062761506276, 0.7615062761506276, 0.7717842323651452, 0.7935222672064777, 0.7829787234042553</t>
+        </is>
+      </c>
+      <c r="CE72" t="n">
+        <v>0.7705909799947077</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0.7717842323651452</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0.01324964578919523</v>
+      </c>
+      <c r="CH72" t="inlineStr">
+        <is>
+          <t>0.8015925890676057, 0.8166225947719933, 0.8093245666467423, 0.8093245666467423, 0.8166225947719932, 0.8315437422988909, 0.8282139274589515</t>
+        </is>
+      </c>
+      <c r="CI72" t="n">
+        <v>0.8161777973804168</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>0.8166225947719932</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>0.009914190583272548</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>0.8617646147661266</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>0.8614609571788413</v>
+      </c>
+      <c r="CN72" t="n">
+        <v>0.006898266443295649</v>
+      </c>
+      <c r="CO72" t="inlineStr">
+        <is>
+          <t>0.8762886597938144, 0.890625, 0.8860103626943006, 0.8860103626943006, 0.8952879581151832, 0.918918918918919, 0.8934010152284264</t>
+        </is>
+      </c>
+      <c r="CP72" t="inlineStr">
+        <is>
+          <t>0.717741935483871, 0.7322834645669292, 0.7222222222222222, 0.7222222222222222, 0.7265625, 0.7313432835820896, 0.7540983606557377</t>
+        </is>
+      </c>
+      <c r="CQ72" t="n">
+        <v>0.7294962841047246</v>
+      </c>
+      <c r="CR72" t="n">
+        <v>0.7265625</v>
+      </c>
+      <c r="CS72" t="n">
+        <v>0.01114218307562259</v>
+      </c>
+      <c r="CT72" t="n">
+        <v>0.8923631824921349</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>0.890625</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>0.0122880124135262</v>
+      </c>
+      <c r="CW72" t="inlineStr">
+        <is>
+          <t>0.8292682926829268, 0.8341463414634146, 0.8300970873786407, 0.8300970873786407, 0.8300970873786407, 0.8252427184466019, 0.8543689320388349</t>
+        </is>
+      </c>
+      <c r="CX72" t="inlineStr">
+        <is>
+          <t>0.7876106194690266, 0.8157894736842105, 0.8053097345132744, 0.8053097345132744, 0.8230088495575221, 0.8672566371681416, 0.8141592920353983</t>
+        </is>
+      </c>
+      <c r="CY72" t="n">
+        <v>0.8169206201344068</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>0.8141592920353983</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>0.02301672386489479</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>0.8333310781096716</v>
+      </c>
+      <c r="DC72" t="n">
+        <v>0.8300970873786407</v>
+      </c>
+      <c r="DD72" t="n">
+        <v>0.008916756520241553</v>
+      </c>
+      <c r="DE72" t="inlineStr">
+        <is>
+          <t>0.8983595942154112, 0.9132648694908002, 0.9037073631755306, 0.9125139616805568, 0.902547469713893, 0.9174327691382421, 0.9096357075350116</t>
+        </is>
+      </c>
+      <c r="DF72" t="n">
+        <v>0.9082088192784922</v>
+      </c>
+      <c r="DG72" t="n">
+        <v>0.9096357075350116</v>
+      </c>
+      <c r="DH72" t="n">
+        <v>0.006330610174223876</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 2, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.7083333333333333</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9536363636363636</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.7855392156862745</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.835016835016835</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.6339285714285714</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.8987341772151899</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.7434554973821988</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.9450121937057253</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0.8109337040260871</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.8553303913598885</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.9567567567567568</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.8119266055045872</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.8784119106699753</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>0.030034542083740234, 0.023005247116088867, 0.021969079971313477, 0.020972490310668945, 0.021999120712280273, 0.021998167037963867, 0.021998882293701172</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.02313964707510812</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.02199888229370117</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.002866794069568396</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>0.014995574951171875, 0.014993667602539062, 0.015999317169189453, 0.01399850845336914, 0.012999773025512695, 0.012002944946289062, 0.012999773025512695</t>
+        </is>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.01399850845336914</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0.01399850845336914</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0.0013073931243411</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7169811320754716, 0.8490566037735849, 0.8113207547169812, 0.8301886792452831, 0.8679245283018868, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>0.8692307692307693, 0.739010989010989, 0.8745421245421245, 0.848901098901099, 0.8617216117216118, 0.8644688644688645, 0.8974358974358974</t>
+        </is>
+      </c>
+      <c r="AI73" t="n">
+        <v>0.8507587650444793</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0.8644688644688645</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0.04763669807041433</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0.8278426674653091</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0.04911208851918584</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>0.7878787878787877, 0.5945945945945946, 0.7647058823529412, 0.7222222222222223, 0.742857142857143, 0.7741935483870968, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>0.9066666666666667, 0.7826086956521738, 0.8888888888888888, 0.8571428571428572, 0.8732394366197183, 0.9066666666666667, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0.8715610710501797</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0.8857142857142858</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0.03980057310385378</v>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>0.8472727272727272, 0.6886016451233843, 0.826797385620915, 0.7896825396825398, 0.8080482897384307, 0.8404301075268817, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU73" t="n">
+        <v>0.8046541038158443</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0.826797385620915</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0.05074362506646927</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0.737747136581509</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0.7647058823529412</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0.06202595656055507</v>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>0.7222222222222222, 0.4782608695652174, 0.65, 0.5909090909090909, 0.6190476190476191, 0.7058823529411765, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9, 0.9696969696969697, 0.967741935483871, 0.96875, 0.9444444444444444, 1.0</t>
+        </is>
+      </c>
+      <c r="BC73" t="n">
+        <v>0.9564396848671043</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0.02884874594131466</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>0.6289551130069946</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>0.07499403846082844</v>
+      </c>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7857142857142857, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ73" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.6923076923076923, 0.8205128205128205, 0.7692307692307693, 0.7948717948717948, 0.8717948717948718, 0.7948717948717948</t>
+        </is>
+      </c>
+      <c r="BK73" t="n">
+        <v>0.8021978021978021</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>0.7948717948717948</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>0.05768503937004989</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>0.8993197278911564</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>0.0637571402114829</v>
+      </c>
+      <c r="BQ73" t="inlineStr">
+        <is>
+          <t>0.9538461538461538, 0.8827838827838828, 0.9725274725274726, 0.9322344322344323, 0.9194139194139195, 0.9468864468864469, 0.9963369963369964</t>
+        </is>
+      </c>
+      <c r="BR73" t="n">
+        <v>0.9434327577184721</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>0.9468864468864469</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>0.03411392844861806</v>
+      </c>
+      <c r="BU73" t="inlineStr">
+        <is>
+          <t>0.8238993710691824, 0.8495297805642633, 0.8338557993730408, 0.8432601880877743, 0.8463949843260188, 0.8307210031347962, 0.8369905956112853</t>
+        </is>
+      </c>
+      <c r="BV73" t="inlineStr">
+        <is>
+          <t>0.8421855921855922, 0.8712166918049271, 0.8567873303167421, 0.8631975867269985, 0.8615887380593263, 0.8583961789844143, 0.8589240824534943</t>
+        </is>
+      </c>
+      <c r="BW73" t="n">
+        <v>0.8588994572187849</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>0.8589240824534943</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>0.008119541474916534</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>0.8378073888809087</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>0.8369905956112853</v>
+      </c>
+      <c r="CB73" t="n">
+        <v>0.008458523298807166</v>
+      </c>
+      <c r="CC73" t="inlineStr">
+        <is>
+          <t>0.7254901960784315, 0.7647058823529411, 0.7439613526570049, 0.7549019607843137, 0.7562189054726368, 0.7428571428571429, 0.7475728155339805</t>
+        </is>
+      </c>
+      <c r="CD73" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.8894009216589861, 0.8770301624129929, 0.8847926267281105, 0.8878718535469109, 0.8738317757009346, 0.8796296296296297</t>
+        </is>
+      </c>
+      <c r="CE73" t="n">
+        <v>0.8804181914354193</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0.8796296296296297</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>0.006674282797560359</v>
+      </c>
+      <c r="CH73" t="inlineStr">
+        <is>
+          <t>0.7979302832244008, 0.8270534020059637, 0.8104957575349989, 0.8198472937562121, 0.8220453795097739, 0.8083444592790388, 0.813601222581805</t>
+        </is>
+      </c>
+      <c r="CI73" t="n">
+        <v>0.8141882568417419</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>0.813601222581805</v>
+      </c>
+      <c r="CK73" t="n">
+        <v>0.009037397475924984</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>0.7479583222480646</v>
+      </c>
+      <c r="CM73" t="n">
+        <v>0.7475728155339805</v>
+      </c>
+      <c r="CN73" t="n">
+        <v>0.01161215635745573</v>
+      </c>
+      <c r="CO73" t="inlineStr">
+        <is>
+          <t>0.6166666666666667, 0.6554621848739496, 0.6311475409836066, 0.6470588235294118, 0.6551724137931034, 0.624, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="CP73" t="inlineStr">
+        <is>
+          <t>0.9494949494949495, 0.965, 0.9593908629441624, 0.96, 0.9556650246305419, 0.9639175257731959, 0.9595959595959596</t>
+        </is>
+      </c>
+      <c r="CQ73" t="n">
+        <v>0.9590091889198299</v>
+      </c>
+      <c r="CR73" t="n">
+        <v>0.9595959595959596</v>
+      </c>
+      <c r="CS73" t="n">
+        <v>0.004827857498428118</v>
+      </c>
+      <c r="CT73" t="n">
+        <v>0.6379816094586249</v>
+      </c>
+      <c r="CU73" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CV73" t="n">
+        <v>0.01405410262388774</v>
+      </c>
+      <c r="CW73" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9176470588235294, 0.9058823529411765, 0.9058823529411765, 0.8941176470588236, 0.9176470588235294, 0.9058823529411765</t>
+        </is>
+      </c>
+      <c r="CX73" t="inlineStr">
+        <is>
+          <t>0.8034188034188035, 0.8247863247863247, 0.8076923076923077, 0.8205128205128205, 0.8290598290598291, 0.7991452991452992, 0.811965811965812</t>
+        </is>
+      </c>
+      <c r="CY73" t="n">
+        <v>0.8137973137973137</v>
+      </c>
+      <c r="CZ73" t="n">
+        <v>0.811965811965812</v>
+      </c>
+      <c r="DA73" t="n">
+        <v>0.0104322390052717</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>0.9040016006402561</v>
+      </c>
+      <c r="DC73" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD73" t="n">
+        <v>0.01202359473425372</v>
+      </c>
+      <c r="DE73" t="inlineStr">
+        <is>
+          <t>0.9442918192918194, 0.9548516842634489, 0.9425842131724483, 0.9491201608848667, 0.9474610356963299, 0.9497234791352438, 0.9373554550025138</t>
+        </is>
+      </c>
+      <c r="DF73" t="n">
+        <v>0.9464839782066673</v>
+      </c>
+      <c r="DG73" t="n">
+        <v>0.9474610356963299</v>
+      </c>
+      <c r="DH73" t="n">
+        <v>0.005233963743647618</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 2, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.8719135802469136</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.784688995215311</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.787037037037037</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8956228956228957</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.9447513812154696</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.890625</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.9168900804289546</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.978546626984127</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.8883092936081425</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.8976934523809523</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.8189655172413793</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.8597285067873304</v>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>0.022999048233032227, 0.024000883102416992, 0.021998882293701172, 0.021001100540161133, 0.02100086212158203, 0.021117448806762695, 0.021028518676757812</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.02187810625348772</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.0211174488067627</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.001109464118630983</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>0.021013498306274414, 0.01699686050415039, 0.01800060272216797, 0.018029451370239258, 0.017998456954956055, 0.018002033233642578, 0.01800060272216797</t>
+        </is>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.01829164368765695</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0.01800060272216797</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0.001164531986372037</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8301886792452831, 0.8490566037735849, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.8023809523809524, 0.8560371517027863, 0.8707430340557275, 0.8769349845201238, 0.8560371517027863, 0.8738390092879257</t>
+        </is>
+      </c>
+      <c r="AI74" t="n">
+        <v>0.8632484572776479</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0.8707430340557275</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0.02941905328084738</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0.8546470999301187</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0.0403309423454746</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8307692307692307, 0.8524590163934426, 0.8709677419354839, 0.9117647058823528, 0.8524590163934426, 0.8923076923076922</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7317073170731708, 0.7999999999999999, 0.8181818181818181, 0.8421052631578947, 0.7999999999999999, 0.8292682926829269</t>
+        </is>
+      </c>
+      <c r="AQ74" t="n">
+        <v>0.8157359399978141</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>0.04438766094713988</v>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.7812382739212007, 0.8262295081967213, 0.8445747800586509, 0.8769349845201238, 0.8262295081967213, 0.8607879924953096</t>
+        </is>
+      </c>
+      <c r="AU74" t="n">
+        <v>0.8475231020079134</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>0.8445747800586509</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0.03987669207850535</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0.8793102640180128</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0.03651319522787613</v>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.9, 0.9629629629629629, 0.9642857142857143, 0.9117647058823529, 0.9629629629629629, 0.9354838709677419</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6521739130434783, 0.6923076923076923, 0.72, 0.8421052631578947, 0.6923076923076923, 0.7727272727272727</t>
+        </is>
+      </c>
+      <c r="BC74" t="n">
+        <v>0.7589711863046092</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0.0941971519667644</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>0.9366255908543791</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>0.02514734870933703</v>
+      </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.7647058823529411, 0.7941176470588235, 0.9117647058823529, 0.7647058823529411, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8333333333333334, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.8947368421052632</t>
+        </is>
+      </c>
+      <c r="BK74" t="n">
+        <v>0.8934837092731829</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>0.05015663182002379</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>0.8330132052821128</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>0.07596526346750566</v>
+      </c>
+      <c r="BQ74" t="inlineStr">
+        <is>
+          <t>0.9338345864661655, 0.8674603174603175, 0.9303405572755418, 0.9334365325077398, 0.869969040247678, 0.926470588235294, 0.9140866873065016</t>
+        </is>
+      </c>
+      <c r="BR74" t="n">
+        <v>0.9107997584998913</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>0.926470588235294</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>0.02732529744158788</v>
+      </c>
+      <c r="BU74" t="inlineStr">
+        <is>
+          <t>0.8930817610062893, 0.9090909090909091, 0.9122257053291536, 0.8871473354231975, 0.9090909090909091, 0.8871473354231975, 0.9028213166144201</t>
+        </is>
+      </c>
+      <c r="BV74" t="inlineStr">
+        <is>
+          <t>0.9051586445067991, 0.9136927685066325, 0.9140604862960735, 0.8906478219778331, 0.9156284904201393, 0.8926454162728756, 0.9067789328980154</t>
+        </is>
+      </c>
+      <c r="BW74" t="n">
+        <v>0.905516080125481</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>0.9067789328980154</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>0.009491105590848795</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>0.9000864674254394</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>0.9028213166144201</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>0.01000648805486076</v>
+      </c>
+      <c r="CC74" t="inlineStr">
+        <is>
+          <t>0.9123711340206185, 0.9269521410579346, 0.9303482587064676, 0.9095477386934674, 0.9269521410579346, 0.909090909090909, 0.9223057644110276</t>
+        </is>
+      </c>
+      <c r="CD74" t="inlineStr">
+        <is>
+          <t>0.8629032258064516, 0.8796680497925311, 0.8813559322033898, 0.85, 0.8796680497925311, 0.8512396694214877, 0.8702928870292888</t>
+        </is>
+      </c>
+      <c r="CE74" t="n">
+        <v>0.8678754020065258</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>0.8702928870292888</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>0.01245966144652293</v>
+      </c>
+      <c r="CH74" t="inlineStr">
+        <is>
+          <t>0.8876371799135351, 0.9033100954252329, 0.9058520954549287, 0.8797738693467336, 0.9033100954252329, 0.8801652892561983, 0.8962993257201581</t>
+        </is>
+      </c>
+      <c r="CI74" t="n">
+        <v>0.8937639929345743</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>0.8962993257201581</v>
+      </c>
+      <c r="CK74" t="n">
+        <v>0.01037161247919862</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>0.9196525838626227</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>0.9223057644110276</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>0.008406462476321659</v>
+      </c>
+      <c r="CO74" t="inlineStr">
+        <is>
+          <t>0.9672131147540983, 0.9583333333333334, 0.9540816326530612, 0.9427083333333334, 0.9633507853403142, 0.9473684210526315, 0.9533678756476683</t>
+        </is>
+      </c>
+      <c r="CP74" t="inlineStr">
+        <is>
+          <t>0.7925925925925926, 0.8346456692913385, 0.8455284552845529, 0.8031496062992126, 0.828125, 0.7984496124031008, 0.8253968253968254</t>
+        </is>
+      </c>
+      <c r="CQ74" t="n">
+        <v>0.8182696801810889</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>0.01866969245704389</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>0.9552033565877772</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>0.9540816326530612</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>0.007951196825951095</v>
+      </c>
+      <c r="CW74" t="inlineStr">
+        <is>
+          <t>0.8634146341463415, 0.8975609756097561, 0.9077669902912622, 0.8786407766990292, 0.8932038834951457, 0.8737864077669902, 0.8932038834951457</t>
+        </is>
+      </c>
+      <c r="CX74" t="inlineStr">
+        <is>
+          <t>0.9469026548672567, 0.9298245614035088, 0.9203539823008849, 0.9026548672566371, 0.9380530973451328, 0.911504424778761, 0.9203539823008849</t>
+        </is>
+      </c>
+      <c r="CY74" t="n">
+        <v>0.9242353671790094</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>0.9203539823008849</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>0.01411129162159032</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>0.8867967930719528</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>0.8932038834951457</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>0.01424396863531745</v>
+      </c>
+      <c r="DE74" t="inlineStr">
+        <is>
+          <t>0.9802719620116555, 0.9780059905862216, 0.9781338602972764, 0.9726136266002233, 0.978047942263081, 0.9755348397628663, 0.9748260159807544</t>
+        </is>
+      </c>
+      <c r="DF74" t="n">
+        <v>0.976776319643154</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>0.9780059905862216</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>0.00238640545441958</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 9, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8070325900514579</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.8272727272727273</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9215686274509803</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.776595744680851</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.9240506329113924</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.8439306358381502</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.9757287190802462</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.8898988096055359</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.9138601788410173</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.9704433497536946</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9036697247706422</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9358669833729216</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>0.020586490631103516, 0.020001649856567383, 0.018970251083374023, 0.01899862289428711, 0.020032167434692383, 0.01997065544128418, 0.019028902053833008</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01965553419930594</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01997065544128418</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.0006001717819131063</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>0.01598048210144043, 0.016000747680664062, 0.016000032424926758, 0.01600050926208496, 0.015999317169189453, 0.015999794006347656, 0.016000032424926758</t>
+        </is>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01599727358136858</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0.01600003242492676</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>6.868603752941738e-06</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7169811320754716, 0.9056603773584906, 0.7735849056603774, 0.8679245283018868, 0.8867924528301887, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>0.9153846153846155, 0.6932234432234432, 0.8901098901098901, 0.7316849816849818, 0.7957875457875458, 0.8543956043956045, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AI75" t="n">
+        <v>0.8327577184720043</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0.08870799170794878</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0.8546970150743737</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>0.07270486457271676</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>0.8484848484848485, 0.5454545454545454, 0.8275862068965518, 0.6000000000000001, 0.7200000000000001, 0.7857142857142857, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7945205479452054, 0.935064935064935, 0.8421052631578947, 0.9135802469135802, 0.9230769230769231, 0.945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ75" t="n">
+        <v>0.8982324564911168</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0.0529480933225103</v>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>0.8909090909090909, 0.6699875466998755, 0.8813255709807435, 0.7210526315789474, 0.8167901234567901, 0.8543956043956045, 0.910472972972973</t>
+        </is>
+      </c>
+      <c r="AU75" t="n">
+        <v>0.8207047915705751</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0.08490203204859594</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0.7431771266500331</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>0.1180389626084289</v>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.47368421052631576, 0.8, 0.5625, 0.8181818181818182, 0.7857142857142857, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8529411764705882, 0.9473684210526315, 0.8648648648648649, 0.8809523809523809, 0.9230769230769231, 1.0</t>
+        </is>
+      </c>
+      <c r="BC75" t="n">
+        <v>0.9202037126628017</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0.05202589111095973</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>0.7136622671397107</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>0.1266215565701244</v>
+      </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.6428571428571429, 0.8571428571428571, 0.6428571428571429, 0.6428571428571429, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ75" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.7435897435897436, 0.9230769230769231, 0.8205128205128205, 0.9487179487179487, 0.9230769230769231, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="BK75" t="n">
+        <v>0.8791208791208792</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>0.06674310314391428</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>0.7863945578231293</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0.1383747715384067</v>
+      </c>
+      <c r="BQ75" t="inlineStr">
+        <is>
+          <t>0.9641025641025641, 0.8369963369963369, 0.9294871794871795, 0.9065934065934067, 0.9358974358974359, 0.8873626373626373, 0.9642857142857143</t>
+        </is>
+      </c>
+      <c r="BR75" t="n">
+        <v>0.917817896389325</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>0.9294871794871795</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0.04200375309506077</v>
+      </c>
+      <c r="BU75" t="inlineStr">
+        <is>
+          <t>0.8867924528301887, 0.9122257053291536, 0.896551724137931, 0.8871473354231975, 0.896551724137931, 0.8934169278996865, 0.9122257053291536</t>
+        </is>
+      </c>
+      <c r="BV75" t="inlineStr">
+        <is>
+          <t>0.8887362637362637, 0.9176973353443942, 0.9107591754650578, 0.889366515837104, 0.8807943690296631, 0.9086224233283057, 0.9102061337355455</t>
+        </is>
+      </c>
+      <c r="BW75" t="n">
+        <v>0.9008831737823335</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>0.9086224233283057</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>0.01315189239171046</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>0.8978445107267489</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>0.009806420226618663</v>
+      </c>
+      <c r="CC75" t="inlineStr">
+        <is>
+          <t>0.806451612903226, 0.8494623655913979, 0.8290155440414507, 0.8085106382978723, 0.8135593220338984, 0.8247422680412371, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="CD75" t="inlineStr">
+        <is>
+          <t>0.9199999999999999, 0.9380530973451328, 0.9258426966292135, 0.9199999999999999, 0.9284164859002169, 0.9234234234234234, 0.9385964912280702</t>
+        </is>
+      </c>
+      <c r="CE75" t="n">
+        <v>0.9277617420751509</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0.9258426966292135</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0.007238049226197113</v>
+      </c>
+      <c r="CH75" t="inlineStr">
+        <is>
+          <t>0.863225806451613, 0.8937577314682653, 0.8774291203353322, 0.8642553191489362, 0.8709879039670576, 0.8740828457323302, 0.8923751686909582</t>
+        </is>
+      </c>
+      <c r="CI75" t="n">
+        <v>0.8765876993992132</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>0.8740828457323302</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0.01142067025576777</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0.8254136567232754</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0.8247422680412371</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0.01607001022093031</v>
+      </c>
+      <c r="CO75" t="inlineStr">
+        <is>
+          <t>0.7352941176470589, 0.7821782178217822, 0.7407407407407407, 0.7378640776699029, 0.782608695652174, 0.7339449541284404, 0.7938144329896907</t>
+        </is>
+      </c>
+      <c r="CP75" t="inlineStr">
+        <is>
+          <t>0.9583333333333334, 0.9724770642201835, 0.976303317535545, 0.9583333333333334, 0.9427312775330396, 0.9761904761904762, 0.963963963963964</t>
+        </is>
+      </c>
+      <c r="CQ75" t="n">
+        <v>0.9640475380156965</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>0.963963963963964</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>0.01126566342652547</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>0.7580636052356843</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>0.02469921668306894</v>
+      </c>
+      <c r="CW75" t="inlineStr">
+        <is>
+          <t>0.8928571428571429, 0.9294117647058824, 0.9411764705882353, 0.8941176470588236, 0.8470588235294118, 0.9411764705882353, 0.9058823529411765</t>
+        </is>
+      </c>
+      <c r="CX75" t="inlineStr">
+        <is>
+          <t>0.8846153846153846, 0.905982905982906, 0.8803418803418803, 0.8846153846153846, 0.9145299145299145, 0.8760683760683761, 0.9145299145299145</t>
+        </is>
+      </c>
+      <c r="CY75" t="n">
+        <v>0.8943833943833945</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>0.0154445795368419</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>0.9073829531812726</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>0.03116200091248069</v>
+      </c>
+      <c r="DE75" t="inlineStr">
+        <is>
+          <t>0.9729090354090353, 0.9817496229260935, 0.9752639517345401, 0.9681749622926094, 0.9738310708898945, 0.9760180995475113, 0.9789592760180995</t>
+        </is>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.9752722884025405</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.9752639517345401</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>0.004038036200787137</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8659793814432989</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.9066358024691358</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.8103481812876872</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8078703703703703</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.7547169811320754</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.9388888888888889</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.8802083333333334</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.9086021505376345</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.9488839285714286</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.8777244986922406</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.8877232142857143</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.8034188034188035</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.8952380952380953</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.8468468468468467</v>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>0.030999183654785156, 0.028998136520385742, 0.029997825622558594, 0.03000020980834961, 0.029002904891967773, 0.03096771240234375, 0.030028581619262695</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.02999922207423619</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.03000020980834961</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.0007496267452733052</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>0.01600027084350586, 0.01600170135498047, 0.017000198364257812, 0.015999555587768555, 0.01599740982055664, 0.016001462936401367, 0.016001224517822266</t>
+        </is>
+      </c>
+      <c r="AD76" t="n">
+        <v>0.01614311763218471</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0.01600122451782227</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0.0003499044125579084</v>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7547169811320755, 0.8867924528301887, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.7924528301886793</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.7333333333333334, 0.8769349845201238, 0.8854489164086687, 0.8885448916408669, 0.8591331269349844, 0.7685758513931888</t>
+        </is>
+      </c>
+      <c r="AI76" t="n">
+        <v>0.8455340030749142</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0.06196209882034177</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0.8519516821403614</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>0.05497812695603441</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8115942028985507, 0.9117647058823528, 0.888888888888889, 0.9090909090909091, 0.8749999999999999, 0.8405797101449276</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.6486486486486486, 0.8421052631578947, 0.8372093023255814, 0.8500000000000001, 0.8095238095238095, 0.7027027027027027</t>
+        </is>
+      </c>
+      <c r="AQ76" t="n">
+        <v>0.7970112307496465</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>0.0810297910883178</v>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.7301214257735996, 0.8769349845201238, 0.8630490956072352, 0.8795454545454546, 0.8422619047619047, 0.7716412064238152</t>
+        </is>
+      </c>
+      <c r="AU76" t="n">
+        <v>0.8400315340426859</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0.8630490956072352</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0.06104846976951613</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0.8830518373357247</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0.04188503423221462</v>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.8235294117647058, 0.9117647058823529, 0.9655172413793104, 0.9375, 0.9333333333333333, 0.8285714285714286</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.631578947368421, 0.8421052631578947, 0.75, 0.8095238095238095, 0.7391304347826086, 0.7222222222222222</t>
+        </is>
+      </c>
+      <c r="BC76" t="n">
+        <v>0.7765338782347416</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0.09146418310824614</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>0.9027335771214358</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>0.918918918918919</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>0.05099536169503403</v>
+      </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.9117647058823529, 0.8235294117647058, 0.8823529411764706, 0.8235294117647058, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ76" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.6666666666666666, 0.8421052631578947, 0.9473684210526315, 0.8947368421052632, 0.8947368421052632, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BK76" t="n">
+        <v>0.8245614035087717</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>0.1001252348643518</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>0.8665066026410564</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0.05556109731189546</v>
+      </c>
+      <c r="BQ76" t="inlineStr">
+        <is>
+          <t>0.9609022556390978, 0.8507936507936508, 0.9349845201238389, 0.9287925696594427, 0.9287925696594428, 0.9117647058823529, 0.8730650154798762</t>
+        </is>
+      </c>
+      <c r="BR76" t="n">
+        <v>0.9127278981768148</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>0.9287925696594427</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>0.03533956964575925</v>
+      </c>
+      <c r="BU76" t="inlineStr">
+        <is>
+          <t>0.8805031446540881, 0.8840125391849529, 0.877742946708464, 0.877742946708464, 0.8808777429467085, 0.877742946708464, 0.8840125391849529</t>
+        </is>
+      </c>
+      <c r="BV76" t="inlineStr">
+        <is>
+          <t>0.8815022663500971, 0.8824989302524604, 0.8753758913996048, 0.8753758913996048, 0.8798006701606668, 0.8713807028095197, 0.8822278546266862</t>
+        </is>
+      </c>
+      <c r="BW76" t="n">
+        <v>0.8783088867140914</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>0.8798006701606668</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>0.00397388836117678</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>0.8803764008708707</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>0.8805031446540881</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>0.002605369565733566</v>
+      </c>
+      <c r="CC76" t="inlineStr">
+        <is>
+          <t>0.9045226130653267, 0.9077306733167082, 0.903225806451613, 0.903225806451613, 0.9054726368159205, 0.9041769041769042, 0.9081885856079405</t>
+        </is>
+      </c>
+      <c r="CD76" t="inlineStr">
+        <is>
+          <t>0.8403361344537816, 0.8438818565400843, 0.8340425531914893, 0.8340425531914893, 0.8389830508474576, 0.8311688311688311, 0.8425531914893618</t>
+        </is>
+      </c>
+      <c r="CE76" t="n">
+        <v>0.8378583101260707</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0.8389830508474576</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0.004465723556690434</v>
+      </c>
+      <c r="CH76" t="inlineStr">
+        <is>
+          <t>0.8724293737595541, 0.8758062649283962, 0.8686341798215511, 0.8686341798215511, 0.872227843831689, 0.8676728676728677, 0.8753708885486511</t>
+        </is>
+      </c>
+      <c r="CI76" t="n">
+        <v>0.8715393711977514</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>0.8722278438316891</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>0.003070205433312542</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0.9052204322694324</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0.9045226130653267</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0.001878746478652035</v>
+      </c>
+      <c r="CO76" t="inlineStr">
+        <is>
+          <t>0.9326424870466321, 0.9285714285714286, 0.9238578680203046, 0.9238578680203046, 0.9285714285714286, 0.9154228855721394, 0.9289340101522843</t>
+        </is>
+      </c>
+      <c r="CP76" t="inlineStr">
+        <is>
+          <t>0.8, 0.8130081300813008, 0.8032786885245902, 0.8032786885245902, 0.8048780487804879, 0.8135593220338984, 0.8114754098360656</t>
+        </is>
+      </c>
+      <c r="CQ76" t="n">
+        <v>0.8070683268258474</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>0.8048780487804879</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>0.005075402040445072</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>0.925979710850646</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>0.005168661977231579</v>
+      </c>
+      <c r="CW76" t="inlineStr">
+        <is>
+          <t>0.8780487804878049, 0.8878048780487805, 0.883495145631068, 0.883495145631068, 0.883495145631068, 0.8932038834951457, 0.8883495145631068</t>
+        </is>
+      </c>
+      <c r="CX76" t="inlineStr">
+        <is>
+          <t>0.8849557522123894, 0.8771929824561403, 0.8672566371681416, 0.8672566371681416, 0.8761061946902655, 0.8495575221238938, 0.8761061946902655</t>
+        </is>
+      </c>
+      <c r="CY76" t="n">
+        <v>0.8712045600727484</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>0.8761061946902655</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>0.01050697030024156</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>0.8854132133554344</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>0.883495145631068</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>0.004477057210473288</v>
+      </c>
+      <c r="DE76" t="inlineStr">
+        <is>
+          <t>0.9405784588819339, 0.9568677792041078, 0.9498453475384483, 0.9496949909786064, 0.9399218145888822, 0.9515422287138071, 0.9540123721969241</t>
+        </is>
+      </c>
+      <c r="DF76" t="n">
+        <v>0.9489232845861014</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>0.9498453475384483</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>0.005951962278805937</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 4, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.9581818181818181</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.8952380952380952</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.9023569023569024</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.9240506329113924</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.9620833817210545</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.8825366518922604</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.9092730228777146</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.9701492537313433</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.8944954128440367</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0.9307875894988066</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>0.030004262924194336, 0.030002832412719727, 0.031032562255859375, 0.03299856185913086, 0.031032085418701172, 0.029036998748779297, 0.030008792877197266</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.030588013785226</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.03000879287719727</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.00117290310067865</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>0.013970613479614258, 0.014001846313476562, 0.013997554779052734, 0.0618748664855957, 0.013998746871948242, 0.013994455337524414, 0.01499629020690918</t>
+        </is>
+      </c>
+      <c r="AD77" t="n">
+        <v>0.02097633906773158</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0.01399874687194824</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0.01670034727159658</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7547169811320755, 0.9056603773584906, 0.8490566037735849, 0.9056603773584906, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>0.9358974358974359, 0.7417582417582418, 0.8901098901098901, 0.8287545787545787, 0.8901098901098901, 0.7930402930402931, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI77" t="n">
+        <v>0.8557038199895343</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0.8901098901098901</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0.06481967345841085</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.8600878506538885</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0.05150996207507519</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.6060606060606061, 0.8275862068965518, 0.7333333333333334, 0.8275862068965518, 0.689655172413793, 0.8</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>0.9315068493150686, 0.8219178082191781, 0.935064935064935, 0.8947368421052632, 0.935064935064935, 0.8831168831168831, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ77" t="n">
+        <v>0.9004023862272126</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0.9014084507042254</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0.03753512710333558</v>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>0.8943248532289628, 0.7139892071398921, 0.8813255709807435, 0.8140350877192983, 0.8813255709807435, 0.7863860277653381, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU77" t="n">
+        <v>0.8317272204524414</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0.8507042253521127</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0.06027278251910256</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0.7630520546776703</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0.08406134073281447</v>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>0.75, 0.5263157894736842, 0.8, 0.6875, 0.8, 0.6666666666666666, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>1.0, 0.8823529411764706, 0.9473684210526315, 0.918918918918919, 0.9473684210526315, 0.8947368421052632, 1.0</t>
+        </is>
+      </c>
+      <c r="BC77" t="n">
+        <v>0.9415350777579878</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0.04327394604594365</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>0.6995927318295739</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>0.08867558541176399</v>
+      </c>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>1.0, 0.7142857142857143, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ77" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7692307692307693, 0.9230769230769231, 0.8717948717948718, 0.9230769230769231, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK77" t="n">
+        <v>0.8644688644688643</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>0.05075606762106601</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>0.8469387755102041</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0.1108446988897981</v>
+      </c>
+      <c r="BQ77" t="inlineStr">
+        <is>
+          <t>0.9658119658119658, 0.8644688644688645, 0.9652014652014652, 0.9249084249084248, 0.9505494505494505, 0.9212454212454213, 0.9908424908424908</t>
+        </is>
+      </c>
+      <c r="BR77" t="n">
+        <v>0.9404325832897262</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0.9505494505494505</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>0.03832334910963749</v>
+      </c>
+      <c r="BU77" t="inlineStr">
+        <is>
+          <t>0.8773584905660378, 0.896551724137931, 0.8746081504702194, 0.8840125391849529, 0.8840125391849529, 0.8746081504702194, 0.8746081504702194</t>
+        </is>
+      </c>
+      <c r="BV77" t="inlineStr">
+        <is>
+          <t>0.8746947496947497, 0.8995223730517848, 0.8883107088989441, 0.8909753645047762, 0.864756158873806, 0.8733283056812469, 0.8845651080945198</t>
+        </is>
+      </c>
+      <c r="BW77" t="n">
+        <v>0.8823075383999753</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>0.8845651080945198</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>0.01107925032144553</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>0.8808228206406475</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>0.8773584905660378</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>0.0075177406641899</v>
+      </c>
+      <c r="CC77" t="inlineStr">
+        <is>
+          <t>0.7891891891891892, 0.823529411764706, 0.7959183673469388, 0.8062827225130891, 0.7909604519774012, 0.7872340425531914, 0.7938144329896907</t>
+        </is>
+      </c>
+      <c r="CD77" t="inlineStr">
+        <is>
+          <t>0.9135254988913524, 0.926829268292683, 0.9095022624434389, 0.9172259507829978, 0.9197396963123645, 0.9111111111111111, 0.9099099099099099</t>
+        </is>
+      </c>
+      <c r="CE77" t="n">
+        <v>0.9154062425348368</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0.9135254988913524</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0.005850856848822022</v>
+      </c>
+      <c r="CH77" t="inlineStr">
+        <is>
+          <t>0.8513573440402709, 0.8751793400286945, 0.8527103148951889, 0.8617543366480435, 0.8553500741448828, 0.8491725768321512, 0.8518621714498003</t>
+        </is>
+      </c>
+      <c r="CI77" t="n">
+        <v>0.8567694511484333</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>0.8527103148951889</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0.008395144064080168</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0.7981326597620295</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0.7938144329896907</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0.01186335772721111</v>
+      </c>
+      <c r="CO77" t="inlineStr">
+        <is>
+          <t>0.7227722772277227, 0.7549019607843137, 0.7027027027027027, 0.7264150943396226, 0.7608695652173914, 0.7184466019417476, 0.7064220183486238</t>
+        </is>
+      </c>
+      <c r="CP77" t="inlineStr">
+        <is>
+          <t>0.9493087557603687, 0.9631336405529954, 0.9663461538461539, 0.9624413145539906, 0.933920704845815, 0.9490740740740741, 0.9619047619047619</t>
+        </is>
+      </c>
+      <c r="CQ77" t="n">
+        <v>0.9551613436483085</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>0.9619047619047619</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>0.01075441129331724</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>0.7275043172231606</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>0.7227722772277227</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>0.02080204272319971</v>
+      </c>
+      <c r="CW77" t="inlineStr">
+        <is>
+          <t>0.8690476190476191, 0.9058823529411765, 0.9176470588235294, 0.9058823529411765, 0.8235294117647058, 0.8705882352941177, 0.9058823529411765</t>
+        </is>
+      </c>
+      <c r="CX77" t="inlineStr">
+        <is>
+          <t>0.8803418803418803, 0.8931623931623932, 0.8589743589743589, 0.8760683760683761, 0.905982905982906, 0.8760683760683761, 0.8632478632478633</t>
+        </is>
+      </c>
+      <c r="CY77" t="n">
+        <v>0.8791208791208793</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>0.8760683760683761</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>0.01510295100958851</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>0.8854941976790717</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>0.03073655213832839</v>
+      </c>
+      <c r="DE77" t="inlineStr">
+        <is>
+          <t>0.9552808302808302, 0.9605329311211663, 0.9559074912016088, 0.9574157868275515, 0.9592257415786827, 0.9582704876822524, 0.9564102564102565</t>
+        </is>
+      </c>
+      <c r="DF77" t="n">
+        <v>0.9575776464431928</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>0.9574157868275515</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>0.001747804137641099</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 7, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.9529320987654322</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8233908948194661</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.818287037037037</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.9997767857142857</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>1.5212345123291016, 1.4071695804595947, 1.3986170291900635, 1.4634394645690918, 1.4384980201721191, 1.4530487060546875, 1.4374234676361084</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.445632968630109</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>1.438498020172119</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.03759918702749595</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>0.016000986099243164, 0.01576709747314453, 0.017000675201416016, 0.01548004150390625, 0.017002105712890625, 0.016001224517822266, 0.017000198364257812</t>
+        </is>
+      </c>
+      <c r="AD78" t="n">
+        <v>0.01632176126752581</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0.01600122451782227</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0.0006101351360797819</v>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>0.9814814814814815, 0.8679245283018868, 0.9056603773584906, 0.8301886792452831, 0.9245283018867925, 0.8679245283018868, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>0.9736842105263157, 0.8595238095238096, 0.903250773993808, 0.8212074303405572, 0.9179566563467492, 0.8738390092879257, 0.8243034055727554</t>
+        </is>
+      </c>
+      <c r="AI78" t="n">
+        <v>0.8819664707988458</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0.05035144708288122</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0.889537785764201</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0.04785875900816195</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>0.9859154929577464, 0.8985507246376812, 0.9253731343283583, 0.8656716417910447, 0.9411764705882353, 0.8923076923076922, 0.8857142857142858</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>0.972972972972973, 0.8108108108108109, 0.8717948717948718, 0.7692307692307692, 0.8947368421052632, 0.8292682926829269, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0.8466560481964845</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0.06678942786701694</v>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>0.9794442329653597, 0.8546807677242461, 0.898584003061615, 0.8174512055109069, 0.9179566563467492, 0.8607879924953096, 0.8317460317460318</t>
+        </is>
+      </c>
+      <c r="AU78" t="n">
+        <v>0.8800929842643168</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0.8607879924953096</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0.05199743095035948</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0.9135299203321493</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0.8985507246376812</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0.03757496925812932</v>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.9117647058823529, 0.9393939393939394, 0.8787878787878788, 0.9411764705882353, 0.9354838709677419, 0.8611111111111112</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>1.0, 0.7894736842105263, 0.85, 0.75, 0.8947368421052632, 0.7727272727272727, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BC78" t="n">
+        <v>0.8400667444011096</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0.07941383416610909</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>0.9199914569933545</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>0.03590789462232686</v>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>1.0, 0.8857142857142857, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353, 0.8529411764705882, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8333333333333334, 0.8947368421052632, 0.7894736842105263, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK78" t="n">
+        <v>0.8558897243107768</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>0.06759951859278786</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>0.9080432172869147</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>0.04803661149198953</v>
+      </c>
+      <c r="BQ78" t="inlineStr">
+        <is>
+          <t>0.9984962406015038, 0.9476190476190477, 0.9814241486068112, 0.9551083591331269, 0.955108359133127, 0.9427244582043344, 0.9473684210526316</t>
+        </is>
+      </c>
+      <c r="BR78" t="n">
+        <v>0.9611212906215119</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>0.9551083591331269</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0.01924020733853268</v>
+      </c>
+      <c r="BU78" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 0.9968652037617555, 0.9968652037617555, 0.9937304075235109, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV78" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 0.9956140350877193, 0.995575221238938, 0.9931480367729186, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW78" t="n">
+        <v>0.9958661366880558</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>0.001885242517235258</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>0.9968637954974975</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>0.001675622622249898</v>
+      </c>
+      <c r="CC78" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 0.9975669099756691, 0.9975786924939467, 0.9951456310679612, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD78" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 0.9955947136563876, 0.9955555555555555, 0.9911504424778761, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE78" t="n">
+        <v>0.9955667683366408</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0.002365186821933608</v>
+      </c>
+      <c r="CH78" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 0.9965808118160284, 0.9965671240247511, 0.9931480367729186, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI78" t="n">
+        <v>0.9965702076326874</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>0.001831273974945286</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0.9975736469287341</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>0.001297393947929273</v>
+      </c>
+      <c r="CO78" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 0.9951456310679612, 0.9951690821256038, 0.9951456310679612, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP78" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9911504424778761, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ78" t="n">
+        <v>0.9987357774968394</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>0.003096700054087461</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>0.9958491627972421</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>0.001694606963530478</v>
+      </c>
+      <c r="CW78" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX78" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 0.9912280701754386, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY78" t="n">
+        <v>0.9924257546521169</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>0.003092288713291248</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>0.9993065187239945</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>0.001698675272387779</v>
+      </c>
+      <c r="DE78" t="inlineStr">
+        <is>
+          <t>0.9994603928340168, 0.9999572100984168, 0.9995059713033766, 0.9996348483546696, 0.9994200532691812, 1.0, 0.9995918893375719</t>
+        </is>
+      </c>
+      <c r="DF78" t="n">
+        <v>0.9996529093138904</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>0.9995918893375719</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>0.0002171226970828094</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CatBoostClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'estimator': 'CatBoostClassifier', 'estimator_params': {'verbose': False}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 7, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.979090909090909</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.8977272727272727</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.9875</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.9937106918238994</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.9998838694692833</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.9957059206245933</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.9977064220183487</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.9954128440366973</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.9977011494252873</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>1.369708776473999, 1.3298521041870117, 1.404482126235962, 1.3510429859161377, 1.344148874282837, 1.376110315322876, 1.350316047668457</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.360808747155326</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1.351042985916138</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.02287245534223611</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>0.014877557754516602, 0.014001607894897461, 0.014999866485595703, 0.013999462127685547, 0.01400136947631836, 0.014001607894897461, 0.013001203536987305</t>
+        </is>
+      </c>
+      <c r="AD79" t="n">
+        <v>0.01412609645298549</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0.01400160789489746</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0.0006159939822632492</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9433962264150944, 0.9433962264150944, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>0.8410256410256409, 0.8745421245421245, 0.88003663003663, 0.8772893772893773, 0.8928571428571428, 0.9157509157509157, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI79" t="n">
+        <v>0.8885923600209314</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0.88003663003663</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>0.02908600775488407</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0.9113507038035341</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0.03431491006265949</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>0.7857142857142856, 0.7647058823529412, 0.8461538461538461, 0.7999999999999999, 0.88, 0.888888888888889, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>0.9249999999999999, 0.8888888888888888, 0.9500000000000001, 0.9210526315789475, 0.962962962962963, 0.9620253164556962, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0.9387098229893509</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0.02602127334831665</v>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>0.8553571428571427, 0.826797385620915, 0.8980769230769231, 0.8605263157894737, 0.9214814814814816, 0.9254571026722926, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU79" t="n">
+        <v>0.8880702420123823</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0.8980769230769231</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0.03752319932713236</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>0.8374306610354133</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0.04985124040726818</v>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.65, 0.9166666666666666, 0.75, 1.0, 0.9230769230769231, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.9696969696969697, 0.926829268292683, 0.9459459459459459, 0.9285714285714286, 0.95, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC79" t="n">
+        <v>0.9424524067747981</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0.02337488742705745</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>0.8503663003663006</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>0.108612228051589</v>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8205128205128205, 0.9743589743589743, 0.8974358974358975, 1.0, 0.9743589743589743, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK79" t="n">
+        <v>0.9377289377289377</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>0.8394557823129251</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>0.06922750603106696</v>
+      </c>
+      <c r="BQ79" t="inlineStr">
+        <is>
+          <t>0.9709401709401709, 0.9065934065934066, 0.9835164835164836, 0.9304029304029304, 0.9816849816849818, 0.9175824175824175, 0.9890109890109889</t>
+        </is>
+      </c>
+      <c r="BR79" t="n">
+        <v>0.9542473399616257</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0.9709401709401709</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>0.03225000246914392</v>
+      </c>
+      <c r="BU79" t="inlineStr">
+        <is>
+          <t>0.9937106918238994, 1.0, 1.0, 1.0, 0.9968652037617555, 1.0, 0.9937304075235109</t>
+        </is>
+      </c>
+      <c r="BV79" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 1.0, 1.0, 1.0, 0.9978632478632479, 1.0, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="BW79" t="n">
+        <v>0.9973935728137409</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>0.003520381297075402</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>0.9977580433013095</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>0.002764715065114586</v>
+      </c>
+      <c r="CC79" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9941520467836257, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CD79" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 1.0, 1.0, 0.9978586723768736, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CE79" t="n">
+        <v>0.9984730948328379</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0.001881901994348784</v>
+      </c>
+      <c r="CH79" t="inlineStr">
+        <is>
+          <t>0.9919108669108669, 1.0, 1.0, 1.0, 0.9960053595802496, 1.0, 0.9919808949220714</t>
+        </is>
+      </c>
+      <c r="CI79" t="n">
+        <v>0.997128160201884</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0.003544916394044739</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0.9957832255709301</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0.005207987152011779</v>
+      </c>
+      <c r="CO79" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 0.9883720930232558, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CP79" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 1.0, 1.0, 1.0, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CQ79" t="n">
+        <v>0.9987789987789988</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>0.001930572442105231</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>0.9949575178908773</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>0.005823026954887153</v>
+      </c>
+      <c r="CW79" t="inlineStr">
+        <is>
+          <t>0.9880952380952381, 1.0, 1.0, 1.0, 1.0, 1.0, 0.9882352941176471</t>
+        </is>
+      </c>
+      <c r="CX79" t="inlineStr">
+        <is>
+          <t>0.9957264957264957, 1.0, 1.0, 1.0, 0.9957264957264957, 1.0, 0.9957264957264957</t>
+        </is>
+      </c>
+      <c r="CY79" t="n">
+        <v>0.9981684981684982</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>0.002114836150877742</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>0.9966186474589837</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>0.005346518833527797</v>
+      </c>
+      <c r="DE79" t="inlineStr">
+        <is>
+          <t>0.9998982498982498, 1.0, 0.9999999999999999, 1.0, 1.0, 1.0, 0.9999497234791351</t>
+        </is>
+      </c>
+      <c r="DF79" t="n">
+        <v>0.999978281911055</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>3.69924394678528e-05</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>XGBClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9019607843137255</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9292929292929293</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.9421296296296297</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.8960190136660724</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.8865740740740741</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.8627450980392156</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>0.04624176025390625, 0.048256635665893555, 0.046860456466674805, 0.047483205795288086, 0.056001901626586914, 0.05306220054626465, 0.04600119590759277</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.04912962232317243</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.04748320579528809</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.003574554922245634</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>0.017999649047851562, 0.01800084114074707, 0.017805099487304688, 0.018000125885009766, 0.018431425094604492, 0.017454862594604492, 0.019001007080078125</t>
+        </is>
+      </c>
+      <c r="AD80" t="n">
+        <v>0.01809900147574289</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0.01800012588500977</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0.0004558658305699464</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8301886792452831, 0.9056603773584906, 0.8679245283018868, 0.9245283018867925, 0.8113207547169812, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.8444444444444444, 0.903250773993808, 0.8738390092879257, 0.9179566563467492, 0.8297213622291022, 0.8653250773993808</t>
+        </is>
+      </c>
+      <c r="AI80" t="n">
+        <v>0.8831293921077202</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0.03872376319073297</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0.884196865328941</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0.04897629594103543</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8615384615384616, 0.9253731343283583, 0.8923076923076922, 0.9411764705882353, 0.8387096774193549, 0.9142857142857143</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7804878048780488, 0.8717948717948718, 0.8292682926829269, 0.8947368421052632, 0.7727272727272727, 0.8333333333333333</t>
+        </is>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0.8466846945665943</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0.05710868951970268</v>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.8210131332082552, 0.898584003061615, 0.8607879924953096, 0.9179566563467492, 0.8057184750733137, 0.8738095238095238</t>
+        </is>
+      </c>
+      <c r="AU80" t="n">
+        <v>0.8766004453325856</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0.8738095238095238</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0.04963567821859501</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0.906516196098577</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0.0426901932372783</v>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9333333333333333, 0.9393939393939394, 0.9354838709677419, 0.9411764705882353, 0.9285714285714286, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>1.0, 0.6956521739130435, 0.85, 0.7727272727272727, 0.8947368421052632, 0.68, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BC80" t="n">
+        <v>0.8250670328460069</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0.1068315454245203</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>0.9303991253842163</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>0.01772675903731844</v>
+      </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.8529411764705882, 0.9411764705882353, 0.7647058823529411, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ80" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK80" t="n">
+        <v>0.8788638262322472</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>0.03654911086754779</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>0.8873949579831933</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0.07831824574576308</v>
+      </c>
+      <c r="BQ80" t="inlineStr">
+        <is>
+          <t>0.9924812030075187, 0.9444444444444445, 0.978328173374613, 0.9690402476780186, 0.9489164086687306, 0.9465944272445821, 0.931888544891641</t>
+        </is>
+      </c>
+      <c r="BR80" t="n">
+        <v>0.9588133499013641</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0.9489164086687306</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>0.01999144171032029</v>
+      </c>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV80" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW80" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC80" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD80" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE80" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH80" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI80" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO80" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP80" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW80" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX80" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY80" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE80" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF80" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>9.712984233453662e-06</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>XGBClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'estimator': 'XGBClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 2, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9918181818181817</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.9318181818181819</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9318181818181819</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>0.04399824142456055, 0.04052376747131348, 0.0429990291595459, 0.0410006046295166, 0.04400157928466797, 0.04200148582458496, 0.04300189018249512</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.04250379971095494</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.0429990291595459</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.001276294210075594</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>0.01599907875061035, 0.01600050926208496, 0.01699995994567871, 0.015999794006347656, 0.01599907875061035, 0.01599884033203125, 0.01600027084350586</t>
+        </is>
+      </c>
+      <c r="AD81" t="n">
+        <v>0.01614250455583845</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0.01599979400634766</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0.0003500551938698708</v>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.9245283018867925, 0.8867924528301887, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>0.8205128205128205, 0.8186813186813187, 0.8543956043956045, 0.8287545787545787, 0.88003663003663, 0.8543956043956045, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI81" t="n">
+        <v>0.8546572475143904</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0.03553678025461151</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0.8897873614854747</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0.02554992364329579</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>0.7692307692307692, 0.7407407407407408, 0.7857142857142857, 0.7333333333333334, 0.8461538461538461, 0.7857142857142857, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>0.9268292682926831, 0.9113924050632911, 0.9230769230769231, 0.8947368421052632, 0.9500000000000001, 0.9230769230769231, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0.9252115403811023</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0.01787576592953244</v>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>0.8480300187617261, 0.826066572902016, 0.8543956043956045, 0.8140350877192983, 0.8980769230769231, 0.8543956043956045, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU81" t="n">
+        <v>0.8574310507301173</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0.03181341717342787</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0.7896505610791325</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0.046500167184395</v>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.7692307692307693, 0.7857142857142857, 0.6875, 0.9166666666666666, 0.7857142857142857, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>0.8837209302325582, 0.9, 0.9230769230769231, 0.918918918918919, 0.926829268292683, 0.9230769230769231, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC81" t="n">
+        <v>0.9212279909387114</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0.02557480230206304</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>0.8094881309167024</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>0.07468904489068662</v>
+      </c>
+      <c r="BI81" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.7142857142857143, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ81" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.9230769230769231, 0.9230769230769231, 0.8717948717948718, 0.9743589743589743, 0.9230769230769231, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK81" t="n">
+        <v>0.9304029304029304</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>0.03276290076922767</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>0.7789115646258503</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>0.07498437988111771</v>
+      </c>
+      <c r="BQ81" t="inlineStr">
+        <is>
+          <t>0.9863247863247864, 0.9285714285714285, 0.9780219780219781, 0.9413919413919414, 0.9853479853479853, 0.9194139194139194, 0.9945054945054944</t>
+        </is>
+      </c>
+      <c r="BR81" t="n">
+        <v>0.9619396476539334</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>0.9780219780219781</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>0.02879941674144619</v>
+      </c>
+      <c r="BU81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX81" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE81" t="inlineStr">
+        <is>
+          <t>0.9999999999999999, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 3, 'sampling_strategy': 0.6}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.836734693877551</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.8777006172839507</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.7645211930926217</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.9494949494949495</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.9538461538461539</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.9612403100775193</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.994593253968254</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.9443882709807886</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.9415178571428571</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>0.07396793365478516, 0.07299995422363281, 0.08366131782531738, 0.07398295402526855, 0.07351970672607422, 0.07400083541870117, 0.07426261901855469</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.07519933155604772</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.07398295402526855</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.003475903794058703</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>0.021999835968017578, 0.02299976348876953, 0.02549457550048828, 0.021997690200805664, 0.02300095558166504, 0.022002696990966797, 0.02357029914855957</t>
+        </is>
+      </c>
+      <c r="AD82" t="n">
+        <v>0.02300940241132464</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0.02299976348876953</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0.001167848846288765</v>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7547169811320755, 0.8301886792452831, 0.7547169811320755, 0.9245283018867925, 0.7924528301886793, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>0.868421052631579, 0.7333333333333334, 0.8095975232198143, 0.7275541795665634, 0.9179566563467492, 0.791795665634675, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AI82" t="n">
+        <v>0.8120816747751732</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0.8095975232198143</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0.06404850403938193</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0.830438254966557</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0.8301886792452831</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0.06328417504179591</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.8115942028985507, 0.8695652173913043, 0.8115942028985507, 0.9411764705882353, 0.8307692307692308, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>0.8484848484848484, 0.6486486486486486, 0.7567567567567567, 0.6486486486486486, 0.8947368421052632, 0.7317073170731707, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0.7597795351325518</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0.7567567567567567</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0.08657051979992111</v>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>0.8909090909090909, 0.7301214257735996, 0.8131609870740305, 0.7301214257735996, 0.9179566563467492, 0.7812382739212007, 0.8359133126934984</t>
+        </is>
+      </c>
+      <c r="AU82" t="n">
+        <v>0.8142030246416813</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0.8131609870740305</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0.06797811041618552</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0.8686265141508108</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0.05011174306207925</v>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>0.875, 0.8235294117647058, 0.8571428571428571, 0.8, 0.9411764705882353, 0.8709677419354839, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>1.0, 0.631578947368421, 0.7777777777777778, 0.6666666666666666, 0.8947368421052632, 0.6818181818181818, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BC82" t="n">
+        <v>0.7774360142781196</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0.1231295116482396</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>0.8643099175153933</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>0.04182071268808042</v>
+      </c>
+      <c r="BI82" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.8823529411764706, 0.8235294117647058, 0.9411764705882353, 0.7941176470588235, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="BJ82" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.6666666666666666, 0.7368421052631579, 0.631578947368421, 0.8947368421052632, 0.7894736842105263, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK82" t="n">
+        <v>0.7493734335839599</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>0.08051317495844118</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>0.8747899159663864</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0.0706382375921597</v>
+      </c>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>0.9308270676691729, 0.8396825396825397, 0.9473684210526315, 0.8978328173374613, 0.955108359133127, 0.8134674922600619, 0.9055727554179566</t>
+        </is>
+      </c>
+      <c r="BR82" t="n">
+        <v>0.8985513503647073</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>0.9055727554179566</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>0.04982560982156527</v>
+      </c>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>0.9276729559748428, 0.9247648902821317, 0.9247648902821317, 0.9373040752351097, 0.9216300940438872, 0.9623824451410659, 0.9467084639498433</t>
+        </is>
+      </c>
+      <c r="BV82" t="inlineStr">
+        <is>
+          <t>0.9280164040578459, 0.9181001283697048, 0.9197740355700661, 0.9274851791391012, 0.9153492568090043, 0.9628834092275969, 0.9427571097173297</t>
+        </is>
+      </c>
+      <c r="BW82" t="n">
+        <v>0.9306236461272356</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>0.9274851791391012</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>0.015640699909156</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.9350325449870017</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>0.9276729559748428</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>0.01380549931688482</v>
+      </c>
+      <c r="CC82" t="inlineStr">
+        <is>
+          <t>0.9429280397022332, 0.9414634146341464, 0.9414634146341464, 0.951923076923077, 0.9391727493917275, 0.9705882352941178, 0.9586374695863747</t>
+        </is>
+      </c>
+      <c r="CD82" t="inlineStr">
+        <is>
+          <t>0.9012875536480688, 0.8947368421052632, 0.8947368421052632, 0.9099099099099099, 0.8898678414096916, 0.9478260869565217, 0.9251101321585904</t>
+        </is>
+      </c>
+      <c r="CE82" t="n">
+        <v>0.9090678868990442</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0.9012875536480688</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0.01927320022898514</v>
+      </c>
+      <c r="CH82" t="inlineStr">
+        <is>
+          <t>0.922107796675151, 0.9181001283697048, 0.9181001283697048, 0.9309164934164935, 0.9145202954007094, 0.9592071611253197, 0.9418738008724825</t>
+        </is>
+      </c>
+      <c r="CI82" t="n">
+        <v>0.9292608291756521</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>0.922107796675151</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0.015005631186926</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0.9494537714522604</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>0.9429280397022332</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0.01077748669650606</v>
+      </c>
+      <c r="CO82" t="inlineStr">
+        <is>
+          <t>0.9595959595959596, 0.9414634146341463, 0.946078431372549, 0.9428571428571428, 0.9414634146341463, 0.9801980198019802, 0.9609756097560975</t>
+        </is>
+      </c>
+      <c r="CP82" t="inlineStr">
+        <is>
+          <t>0.875, 0.8947368421052632, 0.8869565217391304, 0.926605504587156, 0.8859649122807017, 0.9316239316239316, 0.9210526315789473</t>
+        </is>
+      </c>
+      <c r="CQ82" t="n">
+        <v>0.9031343348450187</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>0.02105159539628221</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>0.9532331418074317</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>0.946078431372549</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>0.0134347103562673</v>
+      </c>
+      <c r="CW82" t="inlineStr">
+        <is>
+          <t>0.926829268292683, 0.9414634146341463, 0.9368932038834952, 0.9611650485436893, 0.9368932038834952, 0.9611650485436893, 0.9563106796116505</t>
+        </is>
+      </c>
+      <c r="CX82" t="inlineStr">
+        <is>
+          <t>0.9292035398230089, 0.8947368421052632, 0.9026548672566371, 0.8938053097345132, 0.8938053097345132, 0.9646017699115044, 0.9292035398230089</t>
+        </is>
+      </c>
+      <c r="CY82" t="n">
+        <v>0.9154301683412071</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>0.024853712033667</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>0.9458171239132642</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>0.9414634146341463</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>0.0126491018036183</v>
+      </c>
+      <c r="DE82" t="inlineStr">
+        <is>
+          <t>0.9888409238074681, 0.9847026101839965, 0.9852650571354928, 0.9887662170289544, 0.9831815448062547, 0.9940931351490677, 0.9866182661740699</t>
+        </is>
+      </c>
+      <c r="DF82" t="n">
+        <v>0.987352536326472</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>0.9866182661740699</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>0.00335868732353908</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AdaBoostClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'estimator': 'AdaBoostClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 2, 'sampling_strategy': 0.9}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.9381818181818181</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.8952380952380952</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.9562289562289562</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.9873417721518988</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.9230769230769232</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.9959354314249216</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.9462443438914028</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.9661479502961329</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.944954128440367</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.9694117647058824</v>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>0.07903194427490234, 0.07796835899353027, 0.07803130149841309, 0.07797074317932129, 0.08209776878356934, 0.07929754257202148, 0.07697010040283203</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>0.07876682281494141</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0.07803130149841309</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.001534723995130293</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>0.02200150489807129, 0.021999597549438477, 0.0219576358795166, 0.021028518676757812, 0.02244257926940918, 0.02097153663635254, 0.020999431610107422</t>
+        </is>
+      </c>
+      <c r="AD83" t="n">
+        <v>0.02162868635995047</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0.0219576358795166</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0.0005650798647369137</v>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.9056603773584906, 0.8301886792452831, 0.8490566037735849, 0.8867924528301887, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>0.8358974358974359, 0.7060439560439561, 0.8672161172161172, 0.8159340659340659, 0.8516483516483516, 0.8543956043956045, 0.8388278388278387</t>
+        </is>
+      </c>
+      <c r="AI83" t="n">
+        <v>0.8242804814233385</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0.8388278388278387</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.05056185405341862</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0.8413696715583506</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0.05035604418245616</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>0.7500000000000001, 0.5625000000000001, 0.8148148148148148, 0.7096774193548386, 0.75, 0.7857142857142857, 0.7272727272727273</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8108108108108107, 0.9367088607594937, 0.8799999999999999, 0.8918918918918919, 0.9230769230769231, 0.8767123287671232</t>
+        </is>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0.8877053796302151</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0.03744033416077118</v>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>0.8223684210526316, 0.6866554054054055, 0.8757618377871542, 0.7948387096774192, 0.8209459459459459, 0.8543956043956045, 0.8019925280199253</t>
+        </is>
+      </c>
+      <c r="AU83" t="n">
+        <v>0.8081369217548693</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0.8209459459459459</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0.05612735072316926</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0.7285684638795239</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0.07517596944662831</v>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>0.7058823529411765, 0.5, 0.8461538461538461, 0.6470588235294118, 0.6666666666666666, 0.7857142857142857, 0.631578947368421</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.8571428571428571, 0.925, 0.9166666666666666, 0.9428571428571428, 0.9230769230769231, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BC83" t="n">
+        <v>0.9178341398929634</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0.02655404985884725</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>0.6832935603391155</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>0.1037745299294938</v>
+      </c>
+      <c r="BI83" t="inlineStr">
+        <is>
+          <t>0.8, 0.6428571428571429, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ83" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7692307692307693, 0.9487179487179487, 0.8461538461538461, 0.8461538461538461, 0.9230769230769231, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK83" t="n">
+        <v>0.8608058608058607</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>0.05627213002101544</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>0.7877551020408163</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>0.06631868085417107</v>
+      </c>
+      <c r="BQ83" t="inlineStr">
+        <is>
+          <t>0.9572649572649572, 0.8608058608058609, 0.9798534798534799, 0.9413919413919414, 0.9432234432234433, 0.9084249084249085, 0.923992673992674</t>
+        </is>
+      </c>
+      <c r="BR83" t="n">
+        <v>0.9307081807081808</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>0.03549501761648896</v>
+      </c>
+      <c r="BU83" t="inlineStr">
+        <is>
+          <t>0.9465408805031447, 0.9655172413793104, 0.9373040752351097, 0.9435736677115988, 0.9529780564263323, 0.9561128526645768, 0.9310344827586207</t>
+        </is>
+      </c>
+      <c r="BV83" t="inlineStr">
+        <is>
+          <t>0.956043956043956, 0.9652589240824535, 0.9422825540472599, 0.9503016591251885, 0.9642031171442936, 0.958848667672197, 0.94175465057818</t>
+        </is>
+      </c>
+      <c r="BW83" t="n">
+        <v>0.9540990755276469</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>0.956043956043956</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>0.008939562477968913</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>0.9475801795255278</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>0.9465408805031447</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>0.0108243934448579</v>
+      </c>
+      <c r="CC83" t="inlineStr">
+        <is>
+          <t>0.9060773480662984, 0.9371428571428572, 0.8901098901098902, 0.9010989010989011, 0.9180327868852458, 0.9213483146067416, 0.881720430107527</t>
+        </is>
+      </c>
+      <c r="CD83" t="inlineStr">
+        <is>
+          <t>0.9626373626373627, 0.9762419006479482, 0.9561403508771931, 0.9605263157894737, 0.967032967032967, 0.9695652173913043, 0.9513274336283185</t>
+        </is>
+      </c>
+      <c r="CE83" t="n">
+        <v>0.9633530782863667</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0.9626373626373627</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0.007777223123047133</v>
+      </c>
+      <c r="CH83" t="inlineStr">
+        <is>
+          <t>0.9343573553518305, 0.9566923788954027, 0.9231251204935416, 0.9308126084441875, 0.9425328769591064, 0.945456765999023, 0.9165239318679228</t>
+        </is>
+      </c>
+      <c r="CI83" t="n">
+        <v>0.9356430054301449</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>0.9343573553518305</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0.01272836201895075</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0.9079329325739229</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>0.9060773480662984</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>0.01768818222838265</v>
+      </c>
+      <c r="CO83" t="inlineStr">
+        <is>
+          <t>0.845360824742268, 0.9111111111111111, 0.8350515463917526, 0.845360824742268, 0.8571428571428571, 0.8817204301075269, 0.8118811881188119</t>
+        </is>
+      </c>
+      <c r="CP83" t="inlineStr">
+        <is>
+          <t>0.9909502262443439, 0.9868995633187773, 0.9819819819819819, 0.9864864864864865, 0.995475113122172, 0.9867256637168141, 0.9862385321100917</t>
+        </is>
+      </c>
+      <c r="CQ83" t="n">
+        <v>0.9878225095686667</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>0.9867256637168141</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>0.003942543742117327</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>0.8553755403366565</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>0.03002152308138378</v>
+      </c>
+      <c r="CW83" t="inlineStr">
+        <is>
+          <t>0.9761904761904762, 0.9647058823529412, 0.9529411764705882, 0.9647058823529412, 0.9882352941176471, 0.9647058823529412, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="CX83" t="inlineStr">
+        <is>
+          <t>0.9358974358974359, 0.9658119658119658, 0.9316239316239316, 0.9358974358974359, 0.9401709401709402, 0.9529914529914529, 0.9188034188034188</t>
+        </is>
+      </c>
+      <c r="CY83" t="n">
+        <v>0.9401709401709403</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>0.9358974358974359</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>0.01408127300936605</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>0.9680272108843538</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>0.9647058823529412</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>0.01032831652448378</v>
+      </c>
+      <c r="DE83" t="inlineStr">
+        <is>
+          <t>0.9935897435897435, 0.9957264957264957, 0.9914027149321267, 0.9935646053293112, 0.9939165409753645, 0.9928607340372047, 0.9932126696832579</t>
+        </is>
+      </c>
+      <c r="DF83" t="n">
+        <v>0.9934676434676435</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>0.9935646053293112</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>0.001196752336621663</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 9, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.9347993827160493</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.8068924539512775</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.7450980392156864</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>0.13696956634521484, 0.1351180076599121, 0.13399982452392578, 0.1340010166168213, 0.13599801063537598, 0.13596534729003906, 0.13470745086669922</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>0.1352513177054269</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0.1351180076599121</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.001032529326424432</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>0.023028850555419922, 0.021999835968017578, 0.023000001907348633, 0.02299976348876953, 0.0240328311920166, 0.04999899864196777, 0.02303624153137207</t>
+        </is>
+      </c>
+      <c r="AD84" t="n">
+        <v>0.02687093189784459</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0.02302885055541992</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0.009457622364948981</v>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>0.9629629629629629, 0.8679245283018868, 0.8867924528301887, 0.8490566037735849, 0.9433962264150944, 0.8490566037735849, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>0.9473684210526316, 0.873015873015873, 0.8769349845201238, 0.8475232198142415, 0.9326625386996904, 0.8707430340557275, 0.891640866873065</t>
+        </is>
+      </c>
+      <c r="AI84" t="n">
+        <v>0.8914127054330504</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0.03323984919429478</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0.8949785364879704</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0.04157065551294201</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.8955223880597014, 0.9117647058823528, 0.8787878787878787, 0.9565217391304348, 0.8709677419354839, 0.9275362318840579</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8205128205128205, 0.8421052631578947, 0.8, 0.918918918918919, 0.8181818181818181, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0.8584325900115374</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0.05047912153530736</v>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>0.9583333333333333, 0.858017604286261, 0.8769349845201238, 0.8393939393939394, 0.937720329024677, 0.8445747800586509, 0.8962005483744614</t>
+        </is>
+      </c>
+      <c r="AU84" t="n">
+        <v>0.8873107884273496</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0.04268236550630779</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0.9161889868431616</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0.03542739211842745</v>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.9375, 0.9117647058823529, 0.90625, 0.9428571428571428, 0.9642857142857143, 0.9142857142857143</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>1.0, 0.7619047619047619, 0.8421052631578947, 0.7619047619047619, 0.9444444444444444, 0.72, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="BC84" t="n">
+        <v>0.8456068743286789</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0.09657038196732359</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0.9318413176081244</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>0.01989663859611546</v>
+      </c>
+      <c r="BI84" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9117647058823529, 0.8529411764705882, 0.9705882352941176, 0.7941176470588235, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ84" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.8421052631578947, 0.8421052631578947, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK84" t="n">
+        <v>0.8788638262322472</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>0.03654911086754781</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>0.9039615846338535</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>0.06757967800738331</v>
+      </c>
+      <c r="BQ84" t="inlineStr">
+        <is>
+          <t>0.9969924812030075, 0.9492063492063493, 0.9798761609907121, 0.9040247678018577, 0.9481424148606812, 0.9148606811145511, 0.9481424148606811</t>
+        </is>
+      </c>
+      <c r="BR84" t="n">
+        <v>0.9487493242911199</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>0.9481424148606812</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>0.03034551930008955</v>
+      </c>
+      <c r="BU84" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV84" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW84" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC84" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD84" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE84" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH84" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI84" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO84" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP84" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW84" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX84" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY84" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE84" t="inlineStr">
+        <is>
+          <t>0.999935247140082, 1.0, 0.9999785204914512, 0.9999785204914511, 0.9999785204914511, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF84" t="n">
+        <v>0.9999784755865553</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.99832336814524e-05</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'estimator': 'RandomForestClassifier', 'estimator_params': {}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 5, 'sampling_strategy': 0.7}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.9007936507936508</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.9622641509433962</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>0.13149046897888184, 0.13099980354309082, 0.13100266456604004, 0.14188814163208008, 0.13148117065429688, 0.130967378616333, 0.14041733741760254</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>0.1340352807726179</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.1314811706542969</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.00452328140951783</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>0.020968914031982422, 0.020999908447265625, 0.02102971076965332, 0.020251750946044922, 0.020992040634155273, 0.02100229263305664, 0.02106451988220215</t>
+        </is>
+      </c>
+      <c r="AD85" t="n">
+        <v>0.02090130533490862</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0.02099990844726562</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0.0002666653030125489</v>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7735849056603774, 0.9056603773584906, 0.7924528301886793, 0.9622641509433962, 0.9056603773584906, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>0.7948717948717949, 0.7087912087912087, 0.8672161172161172, 0.7673992673992673, 0.9285714285714286, 0.8901098901098901, 0.9386446886446886</t>
+        </is>
+      </c>
+      <c r="AI85" t="n">
+        <v>0.8422291993720564</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>0.8672161172161172</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>0.08045919421313064</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>0.8764101028251972</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>0.06739453977866409</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>0.7142857142857142, 0.5714285714285714, 0.8148148148148148, 0.6451612903225806, 0.923076923076923, 0.8275862068965518, 0.896551724137931</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>0.9, 0.8461538461538461, 0.9367088607594937, 0.8533333333333333, 0.975, 0.935064935064935, 0.9610389610389611</t>
+        </is>
+      </c>
+      <c r="AQ85" t="n">
+        <v>0.9153285623357955</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>0.935064935064935</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>0.04684362617552858</v>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>0.8071428571428572, 0.7087912087912087, 0.8757618377871542, 0.749247311827957, 0.9490384615384615, 0.8813255709807435, 0.9287953425884461</t>
+        </is>
+      </c>
+      <c r="AU85" t="n">
+        <v>0.842871798665261</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0.8757618377871542</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0.0838658532279085</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0.7704150349947267</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>0.1212380265933483</v>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>0.7692307692307693, 0.5714285714285714, 0.8461538461538461, 0.5882352941176471, 1.0, 0.8, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>0.8780487804878049, 0.8461538461538461, 0.925, 0.8888888888888888, 0.9512195121951219, 0.9473684210526315, 0.9736842105263158</t>
+        </is>
+      </c>
+      <c r="BC85" t="n">
+        <v>0.9157662370435158</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0.04257140240994366</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>0.7773878782282144</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>0.141941335860396</v>
+      </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>0.6666666666666666, 0.5714285714285714, 0.7857142857142857, 0.7142857142857143, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ85" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.8461538461538461, 0.9487179487179487, 0.8205128205128205, 1.0, 0.9230769230769231, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BK85" t="n">
+        <v>0.9157509157509158</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>0.0576850393700499</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>0.7687074829931974</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>0.1157462552868949</v>
+      </c>
+      <c r="BQ85" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8608058608058609, 0.9734432234432234, 0.9075091575091575, 0.9945054945054945, 0.945054945054945, 0.988095238095238</t>
+        </is>
+      </c>
+      <c r="BR85" t="n">
+        <v>0.9454474097331239</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>0.04411616446742538</v>
+      </c>
+      <c r="BU85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE85" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_splashing_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 2, 'sampling_strategy': 0.8}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.9398148148148148</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.9948186528497409</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.9974025974025974</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.996308954203691</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.9952380952380953</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.9952153110047847</v>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>0.0810081958770752, 0.03600311279296875, 0.03700113296508789, 0.03900027275085449, 0.03651785850524902, 0.03800034523010254, 0.037000417709350586</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>0.04350447654724121</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0.03700113296508789</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.01533805643265672</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>0.01699066162109375, 0.017995119094848633, 0.01800060272216797, 0.01699972152709961, 0.016997098922729492, 0.01799774169921875, 0.01799941062927246</t>
+        </is>
+      </c>
+      <c r="AD86" t="n">
+        <v>0.01756862231663295</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0.01799511909484863</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0.0004960636841476409</v>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8113207547169812, 0.9245283018867925, 0.7924528301886793, 0.9245283018867925, 0.8867924528301887, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.7896825396825397, 0.9179566563467492, 0.791795665634675, 0.9179566563467492, 0.9001547987616099, 0.891640866873065</t>
+        </is>
+      </c>
+      <c r="AI86" t="n">
+        <v>0.8757485450320479</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>0.9001547987616099</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>0.05466676181308377</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>0.8842467804731956</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0.0548742950532408</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.8571428571428571, 0.9411764705882353, 0.8307692307692308, 0.9411764705882353, 0.90625, 0.9275362318840579</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.7222222222222222, 0.8947368421052632, 0.7317073170731707, 0.8947368421052632, 0.8571428571428571, 0.8648648648648649</t>
+        </is>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.8399566656856221</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>0.8648648648648649</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0.07369982277430034</v>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>0.9365949119373776, 0.7896825396825397, 0.9179566563467492, 0.7812382739212007, 0.9179566563467492, 0.8816964285714286, 0.8962005483744614</t>
+        </is>
+      </c>
+      <c r="AU86" t="n">
+        <v>0.8744751450257866</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>0.8962005483744614</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0.05861154108149978</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0.908993624365951</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0.04427421258567169</v>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.8571428571428571, 0.9411764705882353, 0.8709677419354839, 0.9411764705882353, 0.9666666666666667, 0.9142857142857143</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>1.0, 0.7222222222222222, 0.8947368421052632, 0.6818181818181818, 0.8947368421052632, 0.782608695652174, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="BC86" t="n">
+        <v>0.8378588103988562</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0.1042915752864254</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>0.9160669361123058</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>0.03655782988957913</v>
+      </c>
+      <c r="BI86" t="inlineStr">
+        <is>
+          <t>1.0, 0.8571428571428571, 0.9411764705882353, 0.7941176470588235, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ86" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7222222222222222, 0.8947368421052632, 0.7894736842105263, 0.8947368421052632, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK86" t="n">
+        <v>0.8475355054302423</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>0.06923677027158424</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>0.9039615846338535</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>0.0657256053070457</v>
+      </c>
+      <c r="BQ86" t="inlineStr">
+        <is>
+          <t>0.9864661654135338, 0.9412698412698413, 0.9767801857585139, 0.9334365325077398, 0.9504643962848297, 0.9318885448916409, 0.934984520123839</t>
+        </is>
+      </c>
+      <c r="BR86" t="n">
+        <v>0.9507557408928484</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>0.9412698412698413</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>0.02051908794941798</v>
+      </c>
+      <c r="BU86" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV86" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.995575221238938, 0.995575221238938, 0.995575221238938, 1.0, 0.995575221238938</t>
+        </is>
+      </c>
+      <c r="BW86" t="n">
+        <v>0.9968394437420985</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>0.995575221238938</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>0.001998911289613391</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC86" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975786924939467, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975786924939467</t>
+        </is>
+      </c>
+      <c r="CD86" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955555555555555, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955555555555555</t>
+        </is>
+      </c>
+      <c r="CE86" t="n">
+        <v>0.9968253968253968</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0.9955555555555555</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0.00200779533978946</v>
+      </c>
+      <c r="CH86" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965671240247511, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965671240247511</t>
+        </is>
+      </c>
+      <c r="CI86" t="n">
+        <v>0.9975471041235167</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>0.9965671240247511</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0.001551348844990803</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>0.9982688114216364</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>0.001094907038779773</v>
+      </c>
+      <c r="CO86" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 0.9951690821256038, 0.9951690821256038, 0.9951690821256038, 1.0, 0.9951690821256038</t>
+        </is>
+      </c>
+      <c r="CP86" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>0.9965459942243395</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>0.9951690821256038</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>0.002184519446236978</v>
+      </c>
+      <c r="CW86" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX86" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 0.9911504424778761, 0.9911504424778761, 0.9911504424778761, 1.0, 0.9911504424778761</t>
+        </is>
+      </c>
+      <c r="CY86" t="n">
+        <v>0.9936788874841972</v>
+      </c>
+      <c r="CZ86" t="n">
+        <v>0.9911504424778761</v>
+      </c>
+      <c r="DA86" t="n">
+        <v>0.003997822579226782</v>
+      </c>
+      <c r="DB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE86" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914511, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914511</t>
+        </is>
+      </c>
+      <c r="DF86" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>9.712984233463661e-06</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>LGBMClassifier_no_fragmentation_smotenc_opt-smotenc_default-model</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LGBMClassifier', 'estimator_params': {'verbose': -1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination'), 'k_neighbors': 4, 'sampling_strategy': 1.0}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.9338624338624338</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.9477272727272728</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.9811320754716981</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>0.055190086364746094, 0.049462318420410156, 0.03999972343444824, 0.03999948501586914, 0.0410003662109375, 0.0385279655456543, 0.04252314567565918</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>0.04381472723824637</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0.0410003662109375</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.005706425811251333</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>0.015636682510375977, 0.016001224517822266, 0.014999866485595703, 0.0149993896484375, 0.015999555587768555, 0.014998912811279297, 0.014998197555541992</t>
+        </is>
+      </c>
+      <c r="AD87" t="n">
+        <v>0.01537626130240304</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0.0149998664855957</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0.0004497496723551032</v>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8490566037735849, 0.8867924528301887, 0.8867924528301887, 0.9245283018867925, 0.9245283018867925, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>0.8538461538461538, 0.8287545787545787, 0.8543956043956045, 0.8772893772893773, 0.8571428571428572, 0.9029304029304028, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI87" t="n">
+        <v>0.87145473574045</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0.0307292463676221</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0.9005191175002496</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0.02619161345480605</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>0.8148148148148148, 0.7333333333333334, 0.7857142857142857, 0.7999999999999999, 0.8333333333333333, 0.8571428571428571, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>0.9382716049382716, 0.8947368421052632, 0.9230769230769231, 0.9210526315789475, 0.951219512195122, 0.9487179487179487, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0.9320634119521582</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0.9382716049382716</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0.01894496472261122</v>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>0.8765432098765431, 0.8140350877192983, 0.8543956043956045, 0.8605263157894737, 0.8922764227642277, 0.9029304029304028, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU87" t="n">
+        <v>0.8725320839050283</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0.8765432098765431</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0.03027068765132834</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0.8130007558578985</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0.0422673952743761</v>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>0.9166666666666666, 0.6875, 0.7857142857142857, 0.75, 1.0, 0.8571428571428571, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>0.9047619047619048, 0.918918918918919, 0.9230769230769231, 0.9459459459459459, 0.9069767441860465, 0.9487179487179487, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC87" t="n">
+        <v>0.9316244797972374</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0.02320895692770196</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0.8299319727891156</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>0.09719019490586091</v>
+      </c>
+      <c r="BI87" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7857142857142857, 0.7857142857142857, 0.8571428571428571, 0.7142857142857143, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ87" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.8717948717948718, 0.9230769230769231, 0.8974358974358975, 1.0, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK87" t="n">
+        <v>0.9340659340659341</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>0.04078948251157524</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>0.8088435374149661</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>0.07042048595704781</v>
+      </c>
+      <c r="BQ87" t="inlineStr">
+        <is>
+          <t>0.9794871794871794, 0.9249084249084248, 0.9816849816849816, 0.9468864468864469, 0.9908424908424909, 0.9047619047619047, 0.9798534798534798</t>
+        </is>
+      </c>
+      <c r="BR87" t="n">
+        <v>0.9583464154892726</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>0.9794871794871794</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>0.0307777730322408</v>
+      </c>
+      <c r="BU87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE87" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 0.9999999999999999, 1.0</t>
+        </is>
+      </c>
+      <c r="DF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>4.196248604251576e-17</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH87"/>
+  <dimension ref="A1:DH92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34528,6 +34528,1956 @@
       </c>
       <c r="DH87" t="n">
         <v>4.196248604251576e-17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_opt-model</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.552828000398145, 'class_weight': 'balanced', 'penalty': 'l2'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.552828000398145, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.8478260869565217</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.8297872340425533</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.886574074074074</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.7720364741641338</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.7766203703703703</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.835016835016835</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.9440993788819876</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.8611898016997168</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.9174355158730159</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.828935149812514</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0.8529761904761904</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0.7966804979253113</v>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>0.010000228881835938, 0.009027719497680664, 0.007972478866577148, 0.008032798767089844, 0.00700831413269043, 0.0070002079010009766, 0.0069963932037353516</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>0.008005448750087194</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.007972478866577148</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.001072313919758811</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>0.020000934600830078, 0.016000032424926758, 0.015268802642822266, 0.016999006271362305, 0.015991687774658203, 0.015967845916748047, 0.014999628067016602</t>
+        </is>
+      </c>
+      <c r="AD88" t="n">
+        <v>0.01646113395690918</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0.0159916877746582</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0.00156083659277844</v>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8113207547169812, 0.8490566037735849, 0.8113207547169812, 0.8113207547169812, 0.7547169811320755, 0.7547169811320755</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.8166666666666667, 0.8707430340557275, 0.8413312693498451, 0.818111455108359, 0.7856037151702786, 0.7507739938080495</t>
+        </is>
+      </c>
+      <c r="AI88" t="n">
+        <v>0.8288610180914471</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0.818111455108359</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0.05103377431461123</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0.816911250873515</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>0.05444202474588818</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848486, 0.8709677419354839, 0.8333333333333333, 0.84375, 0.7796610169491526, 0.7999999999999999</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7499999999999999, 0.8181818181818181, 0.782608695652174, 0.761904761904762, 0.7234042553191489, 0.6829268292682926</t>
+        </is>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0.7733947432044941</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>0.06344571355692517</v>
+      </c>
+      <c r="AT88" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7992424242424243, 0.8445747800586509, 0.8079710144927537, 0.8028273809523809, 0.7515326361341508, 0.7414634146341463</t>
+        </is>
+      </c>
+      <c r="AU88" t="n">
+        <v>0.8094869489993871</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>0.8028273809523809</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0.05518455178911399</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0.8455791547942801</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0.04883206875705084</v>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.9032258064516129, 0.9642857142857143, 0.9615384615384616, 0.9, 0.92, 0.8387096774193549</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6818181818181818, 0.72, 0.6666666666666666, 0.6956521739130435, 0.6071428571428571, 0.6363636363636364</t>
+        </is>
+      </c>
+      <c r="BC88" t="n">
+        <v>0.7003400511442355</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0.08656480413235169</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>0.9186595432217552</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>0.04050754709259869</v>
+      </c>
+      <c r="BI88" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.7941176470588235, 0.7352941176470589, 0.7941176470588235, 0.6764705882352942, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="BJ88" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.8947368421052632, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK88" t="n">
+        <v>0.8709273182957392</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>0.06870551459585363</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>0.7867947178871548</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>0.07554445485019097</v>
+      </c>
+      <c r="BQ88" t="inlineStr">
+        <is>
+          <t>0.9578947368421052, 0.8682539682539683, 0.9504643962848298, 0.8715170278637772, 0.936532507739938, 0.8297213622291021, 0.8668730650154799</t>
+        </is>
+      </c>
+      <c r="BR88" t="n">
+        <v>0.8973224377470286</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>0.8715170278637772</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>0.04635032065320189</v>
+      </c>
+      <c r="BU88" t="inlineStr">
+        <is>
+          <t>0.8081761006289309, 0.8181818181818182, 0.8244514106583072, 0.8244514106583072, 0.8275862068965517, 0.8275862068965517, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="BV88" t="inlineStr">
+        <is>
+          <t>0.8234189510036694, 0.8332263585793753, 0.8401065383624022, 0.8321161611822321, 0.8405361285333792, 0.8445313171234642, 0.8486768622733911</t>
+        </is>
+      </c>
+      <c r="BW88" t="n">
+        <v>0.8375160452939875</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>0.8401065383624022</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>0.007891203597854857</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>0.8248133345726059</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>0.8244514106583072</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>0.009832167231209065</v>
+      </c>
+      <c r="CC88" t="inlineStr">
+        <is>
+          <t>0.8381962864721485, 0.8465608465608465, 0.8526315789473684, 0.8556701030927835, 0.8563968668407311, 0.8548812664907651, 0.8724489795918366</t>
+        </is>
+      </c>
+      <c r="CD88" t="inlineStr">
+        <is>
+          <t>0.7644787644787645, 0.7769230769230769, 0.7829457364341085, 0.776, 0.7843137254901961, 0.7876447876447877, 0.7967479674796748</t>
+        </is>
+      </c>
+      <c r="CE88" t="n">
+        <v>0.7812934369215155</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0.7829457364341085</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0.009417977776689589</v>
+      </c>
+      <c r="CH88" t="inlineStr">
+        <is>
+          <t>0.8013375254754564, 0.8117419617419617, 0.8177886576907385, 0.8158350515463917, 0.8203552961654637, 0.8212630270677764, 0.8345984735357557</t>
+        </is>
+      </c>
+      <c r="CI88" t="n">
+        <v>0.817559999031935</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>0.8177886576907385</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0.009349420539145593</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0.8538265611423543</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>0.8548812664907651</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>0.009683830910175054</v>
+      </c>
+      <c r="CO88" t="inlineStr">
+        <is>
+          <t>0.9186046511627907, 0.9248554913294798, 0.9310344827586207, 0.9120879120879121, 0.9265536723163842, 0.9364161849710982, 0.9193548387096774</t>
+        </is>
+      </c>
+      <c r="CP88" t="inlineStr">
+        <is>
+          <t>0.678082191780822, 0.6917808219178082, 0.696551724137931, 0.708029197080292, 0.704225352112676, 0.6986301369863014, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="CQ88" t="n">
+        <v>0.7020202184684268</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>0.6986301369863014</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>0.01678777482237482</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>0.9241296047622803</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>0.9248554913294798</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>0.007591031115589147</v>
+      </c>
+      <c r="CW88" t="inlineStr">
+        <is>
+          <t>0.7707317073170732, 0.7804878048780488, 0.7864077669902912, 0.8058252427184466, 0.7961165048543689, 0.7864077669902912, 0.8300970873786407</t>
+        </is>
+      </c>
+      <c r="CX88" t="inlineStr">
+        <is>
+          <t>0.8761061946902655, 0.8859649122807017, 0.8938053097345132, 0.8584070796460177, 0.8849557522123894, 0.9026548672566371, 0.8672566371681416</t>
+        </is>
+      </c>
+      <c r="CY88" t="n">
+        <v>0.8813072504269523</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>0.01412098815595993</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>0.793724840161023</v>
+      </c>
+      <c r="DC88" t="n">
+        <v>0.7864077669902912</v>
+      </c>
+      <c r="DD88" t="n">
+        <v>0.01807153464251965</v>
+      </c>
+      <c r="DE88" t="inlineStr">
+        <is>
+          <t>0.9004748543060652, 0.9134788189987163, 0.9035784861242375, 0.9139745682618782, 0.9036214451413351, 0.9203110232837873, 0.9124280436463613</t>
+        </is>
+      </c>
+      <c r="DF88" t="n">
+        <v>0.9096953199660545</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>0.9124280436463613</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>0.00667738577131045</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_opt-model</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 3.6236985622991797, 'class_weight': None, 'penalty': 'l2'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 3.6236985622991797, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.9436363636363636</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.7985953315430696</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.8340909090909091</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.8737864077669902</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.8653198653198653</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.693069306930693</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.8860759493670886</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0.937231448147718</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0.8405797101449275</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0.8719370572523516</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0.9540816326530612</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0.8577981651376146</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0.9033816425120772</v>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>0.00800013542175293, 0.0069997310638427734, 0.0069997310638427734, 0.006999969482421875, 0.007001161575317383, 0.007002353668212891, 0.008000850677490234</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>0.007286276136125837</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.007001161575317383</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.0004517113161977159</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>0.014000415802001953, 0.014000177383422852, 0.01300048828125, 0.01399993896484375, 0.012998580932617188, 0.013000011444091797, 0.012981653213500977</t>
+        </is>
+      </c>
+      <c r="AD89" t="n">
+        <v>0.01342589514596122</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0.01300048828125</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0.0004973783610121497</v>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7169811320754716, 0.8867924528301887, 0.8490566037735849, 0.8867924528301887, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>0.882051282051282, 0.7161172161172161, 0.9001831501831502, 0.8745421245421245, 0.9001831501831502, 0.8543956043956045, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="AI89" t="n">
+        <v>0.8643642072213501</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0.882051282051282</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0.06381462257831934</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0.8574423480083857</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0.05883909467264655</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>0.8125, 0.5714285714285714, 0.8125000000000001, 0.7647058823529412, 0.8125000000000001, 0.7857142857142857, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>0.9210526315789475, 0.7887323943661971, 0.9189189189189189, 0.8888888888888888, 0.9189189189189189, 0.9230769230769231, 0.9166666666666666</t>
+        </is>
+      </c>
+      <c r="AQ89" t="n">
+        <v>0.8966079060593516</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>0.9189189189189189</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0.04534436361805354</v>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>0.8667763157894737, 0.6800804828973843, 0.8657094594594594, 0.826797385620915, 0.8657094594594594, 0.8543956043956045, 0.8700980392156863</t>
+        </is>
+      </c>
+      <c r="AU89" t="n">
+        <v>0.8327952495482832</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>0.8657094594594594</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0.06384943344918412</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0.7689825930372149</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0.08279275400268954</v>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>0.7647058823529411, 0.47619047619047616, 0.7222222222222222, 0.65, 0.7222222222222222, 0.7857142857142857, 0.7</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>0.9459459459459459, 0.875, 0.9714285714285714, 0.9696969696969697, 0.9714285714285714, 0.9230769230769231, 1.0</t>
+        </is>
+      </c>
+      <c r="BC89" t="n">
+        <v>0.9509395687967117</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0.03810970229068961</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>0.6887221555288783</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>0.09578384804489491</v>
+      </c>
+      <c r="BI89" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ89" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.717948717948718, 0.8717948717948718, 0.8205128205128205, 0.8717948717948718, 0.9230769230769231, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK89" t="n">
+        <v>0.8498168498168497</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>0.061947012913142</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>0.8789115646258504</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>0.09102437378872236</v>
+      </c>
+      <c r="BQ89" t="inlineStr">
+        <is>
+          <t>0.9384615384615385, 0.9010989010989012, 0.9688644688644688, 0.924908424908425, 0.8772893772893773, 0.9413919413919414, 0.9945054945054945</t>
+        </is>
+      </c>
+      <c r="BR89" t="n">
+        <v>0.9352171637885923</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>0.9384615384615385</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>0.0364923779487796</v>
+      </c>
+      <c r="BU89" t="inlineStr">
+        <is>
+          <t>0.8584905660377359, 0.8808777429467085, 0.8495297805642633, 0.8557993730407524, 0.8589341692789969, 0.8652037617554859, 0.8526645768025078</t>
+        </is>
+      </c>
+      <c r="BV89" t="inlineStr">
+        <is>
+          <t>0.8656898656898657, 0.8888386123680241, 0.8562342885872298, 0.8605077928607341, 0.8588989441930618, 0.8744092508798391, 0.8546254399195575</t>
+        </is>
+      </c>
+      <c r="BW89" t="n">
+        <v>0.8656005992140445</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>0.8605077928607341</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>0.01131772516824489</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>0.860214281489493</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0.8584905660377359</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>0.009614954516208677</v>
+      </c>
+      <c r="CC89" t="inlineStr">
+        <is>
+          <t>0.766839378238342, 0.8020833333333333, 0.7551020408163265, 0.7628865979381444, 0.7643979057591622, 0.7794871794871796, 0.7564766839378239</t>
+        </is>
+      </c>
+      <c r="CD89" t="inlineStr">
+        <is>
+          <t>0.8984198645598194, 0.914798206278027, 0.8914027149321265, 0.8963963963963965, 0.8993288590604026, 0.9029345372460497, 0.89438202247191</t>
+        </is>
+      </c>
+      <c r="CE89" t="n">
+        <v>0.8996660858492473</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0.8984198645598194</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0.007053126220958513</v>
+      </c>
+      <c r="CH89" t="inlineStr">
+        <is>
+          <t>0.8326296213990807, 0.8584407698056802, 0.8232523778742264, 0.8296414971672704, 0.8318633824097824, 0.8412108583666147, 0.8254293532048669</t>
+        </is>
+      </c>
+      <c r="CI89" t="n">
+        <v>0.8346382657467888</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>0.8318633824097824</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>0.01108991183758527</v>
+      </c>
+      <c r="CL89" t="n">
+        <v>0.7696104456443302</v>
+      </c>
+      <c r="CM89" t="n">
+        <v>0.7643979057591622</v>
+      </c>
+      <c r="CN89" t="n">
+        <v>0.01518969259578258</v>
+      </c>
+      <c r="CO89" t="inlineStr">
+        <is>
+          <t>0.6788990825688074, 0.719626168224299, 0.6666666666666666, 0.6788990825688074, 0.6886792452830188, 0.6909090909090909, 0.6759259259259259</t>
+        </is>
+      </c>
+      <c r="CP89" t="inlineStr">
+        <is>
+          <t>0.9521531100478469, 0.9622641509433962, 0.9471153846153846, 0.9476190476190476, 0.9436619718309859, 0.9569377990430622, 0.943127962085308</t>
+        </is>
+      </c>
+      <c r="CQ89" t="n">
+        <v>0.9504113465978615</v>
+      </c>
+      <c r="CR89" t="n">
+        <v>0.9476190476190476</v>
+      </c>
+      <c r="CS89" t="n">
+        <v>0.006583305085779567</v>
+      </c>
+      <c r="CT89" t="n">
+        <v>0.6856578945923736</v>
+      </c>
+      <c r="CU89" t="n">
+        <v>0.6788990825688074</v>
+      </c>
+      <c r="CV89" t="n">
+        <v>0.01575385788795243</v>
+      </c>
+      <c r="CW89" t="inlineStr">
+        <is>
+          <t>0.8809523809523809, 0.9058823529411765, 0.8705882352941177, 0.8705882352941177, 0.8588235294117647, 0.8941176470588236, 0.8588235294117647</t>
+        </is>
+      </c>
+      <c r="CX89" t="inlineStr">
+        <is>
+          <t>0.8504273504273504, 0.8717948717948718, 0.8418803418803419, 0.8504273504273504, 0.8589743589743589, 0.8547008547008547, 0.8504273504273504</t>
+        </is>
+      </c>
+      <c r="CY89" t="n">
+        <v>0.8540903540903539</v>
+      </c>
+      <c r="CZ89" t="n">
+        <v>0.8504273504273504</v>
+      </c>
+      <c r="DA89" t="n">
+        <v>0.008676843958212391</v>
+      </c>
+      <c r="DB89" t="n">
+        <v>0.877110844337735</v>
+      </c>
+      <c r="DC89" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="DD89" t="n">
+        <v>0.01641310052344333</v>
+      </c>
+      <c r="DE89" t="inlineStr">
+        <is>
+          <t>0.9384411884411885, 0.9471593765711412, 0.9345399698340874, 0.9425339366515838, 0.9405731523378582, 0.9429361488185017, 0.929462041226747</t>
+        </is>
+      </c>
+      <c r="DF89" t="n">
+        <v>0.939377973411587</v>
+      </c>
+      <c r="DG89" t="n">
+        <v>0.9405731523378582</v>
+      </c>
+      <c r="DH89" t="n">
+        <v>0.005440705833764539</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_opt-model</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'distance', 'p': 2}, 'base_estimator_params': {'n_neighbors': 3, 'weights': 'distance', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.8811728395061729</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8366013071895425</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.8287037037037037</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.9973890339425587</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0.996324848724834</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0.9973958333333333</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0.9905660377358491</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0.9952606635071091</v>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>0.010028839111328125, 0.006996870040893555, 0.006000995635986328, 0.006015300750732422, 0.006010293960571289, 0.0059702396392822266, 0.006994485855102539</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>0.00685957499912807</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0.006015300750732422</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.001365045215079156</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>0.01797008514404297, 0.015841007232666016, 0.015000104904174805, 0.015995264053344727, 0.015989065170288086, 0.016028881072998047, 0.014969587326049805</t>
+        </is>
+      </c>
+      <c r="AD90" t="n">
+        <v>0.01597057070050921</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>0.01598906517028809</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0.0009229586112470226</v>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8301886792452831, 0.9056603773584906, 0.9056603773584906, 0.8867924528301887, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.830952380952381, 0.914860681114551, 0.903250773993808, 0.8769349845201238, 0.8769349845201238, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI90" t="n">
+        <v>0.885845917314294</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>0.02837456805923068</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0.8923330338424679</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0.03167885777043797</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>0.958904109589041, 0.8656716417910447, 0.923076923076923, 0.9253731343283583, 0.9117647058823528, 0.9117647058823528, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>0.9142857142857143, 0.7692307692307692, 0.8780487804878049, 0.8717948717948718, 0.8421052631578947, 0.8421052631578947, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ90" t="n">
+        <v>0.8513822750389777</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>0.04156179228075492</v>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>0.9365949119373776, 0.8174512055109069, 0.900562851782364, 0.898584003061615, 0.8769349845201238, 0.8769349845201238, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU90" t="n">
+        <v>0.8834282751218049</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>0.8769349845201238</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0.03344386183262089</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>0.9154742752046323</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0.9117647058823528</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>0.02553295682580002</v>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.90625, 0.967741935483871, 0.9393939393939394, 0.9117647058823529, 0.9117647058823529, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>1.0, 0.7142857142857143, 0.8181818181818182, 0.85, 0.8421052631578947, 0.8421052631578947, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC90" t="n">
+        <v>0.8441119031344595</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0.07734436617924688</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>0.9242475177291167</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>0.02043371926778044</v>
+      </c>
+      <c r="BI90" t="inlineStr">
+        <is>
+          <t>1.0, 0.8285714285714286, 0.8823529411764706, 0.9117647058823529, 0.9117647058823529, 0.9117647058823529, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ90" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8333333333333334, 0.9473684210526315, 0.8947368421052632, 0.8421052631578947, 0.8421052631578947, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK90" t="n">
+        <v>0.8634085213032581</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>0.03918921245892704</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>0.9082833133253302</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0.04703615594400541</v>
+      </c>
+      <c r="BQ90" t="inlineStr">
+        <is>
+          <t>0.9443609022556392, 0.8563492063492063, 0.9473684210526316, 0.956656346749226, 0.8831269349845201, 0.9411764705882353, 0.945046439628483</t>
+        </is>
+      </c>
+      <c r="BR90" t="n">
+        <v>0.9248692459439918</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0.9443609022556392</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>0.0358708365325814</v>
+      </c>
+      <c r="BU90" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV90" t="inlineStr">
+        <is>
+          <t>0.9975609756097561, 1.0, 0.9975728155339806, 0.9975728155339806, 0.9975728155339806, 1.0, 0.9975728155339806</t>
+        </is>
+      </c>
+      <c r="BW90" t="n">
+        <v>0.9982646053922398</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>0.9975728155339806</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>0.001097567218380571</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC90" t="inlineStr">
+        <is>
+          <t>0.9975550122249389, 1.0, 0.9975669099756691, 0.9975669099756691, 0.9975669099756691, 1.0, 0.9975669099756691</t>
+        </is>
+      </c>
+      <c r="CD90" t="inlineStr">
+        <is>
+          <t>0.9955947136563876, 1.0, 0.9955947136563876, 0.9955947136563876, 0.9955947136563876, 1.0, 0.9955947136563876</t>
+        </is>
+      </c>
+      <c r="CE90" t="n">
+        <v>0.9968533668974198</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0.9955947136563876</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0.001990105513007176</v>
+      </c>
+      <c r="CH90" t="inlineStr">
+        <is>
+          <t>0.9965748629406632, 1.0, 0.9965808118160284, 0.9965808118160284, 0.9965808118160284, 1.0, 0.9965808118160284</t>
+        </is>
+      </c>
+      <c r="CI90" t="n">
+        <v>0.9975568728863966</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>0.9965808118160284</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>0.001545170567206118</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0.9982603788753737</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>0.9975669099756691</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>0.001100240355913701</v>
+      </c>
+      <c r="CO90" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP90" t="inlineStr">
+        <is>
+          <t>0.9912280701754386, 1.0, 0.9912280701754386, 0.9912280701754386, 0.9912280701754386, 1.0, 0.9912280701754386</t>
+        </is>
+      </c>
+      <c r="CQ90" t="n">
+        <v>0.9937343358395989</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>0.003962753960110763</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW90" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9951456310679612, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX90" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>0.9965292107844796</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>0.002195134436761142</v>
+      </c>
+      <c r="DE90" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF90" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>9.712984233443666e-06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_opt-model</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 5, 'weights': 'distance', 'p': 1}, 'base_estimator_params': {'n_neighbors': 5, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.9727272727272727</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.8903508771929824</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.865909090909091</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.9152542372881356</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.9818181818181818</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>0.008001327514648438, 0.00699925422668457, 0.004000425338745117, 0.00500178337097168, 0.005002498626708984, 0.006001710891723633, 0.004999876022338867</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.005715267998831612</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.005002498626708984</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.001277626694582705</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>0.01999688148498535, 0.014000892639160156, 0.01456141471862793, 0.014660358428955078, 0.013967752456665039, 0.012997865676879883, 0.015000581741333008</t>
+        </is>
+      </c>
+      <c r="AD91" t="n">
+        <v>0.01502653530665806</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0.01456141471862793</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0.002116057717912368</v>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8301886792452831, 0.9056603773584906, 0.8679245283018868, 0.8490566037735849, 0.9245283018867925, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>0.8410256410256409, 0.7930402930402931, 0.8443223443223443, 0.8415750915750916, 0.7371794871794872, 0.88003663003663, 0.8516483516483516</t>
+        </is>
+      </c>
+      <c r="AI91" t="n">
+        <v>0.826975405546834</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>0.8415750915750916</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>0.04367186551670905</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0.8736148547469302</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>0.03157037185529663</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>0.7857142857142856, 0.689655172413793, 0.8, 0.7586206896551724, 0.6363636363636364, 0.8461538461538461, 0.75</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>0.9249999999999999, 0.8831168831168831, 0.9382716049382716, 0.9090909090909091, 0.9047619047619048, 0.9500000000000001, 0.8918918918918919</t>
+        </is>
+      </c>
+      <c r="AQ91" t="n">
+        <v>0.914590456257123</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>0.02253773745095227</v>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>0.8553571428571427, 0.7863860277653381, 0.8691358024691358, 0.8338557993730407, 0.7705627705627706, 0.8980769230769231, 0.8209459459459459</t>
+        </is>
+      </c>
+      <c r="AU91" t="n">
+        <v>0.8334743445786138</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>0.8338557993730407</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0.04184387921364716</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0.7523582329001048</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>0.06503974734665487</v>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.6666666666666666, 0.9090909090909091, 0.7333333333333333, 0.875, 0.9166666666666666, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>0.9024390243902439, 0.8947368421052632, 0.9047619047619048, 0.9210526315789473, 0.8444444444444444, 0.926829268292683, 0.9428571428571428</t>
+        </is>
+      </c>
+      <c r="BC91" t="n">
+        <v>0.9053030369186613</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0.02914409370333505</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>0.801939726939727</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>0.1022886512962076</v>
+      </c>
+      <c r="BI91" t="inlineStr">
+        <is>
+          <t>0.7333333333333333, 0.7142857142857143, 0.7142857142857143, 0.7857142857142857, 0.5, 0.7857142857142857, 0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="BJ91" t="inlineStr">
+        <is>
+          <t>0.9487179487179487, 0.8717948717948718, 0.9743589743589743, 0.8974358974358975, 0.9743589743589743, 0.9743589743589743, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK91" t="n">
+        <v>0.9267399267399267</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>0.05022457582711386</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>0.7272108843537415</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0.1040082441013137</v>
+      </c>
+      <c r="BQ91" t="inlineStr">
+        <is>
+          <t>0.9384615384615385, 0.8663003663003662, 0.9395604395604396, 0.9468864468864469, 0.9670329670329672, 0.8946886446886446, 0.9688644688644689</t>
+        </is>
+      </c>
+      <c r="BR91" t="n">
+        <v>0.9316849816849818</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0.9395604395604396</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>0.03508092749628462</v>
+      </c>
+      <c r="BU91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BV91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="BW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CD91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CX91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE91" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="DF91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SVC_splashing_opt-model</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 18.041415988066607, 'class_weight': None, 'coef0': 0.06653734510998605, 'degree': 2, 'gamma': 'scale'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 18.041415988066607, 'class_weight': None, 'coef0': 0.06653734510998605, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.8989197530864197</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.927461139896373</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.9322916666666666</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.9298701298701298</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.9624751984126985</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0.9003417634996582</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.8994791666666666</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0.8708133971291866</v>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>0.01703166961669922, 0.01800060272216797, 0.014998435974121094, 0.019999027252197266, 0.016000032424926758, 0.014002799987792969, 0.014002084732055664</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>0.01629066467285156</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.01600003242492676</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.002051172993857287</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>0.016968965530395508, 0.02397298812866211, 0.020013093948364258, 0.016998767852783203, 0.016031980514526367, 0.014997720718383789, 0.0149688720703125</t>
+        </is>
+      </c>
+      <c r="AD92" t="n">
+        <v>0.01770748410906111</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.01696896553039551</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0.003006426250579327</v>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8301886792452831, 0.9056603773584906, 0.8679245283018868, 0.9245283018867925, 0.8490566037735849, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.803968253968254, 0.891640866873065, 0.8738390092879257, 0.9179566563467492, 0.8243034055727554, 0.8126934984520124</t>
+        </is>
+      </c>
+      <c r="AI92" t="n">
+        <v>0.8615955153991421</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>0.04370791040306145</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>0.8789058600379356</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>0.03641822060368381</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8732394366197184, 0.9275362318840579, 0.8923076923076922, 0.9411764705882353, 0.8857142857142858, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7428571428571428, 0.8648648648648649, 0.8292682926829269, 0.8947368421052632, 0.7777777777777778, 0.7647058823529413</t>
+        </is>
+      </c>
+      <c r="AQ92" t="n">
+        <v>0.8232999559328293</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>0.05750152776680204</v>
+      </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.8080482897384306, 0.8962005483744614, 0.8607879924953096, 0.9179566563467492, 0.8317460317460318, 0.8267973856209151</t>
+        </is>
+      </c>
+      <c r="AU92" t="n">
+        <v>0.8654576529983663</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0.8607879924953096</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0.04187117052825106</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0.9076153500639033</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0.8923076923076922</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0.02706061269267544</v>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.8611111111111112, 0.9142857142857143, 0.9354838709677419, 0.9411764705882353, 0.8611111111111112, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.7647058823529411, 0.8888888888888888, 0.7727272727272727, 0.8947368421052632, 0.8235294117647058, 0.8666666666666667</t>
+        </is>
+      </c>
+      <c r="BC92" t="n">
+        <v>0.8503473478705674</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0.06100429219131633</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>0.8963132085915325</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>0.03741267709229684</v>
+      </c>
+      <c r="BI92" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8857142857142857, 0.9411764705882353, 0.8529411764705882, 0.9411764705882353, 0.9117647058823529, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="BJ92" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7222222222222222, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BK92" t="n">
+        <v>0.802422723475355</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>0.08008946992652823</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>0.9207683073229292</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0.03727563488458872</v>
+      </c>
+      <c r="BQ92" t="inlineStr">
+        <is>
+          <t>0.9804511278195489, 0.8666666666666666, 0.9489164086687306, 0.9396284829721362, 0.9674922600619195, 0.9396284829721362, 0.9040247678018576</t>
+        </is>
+      </c>
+      <c r="BR92" t="n">
+        <v>0.9352583138518564</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>0.9396284829721362</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>0.03582996849273579</v>
+      </c>
+      <c r="BU92" t="inlineStr">
+        <is>
+          <t>0.8962264150943396, 0.9247648902821317, 0.9059561128526645, 0.9153605015673981, 0.9028213166144201, 0.9059561128526645, 0.9247648902821317</t>
+        </is>
+      </c>
+      <c r="BV92" t="inlineStr">
+        <is>
+          <t>0.8857543708180444, 0.9161531878476679, 0.895222957298737, 0.9045021049918378, 0.8927957728327176, 0.8932253630036945, 0.9157788469799811</t>
+        </is>
+      </c>
+      <c r="BW92" t="n">
+        <v>0.9004903719675258</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>0.895222957298737</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>0.01103266493917355</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>0.9108357485065357</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>0.9059561128526645</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>0.01023858807929395</v>
+      </c>
+      <c r="CC92" t="inlineStr">
+        <is>
+          <t>0.9197080291970803, 0.9417475728155339, 0.927536231884058, 0.9349397590361446, 0.9249394673123488, 0.9278846153846153, 0.9420289855072463</t>
+        </is>
+      </c>
+      <c r="CD92" t="inlineStr">
+        <is>
+          <t>0.8533333333333332, 0.8938053097345132, 0.8660714285714286, 0.8789237668161435, 0.8622222222222222, 0.8648648648648649, 0.8928571428571428</t>
+        </is>
+      </c>
+      <c r="CE92" t="n">
+        <v>0.8731540097713785</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0.8660714285714286</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0.01453673088192685</v>
+      </c>
+      <c r="CH92" t="inlineStr">
+        <is>
+          <t>0.8865206812652067, 0.9177764412750236, 0.8968038302277432, 0.906931762926144, 0.8935808447672855, 0.8963747401247402, 0.9174430641821946</t>
+        </is>
+      </c>
+      <c r="CI92" t="n">
+        <v>0.902204480681191</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>0.8968038302277432</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0.01121573602481712</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0.9312549515910039</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>0.9278846153846153</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>0.007911632608703652</v>
+      </c>
+      <c r="CO92" t="inlineStr">
+        <is>
+          <t>0.9174757281553398, 0.9371980676328503, 0.9230769230769231, 0.9282296650717703, 0.9227053140096618, 0.919047619047619, 0.9375</t>
+        </is>
+      </c>
+      <c r="CP92" t="inlineStr">
+        <is>
+          <t>0.8571428571428571, 0.9017857142857143, 0.8738738738738738, 0.8909090909090909, 0.8660714285714286, 0.8807339449541285, 0.9009009009009009</t>
+        </is>
+      </c>
+      <c r="CQ92" t="n">
+        <v>0.8816311158054277</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>0.8807339449541285</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>0.01588517582355774</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>0.9264619024277377</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>0.007573664841642884</v>
+      </c>
+      <c r="CW92" t="inlineStr">
+        <is>
+          <t>0.9219512195121952, 0.9463414634146341, 0.9320388349514563, 0.941747572815534, 0.9271844660194175, 0.9368932038834952, 0.9466019417475728</t>
+        </is>
+      </c>
+      <c r="CX92" t="inlineStr">
+        <is>
+          <t>0.8495575221238938, 0.8859649122807017, 0.8584070796460177, 0.8672566371681416, 0.8584070796460177, 0.8495575221238938, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY92" t="n">
+        <v>0.864872357885865</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>0.8584070796460177</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>0.01417548890837029</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>0.9361083860491864</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>0.9368932038834952</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>0.008814516510296494</v>
+      </c>
+      <c r="DE92" t="inlineStr">
+        <is>
+          <t>0.957500539607166, 0.9679931536157467, 0.9661268150184723, 0.9622605034796803, 0.9604132657444797, 0.9692413437580547, 0.9713678151043904</t>
+        </is>
+      </c>
+      <c r="DF92" t="n">
+        <v>0.9649862051897128</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>0.9661268150184723</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>0.004683562337012314</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH92"/>
+  <dimension ref="A1:DH93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36173,31 +36173,31 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>0.01703166961669922, 0.01800060272216797, 0.014998435974121094, 0.019999027252197266, 0.016000032424926758, 0.014002799987792969, 0.014002084732055664</t>
+          <t>0.03385305404663086, 0.016930818557739258, 0.015964508056640625, 0.018526554107666016, 0.016786813735961914, 0.014027833938598633, 0.014509916305541992</t>
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>0.01629066467285156</v>
+        <v>0.01865707124982561</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.01600003242492676</v>
+        <v>0.01678681373596191</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.002051172993857287</v>
+        <v>0.006361618933384177</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>0.016968965530395508, 0.02397298812866211, 0.020013093948364258, 0.016998767852783203, 0.016031980514526367, 0.014997720718383789, 0.0149688720703125</t>
+          <t>0.029328107833862305, 0.015465497970581055, 0.015213727951049805, 0.015401363372802734, 0.014502525329589844, 0.016023635864257812, 0.01510477066040039</t>
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>0.01770748410906111</v>
+        <v>0.01729137556893485</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.01696896553039551</v>
+        <v>0.01540136337280273</v>
       </c>
       <c r="AF92" t="n">
-        <v>0.003006426250579327</v>
+        <v>0.004931989007485197</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
@@ -36478,6 +36478,396 @@
       </c>
       <c r="DH92" t="n">
         <v>0.004683562337012314</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_opt-model</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 5.737910803667096, 'class_weight': None, 'coef0': 0.8535469624679377, 'degree': 2, 'gamma': 'scale'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 5.737910803667096, 'class_weight': None, 'coef0': 0.8535469624679377, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.7368421052631577</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.9345454545454545</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.8237781954887217</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.8136363636363636</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.9107142857142856</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.8987341772151899</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.8658536585365854</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0.9734641737312739</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0.9073454339194555</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0.9172569968644757</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0.9622641509433962</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0.9357798165137615</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0.9488372093023256</v>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>0.012425422668457031, 0.009999275207519531, 0.010129451751708984, 0.010998725891113281, 0.011511564254760742, 0.011305809020996094, 0.011202335357666016</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.01108179773603167</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0.01120233535766602</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.0007690863246816449</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>0.01711130142211914, 0.014055728912353516, 0.012678384780883789, 0.014551162719726562, 0.015752315521240234, 0.014023542404174805, 0.01426076889038086</t>
+        </is>
+      </c>
+      <c r="AD93" t="n">
+        <v>0.01463331495012556</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0.01426076889038086</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0.001312864857834909</v>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.7735849056603774, 0.9433962264150944, 0.9245283018867925, 0.9056603773584906, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>0.8948717948717949, 0.7545787545787546, 0.9157509157509157, 0.9487179487179487, 0.8672161172161172, 0.8901098901098901, 0.9258241758241759</t>
+        </is>
+      </c>
+      <c r="AI93" t="n">
+        <v>0.8852956567242282</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0.8948717948717949</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>0.05870157980935895</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0.8978236997104921</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0.05230826099520123</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>0.8387096774193549, 0.6250000000000001, 0.888888888888889, 0.8750000000000001, 0.8148148148148148, 0.8275862068965518, 0.8666666666666666</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>0.935064935064935, 0.8378378378378378, 0.9620253164556962, 0.945945945945946, 0.9367088607594937, 0.935064935064935, 0.9473684210526315</t>
+        </is>
+      </c>
+      <c r="AQ93" t="n">
+        <v>0.9285737503116395</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>0.0380929256656181</v>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>0.886887306242145, 0.731418918918919, 0.9254571026722926, 0.910472972972973, 0.8757618377871542, 0.8813255709807435, 0.9070175438596491</t>
+        </is>
+      </c>
+      <c r="AU93" t="n">
+        <v>0.8740487504905536</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0.886887306242145</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0.06049848657632026</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0.819523750669468</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0.08315764530247687</v>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>0.8125, 0.5555555555555556, 0.9230769230769231, 0.7777777777777778, 0.8461538461538461, 0.8, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>0.9473684210526315, 0.8857142857142857, 0.95, 1.0, 0.925, 0.9473684210526315, 0.972972972972973</t>
+        </is>
+      </c>
+      <c r="BC93" t="n">
+        <v>0.946917728684646</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0.03323672278137914</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>0.7896520146520147</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>0.1049407686566827</v>
+      </c>
+      <c r="BI93" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.8571428571428571, 1.0, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ93" t="inlineStr">
+        <is>
+          <t>0.9230769230769231, 0.7948717948717948, 0.9743589743589743, 0.8974358974358975, 0.9487179487179487, 0.9230769230769231, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK93" t="n">
+        <v>0.9120879120879122</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>0.0528285901166885</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>0.8585034013605443</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>0.08543849378950347</v>
+      </c>
+      <c r="BQ93" t="inlineStr">
+        <is>
+          <t>0.9658119658119659, 0.9175824175824177, 0.9725274725274725, 0.9597069597069597, 0.9597069597069597, 0.9505494505494505, 0.9853479853479854</t>
+        </is>
+      </c>
+      <c r="BR93" t="n">
+        <v>0.9587476016047445</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>0.9597069597069597</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>0.01967955172195972</v>
+      </c>
+      <c r="BU93" t="inlineStr">
+        <is>
+          <t>0.9182389937106918, 0.9310344827586207, 0.9184952978056427, 0.9184952978056427, 0.9184952978056427, 0.9090909090909091, 0.9184952978056427</t>
+        </is>
+      </c>
+      <c r="BV93" t="inlineStr">
+        <is>
+          <t>0.9024725274725275, 0.919281045751634, 0.9182252388134741, 0.9182252388134741, 0.9069884364002011, 0.8968325791855204, 0.9032428355957768</t>
+        </is>
+      </c>
+      <c r="BW93" t="n">
+        <v>0.9093239860046584</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>0.9069884364002011</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>0.008477032436672459</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>0.9189065109689702</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0.9184952978056427</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>0.005910713086204811</v>
+      </c>
+      <c r="CC93" t="inlineStr">
+        <is>
+          <t>0.8488372093023256, 0.8735632183908046, 0.8571428571428571, 0.8571428571428571, 0.8522727272727273, 0.8361581920903954, 0.8505747126436781</t>
+        </is>
+      </c>
+      <c r="CD93" t="inlineStr">
+        <is>
+          <t>0.9439655172413793, 0.9525862068965517, 0.9429824561403509, 0.9429824561403509, 0.9437229437229437, 0.9370932754880693, 0.9439655172413793</t>
+        </is>
+      </c>
+      <c r="CE93" t="n">
+        <v>0.9438997675530036</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0.9437229437229437</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0.004200431880255032</v>
+      </c>
+      <c r="CH93" t="inlineStr">
+        <is>
+          <t>0.8964013632718525, 0.9130747126436782, 0.900062656641604, 0.900062656641604, 0.8979978354978355, 0.8866257337892324, 0.8972701149425287</t>
+        </is>
+      </c>
+      <c r="CI93" t="n">
+        <v>0.8987850104897622</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>0.8979978354978355</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0.00721015834928851</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0.8536702534265208</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0.8522727272727273</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0.01042945052687042</v>
+      </c>
+      <c r="CO93" t="inlineStr">
+        <is>
+          <t>0.8295454545454546, 0.8539325842696629, 0.8041237113402062, 0.8041237113402062, 0.8241758241758241, 0.8043478260869565, 0.8314606741573034</t>
+        </is>
+      </c>
+      <c r="CP93" t="inlineStr">
+        <is>
+          <t>0.9521739130434783, 0.9608695652173913, 0.9684684684684685, 0.9684684684684685, 0.956140350877193, 0.9515418502202643, 0.9521739130434783</t>
+        </is>
+      </c>
+      <c r="CQ93" t="n">
+        <v>0.9585480756198204</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>0.956140350877193</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>0.006952511698038863</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>0.8216728265593732</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>0.8241758241758241</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>0.01740622108788583</v>
+      </c>
+      <c r="CW93" t="inlineStr">
+        <is>
+          <t>0.8690476190476191, 0.8941176470588236, 0.9176470588235294, 0.9176470588235294, 0.8823529411764706, 0.8705882352941177, 0.8705882352941177</t>
+        </is>
+      </c>
+      <c r="CX93" t="inlineStr">
+        <is>
+          <t>0.9358974358974359, 0.9444444444444444, 0.9188034188034188, 0.9188034188034188, 0.9316239316239316, 0.9230769230769231, 0.9358974358974359</t>
+        </is>
+      </c>
+      <c r="CY93" t="n">
+        <v>0.9297924297924298</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>0.9316239316239316</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>0.009096254228175426</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>0.8888555422168868</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>0.01995573404663581</v>
+      </c>
+      <c r="DE93" t="inlineStr">
+        <is>
+          <t>0.9701872201872203, 0.9768225238813475, 0.9674710910005028, 0.9717948717948718, 0.9693564605329311, 0.9747611865258924, 0.963298139768728</t>
+        </is>
+      </c>
+      <c r="DF93" t="n">
+        <v>0.970527356241642</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>0.9701872201872203</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>0.004179030432633732</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH93"/>
+  <dimension ref="A1:DH99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36868,6 +36868,2346 @@
       </c>
       <c r="DH93" t="n">
         <v>0.004179030432633732</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 0.47129737561107793, 'class_weight': None, 'penalty': 'l2'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 0.47129737561107793, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.8444444444444444</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.8172043010752689</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.8865740740740741</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.7594793435200906</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.7662037037037037</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.8383838383838383</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.796875</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.8644067796610169</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.9173859126984127</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0.8322033898305085</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0.8555803571428571</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>0.011999845504760742, 0.011874675750732422, 0.011998891830444336, 0.011457443237304688, 0.010410308837890625, 0.01091313362121582, 0.01103830337524414</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>0.01138465745108468</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.01145744323730469</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.0005723144748496659</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>0.017076492309570312, 0.014981508255004883, 0.015033721923828125, 0.015428781509399414, 0.014036893844604492, 0.014475345611572266, 0.015532970428466797</t>
+        </is>
+      </c>
+      <c r="AD94" t="n">
+        <v>0.01522367341177804</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0.01503372192382812</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0.000897125378465606</v>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8113207547169812, 0.8301886792452831, 0.7924528301886793, 0.8113207547169812, 0.7735849056603774, 0.7735849056603774</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.8166666666666667, 0.8560371517027863, 0.8150154798761611, 0.818111455108359, 0.8119195046439629, 0.7654798761609907</t>
+        </is>
+      </c>
+      <c r="AI94" t="n">
+        <v>0.8288610180914471</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>0.04405704094412394</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0.816911250873515</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>0.04851443893604541</v>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8484848484848486, 0.8524590163934426, 0.819672131147541, 0.84375, 0.7931034482758621, 0.8181818181818182</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7499999999999999, 0.7999999999999999, 0.7555555555555555, 0.761904761904762, 0.75, 0.7</t>
+        </is>
+      </c>
+      <c r="AQ94" t="n">
+        <v>0.7731710227950829</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>0.05652188821857555</v>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7992424242424243, 0.8262295081967213, 0.7876138433515483, 0.8028273809523809, 0.771551724137931, 0.759090909090909</t>
+        </is>
+      </c>
+      <c r="AU94" t="n">
+        <v>0.8093361117790167</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0.7992424242424243</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0.04904140326572431</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0.8455012007629508</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0.04423568934815662</v>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.9032258064516129, 0.9629629629629629, 0.9259259259259259, 0.9, 0.9583333333333334, 0.84375</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.6818181818181818, 0.6923076923076923, 0.6538461538461539, 0.6956521739130435, 0.6206896551724138, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BC94" t="n">
+        <v>0.7008167665470593</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0.08268515244525924</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>0.9195793102187111</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>0.03848380627638249</v>
+      </c>
+      <c r="BI94" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8, 0.7647058823529411, 0.7352941176470589, 0.7941176470588235, 0.6764705882352942, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ94" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.9473684210526315, 0.8947368421052632, 0.8421052631578947, 0.9473684210526315, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BK94" t="n">
+        <v>0.8709273182957393</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>0.06870551459585363</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>0.7867947178871548</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>0.07554445485019097</v>
+      </c>
+      <c r="BQ94" t="inlineStr">
+        <is>
+          <t>0.962406015037594, 0.8650793650793651, 0.9473684210526316, 0.8684210526315789, 0.9380804953560372, 0.8359133126934984, 0.8668730650154799</t>
+        </is>
+      </c>
+      <c r="BR94" t="n">
+        <v>0.897734532409455</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>0.8684210526315789</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>0.04625033392956519</v>
+      </c>
+      <c r="BU94" t="inlineStr">
+        <is>
+          <t>0.8144654088050315, 0.8244514106583072, 0.8181818181818182, 0.8213166144200627, 0.8213166144200627, 0.8213166144200627, 0.8432601880877743</t>
+        </is>
+      </c>
+      <c r="BV94" t="inlineStr">
+        <is>
+          <t>0.8322685085257933, 0.8419982884039368, 0.8352521694303634, 0.8356817596013404, 0.8336841653062979, 0.8376793538963828, 0.8466792679783486</t>
+        </is>
+      </c>
+      <c r="BW94" t="n">
+        <v>0.8376062161632091</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>0.8356817596013404</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>0.004701589271750212</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>0.823472666999017</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0.8213166144200627</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>0.008582152573283645</v>
+      </c>
+      <c r="CC94" t="inlineStr">
+        <is>
+          <t>0.8426666666666668, 0.8510638297872339, 0.8465608465608466, 0.8503937007874015, 0.8511749347258485, 0.8496042216358839, 0.8730964467005077</t>
+        </is>
+      </c>
+      <c r="CD94" t="inlineStr">
+        <is>
+          <t>0.7739463601532568, 0.7862595419847328, 0.7769230769230768, 0.7782101167315174, 0.776470588235294, 0.7799227799227799, 0.7950819672131147</t>
+        </is>
+      </c>
+      <c r="CE94" t="n">
+        <v>0.7809734901662532</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0.7782101167315174</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0.00678016247829866</v>
+      </c>
+      <c r="CH94" t="inlineStr">
+        <is>
+          <t>0.8083065134099618, 0.8186616858859834, 0.8117419617419617, 0.8143019087594594, 0.8138227614805713, 0.8147635007793319, 0.8340892069568112</t>
+        </is>
+      </c>
+      <c r="CI94" t="n">
+        <v>0.8165267912877258</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>0.8143019087594594</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0.007735214967265304</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0.8520800924091985</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>0.8503937007874015</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0.009036337434249156</v>
+      </c>
+      <c r="CO94" t="inlineStr">
+        <is>
+          <t>0.9294117647058824, 0.935672514619883, 0.9302325581395349, 0.9257142857142857, 0.9209039548022598, 0.930635838150289, 0.9148936170212766</t>
+        </is>
+      </c>
+      <c r="CP94" t="inlineStr">
+        <is>
+          <t>0.6824324324324325, 0.6959459459459459, 0.6870748299319728, 0.6944444444444444, 0.6971830985915493, 0.6917808219178082, 0.7404580152671756</t>
+        </is>
+      </c>
+      <c r="CQ94" t="n">
+        <v>0.6984742269330468</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>0.01780458985936085</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>0.9267806475933446</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>0.9294117647058824</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>0.006433621494772158</v>
+      </c>
+      <c r="CW94" t="inlineStr">
+        <is>
+          <t>0.7707317073170732, 0.7804878048780488, 0.7766990291262136, 0.7864077669902912, 0.7912621359223301, 0.7815533980582524, 0.8349514563106796</t>
+        </is>
+      </c>
+      <c r="CX94" t="inlineStr">
+        <is>
+          <t>0.8938053097345132, 0.9035087719298246, 0.8938053097345132, 0.8849557522123894, 0.8761061946902655, 0.8938053097345132, 0.8584070796460177</t>
+        </is>
+      </c>
+      <c r="CY94" t="n">
+        <v>0.8863419610974338</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>0.8938053097345132</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>0.01388140690435868</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>0.7888704712289841</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>0.7815533980582524</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>0.01977086446669224</v>
+      </c>
+      <c r="DE94" t="inlineStr">
+        <is>
+          <t>0.9009497086121303, 0.9152332049636286, 0.9052109287739497, 0.9146619125354412, 0.9054686828765358, 0.9215138757625225, 0.9120843715095799</t>
+        </is>
+      </c>
+      <c r="DF94" t="n">
+        <v>0.9107318121476841</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.9120843715095799</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>0.006629595672810654</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'newton-cholesky', 'C': 6.5706235157060515, 'class_weight': 'balanced', 'penalty': 'l2'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'newton-cholesky', 'C': 6.5706235157060515, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.7346938775510204</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.9509090909090909</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.8029905031319459</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.8712871287128713</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.8316498316498316</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.6260869565217392</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.7422680412371135</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0.9458831726860992</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0.8086340206185567</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.8570723493206364</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.8027522935779816</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>0.009731769561767578, 0.010012388229370117, 0.009104728698730469, 0.009039163589477539, 0.010002613067626953, 0.008647680282592773, 0.008929014205932617</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>0.009352479662214006</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0.009104728698730469</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.0005123651389478475</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>0.01586008071899414, 0.01587843894958496, 0.014185667037963867, 0.013430356979370117, 0.013245820999145508, 0.013036012649536133, 0.01393437385559082</t>
+        </is>
+      </c>
+      <c r="AD95" t="n">
+        <v>0.01422439302716936</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0.01393437385559082</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0.001101771128809612</v>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7169811320754716, 0.8490566037735849, 0.8113207547169812, 0.8301886792452831, 0.8679245283018868, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>0.9025641025641026, 0.7161172161172161, 0.8745421245421245, 0.848901098901099, 0.8617216117216118, 0.8644688644688645, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI95" t="n">
+        <v>0.8540816326530614</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0.8644688644688645</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0.05994291246177208</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0.8331835879005691</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>0.05312903801593512</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.5714285714285714, 0.7647058823529412, 0.7222222222222223, 0.742857142857143, 0.7741935483870968, 0.8</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.7887323943661971, 0.8888888888888888, 0.8571428571428572, 0.8732394366197183, 0.9066666666666667, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ95" t="n">
+        <v>0.876428230472496</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0.04065842864681587</v>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>0.8712241653418124, 0.6800804828973843, 0.826797385620915, 0.7896825396825398, 0.8080482897384307, 0.8404301075268817, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU95" t="n">
+        <v>0.8095667423085823</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0.826797385620915</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0.05844136413827328</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0.7427052541446686</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0.7647058823529412</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0.0765749421739622</v>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.47619047619047616, 0.65, 0.5909090909090909, 0.6190476190476191, 0.7058823529411765, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.875, 0.9696969696969697, 0.967741935483871, 0.96875, 0.9444444444444444, 1.0</t>
+        </is>
+      </c>
+      <c r="BC95" t="n">
+        <v>0.9567231315791224</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0.03655319758017286</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>0.6350769015740267</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>0.07932105676016318</v>
+      </c>
+      <c r="BI95" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7142857142857143, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ95" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.717948717948718, 0.8205128205128205, 0.7692307692307693, 0.7948717948717948, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK95" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>0.05101973727906271</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>0.8986394557823129</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>0.08440858432242775</v>
+      </c>
+      <c r="BQ95" t="inlineStr">
+        <is>
+          <t>0.9555555555555555, 0.8974358974358975, 0.9706959706959708, 0.9395604395604396, 0.9212454212454213, 0.9432234432234432, 1.0</t>
+        </is>
+      </c>
+      <c r="BR95" t="n">
+        <v>0.946816675388104</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>0.9432234432234432</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>0.03078257701345802</v>
+      </c>
+      <c r="BU95" t="inlineStr">
+        <is>
+          <t>0.8207547169811321, 0.8495297805642633, 0.8307210031347962, 0.8432601880877743, 0.8526645768025078, 0.8307210031347962, 0.8307210031347962</t>
+        </is>
+      </c>
+      <c r="BV95" t="inlineStr">
+        <is>
+          <t>0.8438644688644689, 0.8712166918049271, 0.85465057817999, 0.8631975867269985, 0.8621166415284063, 0.85465057817999, 0.8509049773755657</t>
+        </is>
+      </c>
+      <c r="BW95" t="n">
+        <v>0.8572287889514781</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>0.85465057817999</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>0.008341540297438091</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>0.8369103245485808</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>0.8307210031347962</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>0.01084761103219961</v>
+      </c>
+      <c r="CC95" t="inlineStr">
+        <is>
+          <t>0.7246376811594203, 0.7647058823529411, 0.7403846153846153, 0.7549019607843137, 0.7614213197969542, 0.7403846153846153, 0.7378640776699029</t>
+        </is>
+      </c>
+      <c r="CD95" t="inlineStr">
+        <is>
+          <t>0.8671328671328672, 0.8894009216589861, 0.8744186046511628, 0.8847926267281105, 0.8934240362811792, 0.8744186046511628, 0.875</t>
+        </is>
+      </c>
+      <c r="CE95" t="n">
+        <v>0.8797982373004957</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0.008816651843155495</v>
+      </c>
+      <c r="CH95" t="inlineStr">
+        <is>
+          <t>0.7958852741461437, 0.8270534020059637, 0.8074016100178891, 0.8198472937562121, 0.8274226780390667, 0.8074016100178891, 0.8064320388349515</t>
+        </is>
+      </c>
+      <c r="CI95" t="n">
+        <v>0.8130634152597308</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>0.8074016100178891</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>0.01102662315087141</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0.7463285932189662</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>0.7403846153846153</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0.01337280405112217</v>
+      </c>
+      <c r="CO95" t="inlineStr">
+        <is>
+          <t>0.6097560975609756, 0.6554621848739496, 0.6260162601626016, 0.6470588235294118, 0.6696428571428571, 0.6260162601626016, 0.628099173553719</t>
+        </is>
+      </c>
+      <c r="CP95" t="inlineStr">
+        <is>
+          <t>0.9538461538461539, 0.965, 0.9591836734693877, 0.96, 0.9516908212560387, 0.9591836734693877, 0.9545454545454546</t>
+        </is>
+      </c>
+      <c r="CQ95" t="n">
+        <v>0.9576356823694889</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>0.9591836734693877</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>0.004206578742255173</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>0.6374359509980165</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>0.628099173553719</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>0.01915723646869028</v>
+      </c>
+      <c r="CW95" t="inlineStr">
+        <is>
+          <t>0.8928571428571429, 0.9176470588235294, 0.9058823529411765, 0.9058823529411765, 0.8823529411764706, 0.9058823529411765, 0.8941176470588236</t>
+        </is>
+      </c>
+      <c r="CX95" t="inlineStr">
+        <is>
+          <t>0.7948717948717948, 0.8247863247863247, 0.8034188034188035, 0.8205128205128205, 0.8418803418803419, 0.8034188034188035, 0.8076923076923077</t>
+        </is>
+      </c>
+      <c r="CY95" t="n">
+        <v>0.8137973137973137</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>0.01495414983384113</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>0.9006602641056424</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>0.01075183998923873</v>
+      </c>
+      <c r="DE95" t="inlineStr">
+        <is>
+          <t>0.9463268213268213, 0.9540975364504777, 0.9437405731523378, 0.9492709904474611, 0.9479135243841126, 0.9507792860734038, 0.9380593262946205</t>
+        </is>
+      </c>
+      <c r="DF95" t="n">
+        <v>0.9471697225898907</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>0.9479135243841126</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>0.004802692551476039</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 2, 'weights': 'distance', 'p': 1}, 'base_estimator_params': {'n_neighbors': 2, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.8800154320987654</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.8332996564962618</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.9973890339425587</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.9999751984126984</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0.996324848724834</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.9973958333333333</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0.9905660377358491</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0.9952606635071091</v>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>0.011987924575805664, 0.009905338287353516, 0.008966207504272461, 0.009542465209960938, 0.009782791137695312, 0.009510040283203125, 0.009002685546875</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>0.009813921792166573</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.009542465209960938</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.0009470533703167229</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>0.019345521926879883, 0.016130924224853516, 0.01617574691772461, 0.015309572219848633, 0.0145721435546875, 0.015524625778198242, 0.014997482299804688</t>
+        </is>
+      </c>
+      <c r="AD96" t="n">
+        <v>0.01600800241742815</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0.01552462577819824</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0.001463195317602059</v>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8113207547169812, 0.8867924528301887, 0.9245283018867925, 0.9056603773584906, 0.9056603773584906, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8166666666666667, 0.8769349845201238, 0.9295665634674922, 0.891640866873065, 0.914860681114551, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI96" t="n">
+        <v>0.885905941323898</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0.891640866873065</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>0.03340345223601217</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0.8923829489867227</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>0.03614380377193017</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>0.945945945945946, 0.8484848484848486, 0.9117647058823528, 0.9393939393939394, 0.9275362318840579, 0.923076923076923, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.7499999999999999, 0.8421052631578947, 0.9, 0.8648648648648649, 0.8780487804878049, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ96" t="n">
+        <v>0.8513538732635614</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>0.8648648648648649</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0.04577309569572132</v>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>0.9141494435612083, 0.7992424242424243, 0.8769349845201238, 0.9196969696969697, 0.8962005483744614, 0.900562851782364, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU96" t="n">
+        <v>0.8833888866710965</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0.8962005483744614</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0.03758325111698525</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0.9154239000786316</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0.02980664222256574</v>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9032258064516129, 0.9117647058823529, 0.96875, 0.9142857142857143, 0.967741935483871, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>1.0, 0.6818181818181818, 0.8421052631578947, 0.8571428571428571, 0.8888888888888888, 0.8181818181818182, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC96" t="n">
+        <v>0.8471774674782193</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0.08736603921685659</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>0.9249955379174003</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>0.02787721190074099</v>
+      </c>
+      <c r="BI96" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.9117647058823529, 0.9411764705882353, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ96" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.8333333333333334, 0.8421052631578947, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK96" t="n">
+        <v>0.8634085213032582</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>0.05584531317082</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>0.9084033613445379</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>0.0559691623709133</v>
+      </c>
+      <c r="BQ96" t="inlineStr">
+        <is>
+          <t>0.9165413533834588, 0.8603174603174604, 0.9489164086687306, 0.9613003095975232, 0.8893188854489165, 0.9458204334365325, 0.9109907120743034</t>
+        </is>
+      </c>
+      <c r="BR96" t="n">
+        <v>0.9190293661324179</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>0.9165413533834588</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>0.03337758010073159</v>
+      </c>
+      <c r="BU96" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV96" t="inlineStr">
+        <is>
+          <t>0.9975609756097561, 1.0, 0.9975728155339806, 0.9975728155339806, 0.9975728155339806, 1.0, 0.9975728155339806</t>
+        </is>
+      </c>
+      <c r="BW96" t="n">
+        <v>0.9982646053922398</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>0.9975728155339806</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>0.001097567218380571</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC96" t="inlineStr">
+        <is>
+          <t>0.9975550122249389, 1.0, 0.9975669099756691, 0.9975669099756691, 0.9975669099756691, 1.0, 0.9975669099756691</t>
+        </is>
+      </c>
+      <c r="CD96" t="inlineStr">
+        <is>
+          <t>0.9955947136563876, 1.0, 0.9955947136563876, 0.9955947136563876, 0.9955947136563876, 1.0, 0.9955947136563876</t>
+        </is>
+      </c>
+      <c r="CE96" t="n">
+        <v>0.9968533668974198</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0.9955947136563876</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0.001990105513007176</v>
+      </c>
+      <c r="CH96" t="inlineStr">
+        <is>
+          <t>0.9965748629406632, 1.0, 0.9965808118160284, 0.9965808118160284, 0.9965808118160284, 1.0, 0.9965808118160284</t>
+        </is>
+      </c>
+      <c r="CI96" t="n">
+        <v>0.9975568728863966</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>0.9965808118160284</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0.001545170567206118</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0.9982603788753737</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0.9975669099756691</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0.001100240355913701</v>
+      </c>
+      <c r="CO96" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP96" t="inlineStr">
+        <is>
+          <t>0.9912280701754386, 1.0, 0.9912280701754386, 0.9912280701754386, 0.9912280701754386, 1.0, 0.9912280701754386</t>
+        </is>
+      </c>
+      <c r="CQ96" t="n">
+        <v>0.9937343358395989</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>0.9912280701754386</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>0.003962753960110763</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW96" t="inlineStr">
+        <is>
+          <t>0.9951219512195122, 1.0, 0.9951456310679612, 0.9951456310679612, 0.9951456310679612, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX96" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 1.0, 1.0, 1.0, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>0.9965292107844796</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>0.9951456310679612</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>0.002195134436761142</v>
+      </c>
+      <c r="DE96" t="inlineStr">
+        <is>
+          <t>0.9999784157133607, 1.0, 0.9999785204914512, 0.9999785204914512, 0.9999785204914512, 1.0, 0.9999785204914512</t>
+        </is>
+      </c>
+      <c r="DF96" t="n">
+        <v>0.999984642525595</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>0.9999785204914512</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>9.712984233443666e-06</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'base_estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.7391304347826088</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.9031818181818182</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.8118729096989967</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.8431818181818181</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.8363636363636363</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.9427609427609428</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.8369565217391305</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.9746835443037974</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.9005847953216375</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0.9932934618511207</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0.9301978350130646</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0.9529381024271281</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0.9902439024390244</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0.9311926605504587</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0.9598108747044918</v>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>0.010000467300415039, 0.008997917175292969, 0.008598804473876953, 0.007999181747436523, 0.009029865264892578, 0.007953166961669922, 0.0070002079010009766</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>0.008511372974940709</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0.008598804473876953</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.0008934811036678975</v>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>0.019122600555419922, 0.016436338424682617, 0.01525115966796875, 0.016414403915405273, 0.015381813049316406, 0.016277074813842773, 0.016347169876098633</t>
+        </is>
+      </c>
+      <c r="AD97" t="n">
+        <v>0.01646150861467634</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0.01634716987609863</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0.00118092209546679</v>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.9245283018867925, 0.8867924528301887, 0.9056603773584906, 0.9056603773584906, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>0.8564102564102565, 0.728937728937729, 0.9029304029304028, 0.9001831501831502, 0.8672161172161172, 0.8901098901098901, 0.8873626373626373</t>
+        </is>
+      </c>
+      <c r="AI97" t="n">
+        <v>0.8618785975928832</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>0.8873626373626373</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>0.05648084132895018</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>0.868323849455925</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>0.05868696535610506</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>0.7647058823529413, 0.588235294117647, 0.8571428571428571, 0.8125000000000001, 0.8148148148148148, 0.8275862068965518, 0.7878787878787878</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8055555555555556, 0.9487179487179487, 0.9189189189189189, 0.9367088607594937, 0.935064935064935, 0.9041095890410958</t>
+        </is>
+      </c>
+      <c r="AQ97" t="n">
+        <v>0.9058525285642629</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>0.9189189189189189</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>0.04483473261585094</v>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>0.8282988871224166, 0.6968954248366013, 0.9029304029304028, 0.8657094594594594, 0.8757618377871542, 0.8813255709807435, 0.8459941884599418</t>
+        </is>
+      </c>
+      <c r="AU97" t="n">
+        <v>0.8424165387966743</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>0.8657094594594594</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0.06349219516686723</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0.7789805490290858</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0.8125000000000001</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0.08241549925206183</v>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>0.6842105263157895, 0.5, 0.8571428571428571, 0.7222222222222222, 0.8461538461538461, 0.8, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8787878787878788, 0.9487179487179487, 0.9714285714285714, 0.925, 0.9473684210526315, 0.9705882352941176</t>
+        </is>
+      </c>
+      <c r="BC97" t="n">
+        <v>0.9406783140197559</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0.02935146085031867</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>0.7277057111643578</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>0.1144390176954305</v>
+      </c>
+      <c r="BI97" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.8571428571428571, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ97" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.7435897435897436, 0.9487179487179487, 0.8717948717948718, 0.9487179487179487, 0.9230769230769231, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK97" t="n">
+        <v>0.8754578754578753</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>0.0677408132194393</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>0.8482993197278912</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>0.07097034751425839</v>
+      </c>
+      <c r="BQ97" t="inlineStr">
+        <is>
+          <t>0.9128205128205128, 0.7884615384615384, 0.934981684981685, 0.9532967032967032, 0.9597069597069597, 0.8965201465201466, 0.9267399267399267</t>
+        </is>
+      </c>
+      <c r="BR97" t="n">
+        <v>0.9103610675039248</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>0.9267399267399267</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>0.0537321968905618</v>
+      </c>
+      <c r="BU97" t="inlineStr">
+        <is>
+          <t>0.949685534591195, 0.9435736677115988, 0.9435736677115988, 0.9404388714733543, 0.9373040752351097, 0.9498432601880877, 0.9529780564263323</t>
+        </is>
+      </c>
+      <c r="BV97" t="inlineStr">
+        <is>
+          <t>0.9543650793650793, 0.9465560583207642, 0.9503016591251885, 0.944419306184012, 0.9385369532428356, 0.9620663650075415, 0.9567119155354449</t>
+        </is>
+      </c>
+      <c r="BW97" t="n">
+        <v>0.950422476682981</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>0.9503016591251885</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>0.007396416155549377</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>0.9453424476196108</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>0.9435736677115988</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>0.005241863005903344</v>
+      </c>
+      <c r="CC97" t="inlineStr">
+        <is>
+          <t>0.9101123595505619, 0.9, 0.9010989010989011, 0.8950276243093922, 0.8888888888888888, 0.9130434782608696, 0.9162011173184357</t>
+        </is>
+      </c>
+      <c r="CD97" t="inlineStr">
+        <is>
+          <t>0.9650655021834061, 0.9606986899563319, 0.9605263157894737, 0.9584245076586433, 0.9563318777292577, 0.9647577092511014, 0.9673202614379085</t>
+        </is>
+      </c>
+      <c r="CE97" t="n">
+        <v>0.9618749805723031</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0.9606986899563319</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0.003664013124936622</v>
+      </c>
+      <c r="CH97" t="inlineStr">
+        <is>
+          <t>0.937588930866984, 0.9303493449781659, 0.9308126084441875, 0.9267260659840177, 0.9226103833090733, 0.9389005937559856, 0.941760689378172</t>
+        </is>
+      </c>
+      <c r="CI97" t="n">
+        <v>0.9326783738166552</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>0.9308126084441875</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0.0064477892626383</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>0.9034817670610069</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0.9010989010989011</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>0.009253557801305483</v>
+      </c>
+      <c r="CO97" t="inlineStr">
+        <is>
+          <t>0.8617021276595744, 0.8526315789473684, 0.845360824742268, 0.84375, 0.8421052631578947, 0.8484848484848485, 0.8723404255319149</t>
+        </is>
+      </c>
+      <c r="CP97" t="inlineStr">
+        <is>
+          <t>0.9866071428571429, 0.9821428571428571, 0.9864864864864865, 0.9820627802690582, 0.9776785714285714, 0.9954545454545455, 0.9866666666666667</t>
+        </is>
+      </c>
+      <c r="CQ97" t="n">
+        <v>0.9852998643293326</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>0.9864864864864865</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>0.005163501853603294</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>0.8523392955034099</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>0.01021106185390729</v>
+      </c>
+      <c r="CW97" t="inlineStr">
+        <is>
+          <t>0.9642857142857143, 0.9529411764705882, 0.9647058823529412, 0.9529411764705882, 0.9411764705882353, 0.9882352941176471, 0.9647058823529412</t>
+        </is>
+      </c>
+      <c r="CX97" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9401709401709402, 0.9358974358974359, 0.9358974358974359, 0.9358974358974359, 0.9358974358974359, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="CY97" t="n">
+        <v>0.9395604395604397</v>
+      </c>
+      <c r="CZ97" t="n">
+        <v>0.9358974358974359</v>
+      </c>
+      <c r="DA97" t="n">
+        <v>0.004807086614170807</v>
+      </c>
+      <c r="DB97" t="n">
+        <v>0.9612845138055223</v>
+      </c>
+      <c r="DC97" t="n">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="DD97" t="n">
+        <v>0.0136398536179124</v>
+      </c>
+      <c r="DE97" t="inlineStr">
+        <is>
+          <t>0.99239417989418, 0.9927099044746104, 0.9914781297134239, 0.9908748114630468, 0.989693313222725, 0.9942433383609854, 0.9935897435897436</t>
+        </is>
+      </c>
+      <c r="DF97" t="n">
+        <v>0.9921404886741022</v>
+      </c>
+      <c r="DG97" t="n">
+        <v>0.99239417989418</v>
+      </c>
+      <c r="DH97" t="n">
+        <v>0.001460931018726838</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 8.080278139769582, 'class_weight': 'balanced', 'coef0': 0.48875906950513137, 'degree': 2, 'gamma': 'auto'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 8.080278139769582, 'class_weight': 'balanced', 'coef0': 0.48875906950513137, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.8927469135802468</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.8068924539512775</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.7450980392156864</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.9057239057239057</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.9408602150537635</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.9114583333333334</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0.9553323412698412</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.8981481481481481</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.9033482142857143</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0.8468468468468469</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0.8952380952380953</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>0.019130468368530273, 0.017958402633666992, 0.01714777946472168, 0.0182952880859375, 0.0179290771484375, 0.01857900619506836, 0.016715526580810547</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>0.01796507835388184</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.01795840263366699</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.0007629620386935909</v>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>0.014995336532592773, 0.015069723129272461, 0.013968467712402344, 0.015926599502563477, 0.014991998672485352, 0.014536142349243164, 0.01496744155883789</t>
+        </is>
+      </c>
+      <c r="AD98" t="n">
+        <v>0.01492224420819964</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>0.01499199867248535</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>0.0005479174615344102</v>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7735849056603774, 0.9056603773584906, 0.8490566037735849, 0.9056603773584906, 0.9056603773584906, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.7746031746031746, 0.914860681114551, 0.8707430340557275, 0.903250773993808, 0.903250773993808, 0.8738390092879257</t>
+        </is>
+      </c>
+      <c r="AI98" t="n">
+        <v>0.8781877663346039</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>0.903250773993808</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>0.04507467236953443</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0.8762104422481781</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>0.04842005697919719</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8181818181818182, 0.923076923076923, 0.8709677419354839, 0.9253731343283583, 0.9253731343283583, 0.8923076923076922</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7000000000000001, 0.8780487804878049, 0.8181818181818181, 0.8717948717948718, 0.8717948717948718, 0.8292682926829269</t>
+        </is>
+      </c>
+      <c r="AQ98" t="n">
+        <v>0.8368539319758831</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>0.06092334679157772</v>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.7590909090909091, 0.900562851782364, 0.8445747800586509, 0.898584003061615, 0.898584003061615, 0.8607879924953096</t>
+        </is>
+      </c>
+      <c r="AU98" t="n">
+        <v>0.8684073151738756</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>0.898584003061615</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0.05037052563869247</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0.8999606983718683</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0.04034085589719612</v>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.8709677419354839, 0.967741935483871, 0.9642857142857143, 0.9393939393939394, 0.9393939393939394, 0.9354838709677419</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6363636363636364, 0.8181818181818182, 0.72, 0.85, 0.85, 0.7727272727272727</t>
+        </is>
+      </c>
+      <c r="BC98" t="n">
+        <v>0.798349885408709</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0.09193396338834088</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>0.9337408657685157</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>0.03003847115866569</v>
+      </c>
+      <c r="BI98" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.8823529411764706, 0.7941176470588235, 0.9117647058823529, 0.9117647058823529, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ98" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.7777777777777778, 0.9473684210526315, 0.9473684210526315, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632</t>
+        </is>
+      </c>
+      <c r="BK98" t="n">
+        <v>0.8855472013366749</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>0.05528953085304691</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>0.870828331332533</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0.06512580147218698</v>
+      </c>
+      <c r="BQ98" t="inlineStr">
+        <is>
+          <t>0.9789473684210526, 0.8809523809523809, 0.956656346749226, 0.9272445820433437, 0.9690402476780186, 0.911764705882353, 0.9148606811145511</t>
+        </is>
+      </c>
+      <c r="BR98" t="n">
+        <v>0.9342094732629895</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0.9272445820433437</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>0.03269227774760999</v>
+      </c>
+      <c r="BU98" t="inlineStr">
+        <is>
+          <t>0.8962264150943396, 0.9028213166144201, 0.896551724137931, 0.8996865203761756, 0.896551724137931, 0.9059561128526645, 0.9028213166144201</t>
+        </is>
+      </c>
+      <c r="BV98" t="inlineStr">
+        <is>
+          <t>0.8996546514137708, 0.9088147197261447, 0.8959317810808489, 0.9023541541369533, 0.8959317810808489, 0.9052109287739496, 0.912771715783143</t>
+        </is>
+      </c>
+      <c r="BW98" t="n">
+        <v>0.9029528188565228</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>0.9023541541369533</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>0.005924500339170411</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>0.9000878756896975</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>0.8996865203761756</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>0.00357491869218305</v>
+      </c>
+      <c r="CC98" t="inlineStr">
+        <is>
+          <t>0.9168765743073047, 0.9215189873417722, 0.9181141439205956, 0.92, 0.9181141439205956, 0.9257425742574257, 0.921119592875318</t>
+        </is>
+      </c>
+      <c r="CD98" t="inlineStr">
+        <is>
+          <t>0.8619246861924685, 0.8724279835390947, 0.8595744680851064, 0.8655462184873949, 0.8595744680851064, 0.8717948717948718, 0.8734693877551021</t>
+        </is>
+      </c>
+      <c r="CE98" t="n">
+        <v>0.866330297705592</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0.8655462184873949</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0.005723592902356963</v>
+      </c>
+      <c r="CH98" t="inlineStr">
+        <is>
+          <t>0.8894006302498867, 0.8969734854404334, 0.888844306002851, 0.8927731092436975, 0.888844306002851, 0.8987687230261487, 0.89729449031521</t>
+        </is>
+      </c>
+      <c r="CI98" t="n">
+        <v>0.893271292897297</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>0.8927731092436975</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>0.004045115702416007</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0.9202122880890017</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>0.002753989329424617</v>
+      </c>
+      <c r="CO98" t="inlineStr">
+        <is>
+          <t>0.9479166666666666, 0.9578947368421052, 0.9390862944162437, 0.9484536082474226, 0.9390862944162437, 0.9444444444444444, 0.9679144385026738</t>
+        </is>
+      </c>
+      <c r="CP98" t="inlineStr">
+        <is>
+          <t>0.8174603174603174, 0.8217054263565892, 0.8278688524590164, 0.824, 0.8278688524590164, 0.8429752066115702, 0.8106060606060606</t>
+        </is>
+      </c>
+      <c r="CQ98" t="n">
+        <v>0.82464067370751</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>0.009369794886213419</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>0.9492566405051143</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>0.009674706604636844</v>
+      </c>
+      <c r="CW98" t="inlineStr">
+        <is>
+          <t>0.8878048780487805, 0.8878048780487805, 0.8980582524271845, 0.8932038834951457, 0.8980582524271845, 0.9077669902912622, 0.8786407766990292</t>
+        </is>
+      </c>
+      <c r="CX98" t="inlineStr">
+        <is>
+          <t>0.911504424778761, 0.9298245614035088, 0.8938053097345132, 0.911504424778761, 0.8938053097345132, 0.9026548672566371, 0.9469026548672567</t>
+        </is>
+      </c>
+      <c r="CY98" t="n">
+        <v>0.9128573646505646</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>0.911504424778761</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>0.01805025124600332</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>0.893048273062481</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>0.8932038834951457</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>0.008696690437331071</v>
+      </c>
+      <c r="DE98" t="inlineStr">
+        <is>
+          <t>0.9574573710338873, 0.9635002139495079, 0.9559884869834178, 0.965912019932984, 0.9544849213849987, 0.9612939255949824, 0.9649669215568348</t>
+        </is>
+      </c>
+      <c r="DF98" t="n">
+        <v>0.9605148372052303</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>0.9612939255949824</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>0.004220120513062114</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 28.682610859801468, 'class_weight': None, 'coef0': 0.49963292619423594, 'degree': 2, 'gamma': 'auto'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 28.682610859801468, 'class_weight': None, 'coef0': 0.49963292619423594, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.9490909090909091</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.8391938250428816</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.8613636363636363</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.9056603773584905</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.9158249158249159</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.9493670886075949</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0.978341656021368</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.8987384930105694</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0.9265184066891186</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0.9800995024875622</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.9036697247706422</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0.9403341288782816</v>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>0.022585391998291016, 0.019678592681884766, 0.018721342086791992, 0.019030094146728516, 0.021327733993530273, 0.01943683624267578, 0.018349647521972656</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>0.01987566266741072</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0.01943683624267578</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.00141717595152812</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>0.015089035034179688, 0.013850927352905273, 0.014113426208496094, 0.012748003005981445, 0.013571023941040039, 0.01359868049621582, 0.014022111892700195</t>
+        </is>
+      </c>
+      <c r="AD99" t="n">
+        <v>0.01385617256164551</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0.01385092735290527</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0.0006534900100340104</v>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.8301886792452831, 0.9056603773584906, 0.9056603773584906, 0.9245283018867925, 0.8867924528301887, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>0.9025641025641026, 0.8617216117216118, 0.9130036630036631, 0.9358974358974359, 0.9258241758241759, 0.8772893772893773, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="AI99" t="n">
+        <v>0.9056253270538986</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0.9130036630036631</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0.02513740944440836</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0.8897873614854748</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0.02746839050685379</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.742857142857143, 0.8387096774193549, 0.8484848484848484, 0.8666666666666666, 0.7999999999999999, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8732394366197183, 0.9333333333333333, 0.9315068493150686, 0.9473684210526315, 0.9210526315789475, 0.9166666666666666</t>
+        </is>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0.9202980367836122</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>0.9210526315789475</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>0.02157555566799157</v>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>0.8712241653418124, 0.8080482897384307, 0.886021505376344, 0.8899958488999584, 0.9070175438596491, 0.8605263157894737, 0.8700980392156863</t>
+        </is>
+      </c>
+      <c r="AU99" t="n">
+        <v>0.8704188154601934</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0.8712241653418124</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0.02916668012293056</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0.8205395941367748</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0.03725033493668153</v>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.6190476190476191, 0.7647058823529411, 0.7368421052631579, 0.8125, 0.75, 0.7</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.96875, 0.9722222222222222, 1.0, 0.972972972972973, 0.9459459459459459, 1.0</t>
+        </is>
+      </c>
+      <c r="BC99" t="n">
+        <v>0.9759028160813875</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0.01753394670277403</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>0.7314196731324109</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>0.0556785411538445</v>
+      </c>
+      <c r="BI99" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.9285714285714286, 0.9285714285714286, 1.0, 0.9285714285714286, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ99" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7948717948717948, 0.8974358974358975, 0.8717948717948718, 0.9230769230769231, 0.8974358974358975, 0.8461538461538461</t>
+        </is>
+      </c>
+      <c r="BK99" t="n">
+        <v>0.8717948717948717</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>0.03876558697530539</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>0.9394557823129251</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0.04551218689436119</v>
+      </c>
+      <c r="BQ99" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.924908424908425, 0.978021978021978, 0.9505494505494506, 0.978021978021978, 0.9542124542124543, 0.9926739926739927</t>
+        </is>
+      </c>
+      <c r="BR99" t="n">
+        <v>0.9646781789638933</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>0.02112677052662096</v>
+      </c>
+      <c r="BU99" t="inlineStr">
+        <is>
+          <t>0.9119496855345912, 0.9216300940438872, 0.896551724137931, 0.9059561128526645, 0.9059561128526645, 0.9122257053291536, 0.9090909090909091</t>
+        </is>
+      </c>
+      <c r="BV99" t="inlineStr">
+        <is>
+          <t>0.924908424908425, 0.9315987933634993, 0.9182503770739066, 0.9171694318753143, 0.9171694318753143, 0.9289341377576672, 0.9193061840120664</t>
+        </is>
+      </c>
+      <c r="BW99" t="n">
+        <v>0.9224766829808848</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>0.9193061840120664</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>0.00554298195603807</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>0.9090514776916859</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>0.007092298437079058</v>
+      </c>
+      <c r="CC99" t="inlineStr">
+        <is>
+          <t>0.8510638297872339, 0.8663101604278074, 0.83248730964467, 0.8421052631578947, 0.8421052631578947, 0.8541666666666666, 0.8465608465608465</t>
+        </is>
+      </c>
+      <c r="CD99" t="inlineStr">
+        <is>
+          <t>0.9375, 0.9445676274944568, 0.9251700680272109, 0.9330357142857143, 0.9330357142857143, 0.937219730941704, 0.9354120267260579</t>
+        </is>
+      </c>
+      <c r="CE99" t="n">
+        <v>0.9351344116801227</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0.9354120267260579</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0.005439332957729684</v>
+      </c>
+      <c r="CH99" t="inlineStr">
+        <is>
+          <t>0.894281914893617, 0.9054388939611321, 0.8788286888359405, 0.8875704887218046, 0.8875704887218046, 0.8956931988041853, 0.8909864366434522</t>
+        </is>
+      </c>
+      <c r="CI99" t="n">
+        <v>0.891481444368848</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>0.8909864366434522</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0.007665510075981717</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0.8478284770575735</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0.009961937808863407</v>
+      </c>
+      <c r="CO99" t="inlineStr">
+        <is>
+          <t>0.7692307692307693, 0.7941176470588235, 0.7321428571428571, 0.7619047619047619, 0.7619047619047619, 0.7663551401869159, 0.7692307692307693</t>
+        </is>
+      </c>
+      <c r="CP99" t="inlineStr">
+        <is>
+          <t>0.9813084112149533, 0.9815668202764977, 0.9855072463768116, 0.9766355140186916, 0.9766355140186916, 0.9858490566037735, 0.9767441860465116</t>
+        </is>
+      </c>
+      <c r="CQ99" t="n">
+        <v>0.9806066783651329</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>0.9813084112149533</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>0.003767749183357525</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>0.764983815237094</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>0.7663551401869159</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>0.01683628561249153</v>
+      </c>
+      <c r="CW99" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9529411764705882, 0.9647058823529412, 0.9411764705882353, 0.9411764705882353, 0.9647058823529412, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX99" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9102564102564102, 0.8717948717948718, 0.8931623931623932, 0.8931623931623932, 0.8931623931623932, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="CY99" t="n">
+        <v>0.8937728937728939</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>0.8931623931623932</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>0.01057418075438874</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>0.9511804721888756</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>0.009788147472095811</v>
+      </c>
+      <c r="DE99" t="inlineStr">
+        <is>
+          <t>0.9718152218152217, 0.9776772247360482, 0.969683257918552, 0.9755656108597285, 0.9685268979386626, 0.9729512317747612, 0.966817496229261</t>
+        </is>
+      </c>
+      <c r="DF99" t="n">
+        <v>0.971862420181748</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>0.9718152218152217</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>0.003586463161526487</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH99"/>
+  <dimension ref="A1:DH105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39208,6 +39208,2346 @@
       </c>
       <c r="DH99" t="n">
         <v>0.003586463161526487</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LogisticRegression_splashing_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.15947545233607524, 'class_weight': None, 'penalty': 'l2'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.15947545233607524, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.8604651162790697</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.8131868131868132</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.8927469135802469</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.7625256099832372</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.7743055555555556</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.711864406779661</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.8249158249158249</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.9430379746835443</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.7760416666666666</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.8514285714285714</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0.9124751984126984</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0.8191569086651054</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0.8451636904761904</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0.6906474820143885</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>0.025205612182617188, 0.02387094497680664, 0.023152828216552734, 0.022998571395874023, 0.022031307220458984, 0.02233409881591797, 0.02214360237121582</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>0.02310528073992048</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.02299857139587402</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.001047735483569548</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>0.018663406372070312, 0.014111042022705078, 0.015102386474609375, 0.015038013458251953, 0.016478776931762695, 0.01497507095336914, 0.01401066780090332</t>
+        </is>
+      </c>
+      <c r="AD100" t="n">
+        <v>0.01548276628766741</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.01503801345825195</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0.001500355119744491</v>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.8301886792452831, 0.8113207547169812, 0.8113207547169812, 0.7547169811320755, 0.7358490566037735</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.8158730158730159, 0.8560371517027863, 0.8413312693498451, 0.818111455108359, 0.7972136222910217, 0.7244582043343653</t>
+        </is>
+      </c>
+      <c r="AI100" t="n">
+        <v>0.8245459587343709</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0.818111455108359</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0.05482170740612071</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0.8088249975042426</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0.05694948286674879</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8253968253968255, 0.8524590163934426, 0.8333333333333333, 0.84375, 0.7719298245614036, 0.787878787878788</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7441860465116279, 0.7999999999999999, 0.782608695652174, 0.761904761904762, 0.7346938775510204, 0.6500000000000001</t>
+        </is>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0.7668757462464068</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>0.761904761904762</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>0.06858607481606634</v>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>0.918796992481203, 0.7847914359542267, 0.8262295081967213, 0.8079710144927537, 0.8028273809523809, 0.753311851056212, 0.718939393939394</t>
+        </is>
+      </c>
+      <c r="AU100" t="n">
+        <v>0.8018382252961275</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0.8028273809523809</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0.05834686391288818</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0.8368007043458479</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0.05110926623786245</v>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.9285714285714286, 0.9629629629629629, 0.9615384615384616, 0.9, 0.9565217391304348, 0.8125</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.64, 0.6923076923076923, 0.6666666666666666, 0.6956521739130435, 0.6, 0.6190476190476191</t>
+        </is>
+      </c>
+      <c r="BC100" t="n">
+        <v>0.6869158562914693</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0.09107810481693945</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>0.9235645335800615</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>0.04981153692023844</v>
+      </c>
+      <c r="BI100" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.7428571428571429, 0.7647058823529411, 0.7352941176470589, 0.7941176470588235, 0.6470588235294118, 0.7647058823529411</t>
+        </is>
+      </c>
+      <c r="BJ100" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8888888888888888, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.6842105263157895</t>
+        </is>
+      </c>
+      <c r="BK100" t="n">
+        <v>0.8788638262322472</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>0.08756401101589893</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>0.7702280912364946</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0.08243847035055155</v>
+      </c>
+      <c r="BQ100" t="inlineStr">
+        <is>
+          <t>0.9654135338345865, 0.8746031746031746, 0.9427244582043344, 0.869969040247678, 0.9334365325077401, 0.826625386996904, 0.8498452012383901</t>
+        </is>
+      </c>
+      <c r="BR100" t="n">
+        <v>0.8946596182332581</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>0.8746031746031746</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>0.04850459279855573</v>
+      </c>
+      <c r="BU100" t="inlineStr">
+        <is>
+          <t>0.8176100628930818, 0.8181818181818182, 0.8181818181818182, 0.8307210031347962, 0.8213166144200627, 0.8150470219435737, 0.8495297805642633</t>
+        </is>
+      </c>
+      <c r="BV100" t="inlineStr">
+        <is>
+          <t>0.8327217785452191, 0.8390671801454856, 0.8392473580204485, 0.8469585015894836, 0.8376793538963828, 0.8368201735544291, 0.857526419795515</t>
+        </is>
+      </c>
+      <c r="BW100" t="n">
+        <v>0.8414315379352805</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>0.8390671801454856</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>0.007663986785477481</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>0.8243697313313449</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>0.0112876343201273</v>
+      </c>
+      <c r="CC100" t="inlineStr">
+        <is>
+          <t>0.8465608465608465, 0.8440860215053763, 0.8449197860962567, 0.8578947368421053, 0.8496042216358839, 0.841823056300268, 0.876923076923077</t>
+        </is>
+      </c>
+      <c r="CD100" t="inlineStr">
+        <is>
+          <t>0.7751937984496124, 0.7819548872180451, 0.7803030303030304, 0.7906976744186046, 0.7799227799227799, 0.7773584905660378, 0.8064516129032259</t>
+        </is>
+      </c>
+      <c r="CE100" t="n">
+        <v>0.7845546105401909</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0.7803030303030304</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0.01002078727098015</v>
+      </c>
+      <c r="CH100" t="inlineStr">
+        <is>
+          <t>0.8108773225052295, 0.8130204543617107, 0.8126114081996436, 0.8242962056303549, 0.8147635007793319, 0.8095907734331529, 0.8416873449131514</t>
+        </is>
+      </c>
+      <c r="CI100" t="n">
+        <v>0.818121001403225</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>0.8130204543617107</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0.01059909278263525</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0.8516873922662592</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0.01138218176608377</v>
+      </c>
+      <c r="CO100" t="inlineStr">
+        <is>
+          <t>0.9248554913294798, 0.9401197604790419, 0.9404761904761905, 0.9367816091954023, 0.930635838150289, 0.9401197604790419, 0.9293478260869565</t>
+        </is>
+      </c>
+      <c r="CP100" t="inlineStr">
+        <is>
+          <t>0.6896551724137931, 0.6842105263157895, 0.6821192052980133, 0.7034482758620689, 0.6917808219178082, 0.6776315789473685, 0.7407407407407407</t>
+        </is>
+      </c>
+      <c r="CQ100" t="n">
+        <v>0.6956551887850831</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>0.01994099788301986</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>0.934619496599486</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>0.9367816091954023</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>0.0058367951465262</v>
+      </c>
+      <c r="CW100" t="inlineStr">
+        <is>
+          <t>0.7804878048780488, 0.7658536585365854, 0.7669902912621359, 0.7912621359223301, 0.7815533980582524, 0.7621359223300971, 0.8300970873786407</t>
+        </is>
+      </c>
+      <c r="CX100" t="inlineStr">
+        <is>
+          <t>0.8849557522123894, 0.9122807017543859, 0.911504424778761, 0.9026548672566371, 0.8938053097345132, 0.911504424778761, 0.8849557522123894</t>
+        </is>
+      </c>
+      <c r="CY100" t="n">
+        <v>0.9002373189611197</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>0.9026548672566371</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>0.01142182286653244</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>0.7826257569094415</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>0.02164466097906357</v>
+      </c>
+      <c r="DE100" t="inlineStr">
+        <is>
+          <t>0.8992661342542628, 0.9124946512623021, 0.9023326746284045, 0.9098934616375978, 0.9041799123636052, 0.9214709167454249, 0.9104519288598677</t>
+        </is>
+      </c>
+      <c r="DF100" t="n">
+        <v>0.9085842399644949</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>0.9098934616375978</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.006885464430521382</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LogisticRegression_no_fragmentation_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'liblinear', 'C': 377.1313111077982, 'class_weight': None, 'penalty': 'l1'}, 'base_estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'liblinear', 'C': 377.1313111077982, 'class_weight': None, 'penalty': 'l1'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.9581818181818181</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.8161764705882353</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.8590909090909091</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.8316498316498316</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.6355140186915887</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.8607594936708861</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.7311827956989247</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.9419927999070956</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.8043168880455408</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0.8409302055510394</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0.9421052631578948</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0.8774509803921569</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>0.024035215377807617, 0.020569324493408203, 0.02002739906311035, 0.021613359451293945, 0.021079540252685547, 0.021424055099487305, 0.02055525779724121</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>0.02132916450500488</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0.02107954025268555</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.001215711213782499</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>0.013138532638549805, 0.012949466705322266, 0.01444697380065918, 0.012259721755981445, 0.01354074478149414, 0.013348817825317383, 0.012997865676879883</t>
+        </is>
+      </c>
+      <c r="AD101" t="n">
+        <v>0.01324030331202916</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0.0131385326385498</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0.000617986770671858</v>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>0.8518518518518519, 0.7358490566037735, 0.8679245283018868, 0.7924528301886793, 0.7924528301886793, 0.8490566037735849, 0.9056603773584906</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>0.8564102564102565, 0.728937728937729, 0.8873626373626373, 0.7902930402930403, 0.8131868131868132, 0.8287545787545787, 0.9358974358974359</t>
+        </is>
+      </c>
+      <c r="AI101" t="n">
+        <v>0.8344060701203558</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0.8287545787545787</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0.06226763223318901</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0.8278925826095638</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0.05299098539693286</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>0.7647058823529413, 0.588235294117647, 0.7878787878787878, 0.6666666666666667, 0.6857142857142857, 0.7333333333333334, 0.8484848484848484</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>0.8918918918918919, 0.8055555555555556, 0.9041095890410958, 0.8493150684931507, 0.8450704225352113, 0.8947368421052632, 0.9315068493150686</t>
+        </is>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0.8745980312767481</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0.0398069740257037</v>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>0.8282988871224166, 0.6968954248366013, 0.8459941884599418, 0.7579908675799087, 0.7653923541247485, 0.8140350877192983, 0.8899958488999584</t>
+        </is>
+      </c>
+      <c r="AU101" t="n">
+        <v>0.7998003798204104</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>0.8140350877192983</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0.05952821627813664</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0.725002728364073</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0.07973078017929812</v>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>0.6842105263157895, 0.5, 0.6842105263157895, 0.5789473684210527, 0.5714285714285714, 0.6875, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>0.9428571428571428, 0.8787878787878788, 0.9705882352941176, 0.9117647058823529, 0.9375, 0.918918918918919, 1.0</t>
+        </is>
+      </c>
+      <c r="BC101" t="n">
+        <v>0.9372024116772016</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0.03680806491108783</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>0.634734156820623</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>0.0787211584684933</v>
+      </c>
+      <c r="BI101" t="inlineStr">
+        <is>
+          <t>0.8666666666666667, 0.7142857142857143, 0.9285714285714286, 0.7857142857142857, 0.8571428571428571, 0.7857142857142857, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ101" t="inlineStr">
+        <is>
+          <t>0.8461538461538461, 0.7435897435897436, 0.8461538461538461, 0.7948717948717948, 0.7692307692307693, 0.8717948717948718, 0.8717948717948718</t>
+        </is>
+      </c>
+      <c r="BK101" t="n">
+        <v>0.8205128205128206</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>0.04747795383448981</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>0.8482993197278911</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0.08917534480638879</v>
+      </c>
+      <c r="BQ101" t="inlineStr">
+        <is>
+          <t>0.9521367521367521, 0.8974358974358975, 0.9670329670329672, 0.9304029304029304, 0.9175824175824175, 0.9304029304029304, 0.9981684981684982</t>
+        </is>
+      </c>
+      <c r="BR101" t="n">
+        <v>0.941880341880342</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>0.9304029304029304</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>0.03101926764665284</v>
+      </c>
+      <c r="BU101" t="inlineStr">
+        <is>
+          <t>0.8301886792452831, 0.8652037617554859, 0.8369905956112853, 0.8495297805642633, 0.8495297805642633, 0.8463949843260188, 0.8369905956112853</t>
+        </is>
+      </c>
+      <c r="BV101" t="inlineStr">
+        <is>
+          <t>0.8350122100122099, 0.8781548516842634, 0.8514328808446455, 0.8599798893916542, 0.8562342885872298, 0.857843137254902, 0.8514328808446455</t>
+        </is>
+      </c>
+      <c r="BW101" t="n">
+        <v>0.8557271626599355</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>0.8562342885872298</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>0.01190325538086766</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>0.8449754539539835</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0.8463949843260188</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>0.0106827492216419</v>
+      </c>
+      <c r="CC101" t="inlineStr">
+        <is>
+          <t>0.7244897959183674, 0.7817258883248731, 0.7425742574257426, 0.7575757575757577, 0.7551020408163265, 0.7537688442211056, 0.7425742574257426</t>
+        </is>
+      </c>
+      <c r="CD101" t="inlineStr">
+        <is>
+          <t>0.8772727272727272, 0.9024943310657597, 0.8807339449541284, 0.8909090909090909, 0.8914027149321265, 0.8883826879271071, 0.8807339449541284</t>
+        </is>
+      </c>
+      <c r="CE101" t="n">
+        <v>0.8874184917164384</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0.8883826879271071</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0.00800510364667156</v>
+      </c>
+      <c r="CH101" t="inlineStr">
+        <is>
+          <t>0.8008812615955473, 0.8421101096953164, 0.8116541011899354, 0.8242424242424242, 0.8232523778742264, 0.8210757660741064, 0.8116541011899354</t>
+        </is>
+      </c>
+      <c r="CI101" t="n">
+        <v>0.8192671631230704</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>0.8210757660741064</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0.01206923604832221</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0.7511158345297021</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>0.7537688442211056</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0.01628538920568498</v>
+      </c>
+      <c r="CO101" t="inlineStr">
+        <is>
+          <t>0.6339285714285714, 0.6875, 0.6410256410256411, 0.6637168141592921, 0.6666666666666666, 0.6578947368421053, 0.6410256410256411</t>
+        </is>
+      </c>
+      <c r="CP101" t="inlineStr">
+        <is>
+          <t>0.9368932038834952, 0.961352657004831, 0.9504950495049505, 0.9514563106796117, 0.9471153846153846, 0.9512195121951219, 0.9504950495049505</t>
+        </is>
+      </c>
+      <c r="CQ101" t="n">
+        <v>0.9498610239126207</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>0.9504950495049505</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>0.006686392682908714</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>0.6559654387354168</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>0.01734016591389645</v>
+      </c>
+      <c r="CW101" t="inlineStr">
+        <is>
+          <t>0.8452380952380952, 0.9058823529411765, 0.8823529411764706, 0.8823529411764706, 0.8705882352941177, 0.8823529411764706, 0.8823529411764706</t>
+        </is>
+      </c>
+      <c r="CX101" t="inlineStr">
+        <is>
+          <t>0.8247863247863247, 0.8504273504273504, 0.8205128205128205, 0.8376068376068376, 0.8418803418803419, 0.8333333333333334, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="CY101" t="n">
+        <v>0.8327228327228327</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>0.01057418075438876</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>0.8787314925970389</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>0.01680879481881183</v>
+      </c>
+      <c r="DE101" t="inlineStr">
+        <is>
+          <t>0.9433760683760684, 0.9537456008044243, 0.9415786827551533, 0.9482151835093011, 0.945550527903469, 0.9516339869281046, 0.9359477124183007</t>
+        </is>
+      </c>
+      <c r="DF101" t="n">
+        <v>0.9457211089564032</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>0.9455505279034691</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>0.005654104591804274</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_splashing_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 1, 'weights': 'distance', 'p': 1}, 'base_estimator_params': {'n_neighbors': 1, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.8332996564962618</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.9966329966329966</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.9947916666666666</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.9973890339425587</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0.9973958333333333</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.996324848724834</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0.9973958333333333</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0.9905660377358491</v>
+      </c>
+      <c r="W102" t="n">
+        <v>1</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0.9952606635071091</v>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>0.026993751525878906, 0.020168304443359375, 0.019930124282836914, 0.02133655548095703, 0.020959138870239258, 0.021331071853637695, 0.02089977264404297</t>
+        </is>
+      </c>
+      <c r="Z102" t="n">
+        <v>0.02165981701442174</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.02095913887023926</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.002234422033747832</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>0.02968573570251465, 0.015359640121459961, 0.015287637710571289, 0.01620316505432129, 0.015335321426391602, 0.016111373901367188, 0.015524625778198242</t>
+        </is>
+      </c>
+      <c r="AD102" t="n">
+        <v>0.01764392852783203</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0.01552462577819824</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0.004928355766586994</v>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.8113207547169812, 0.9245283018867925, 0.9245283018867925, 0.9056603773584906, 0.9056603773584906, 0.8867924528301887</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8166666666666667, 0.9295665634674922, 0.9295665634674922, 0.891640866873065, 0.914860681114551, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AI102" t="n">
+        <v>0.8934247383163791</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0.03633294461637566</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0.8977737845662374</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0.9056603773584906</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0.03768907413827519</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>0.945945945945946, 0.8484848484848486, 0.9393939393939394, 0.9393939393939394, 0.9275362318840579, 0.923076923076923, 0.9117647058823528</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>0.8823529411764706, 0.7499999999999999, 0.9, 0.9, 0.8648648648648649, 0.8780487804878049, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0.8596245499552906</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0.04850377633896862</v>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>0.9141494435612083, 0.7992424242424243, 0.9196969696969697, 0.9196969696969697, 0.8962005483744614, 0.900562851782364, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="AU102" t="n">
+        <v>0.8894977416963601</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0.9005628517823639</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0.03946590322880562</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0.9193709334374296</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0.9275362318840579</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0.03087109378494328</v>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9032258064516129, 0.96875, 0.96875, 0.9142857142857143, 0.967741935483871, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>1.0, 0.6818181818181818, 0.8571428571428571, 0.8571428571428571, 0.8888888888888888, 0.8181818181818182, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BC102" t="n">
+        <v>0.8493256951903568</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0.08739978033436586</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>0.9331362942199213</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>0.03097341543755244</v>
+      </c>
+      <c r="BI102" t="inlineStr">
+        <is>
+          <t>1.0, 0.8, 0.9117647058823529, 0.9117647058823529, 0.9411764705882353, 0.8823529411764706, 0.9117647058823529</t>
+        </is>
+      </c>
+      <c r="BJ102" t="inlineStr">
+        <is>
+          <t>0.7894736842105263, 0.8333333333333334, 0.9473684210526315, 0.9473684210526315, 0.8421052631578947, 0.9473684210526315, 0.8421052631578947</t>
+        </is>
+      </c>
+      <c r="BK102" t="n">
+        <v>0.8784461152882205</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>0.06192555940153299</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>0.9084033613445379</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0.0559691623709133</v>
+      </c>
+      <c r="BQ102" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8166666666666667, 0.9295665634674923, 0.9295665634674923, 0.891640866873065, 0.9148606811145512, 0.8769349845201238</t>
+        </is>
+      </c>
+      <c r="BR102" t="n">
+        <v>0.8934247383163791</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>0.03633294461637571</v>
+      </c>
+      <c r="BU102" t="inlineStr">
+        <is>
+          <t>0.9968553459119497, 1.0, 0.9968652037617555, 0.9968652037617555, 0.9968652037617555, 1.0, 0.9968652037617555</t>
+        </is>
+      </c>
+      <c r="BV102" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.9975728155339806, 0.995575221238938, 0.995575221238938, 1.0, 0.9975728155339806</t>
+        </is>
+      </c>
+      <c r="BW102" t="n">
+        <v>0.9974101849692536</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>0.9975728155339806</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>0.00183491754827791</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>0.9977594515655674</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0.9968652037617555</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>0.001417051170840857</v>
+      </c>
+      <c r="CC102" t="inlineStr">
+        <is>
+          <t>0.9975669099756691, 1.0, 0.9975669099756691, 0.9975786924939467, 0.9975786924939467, 1.0, 0.9975669099756691</t>
+        </is>
+      </c>
+      <c r="CD102" t="inlineStr">
+        <is>
+          <t>0.9955555555555555, 1.0, 0.9955947136563876, 0.9955555555555555, 0.9955555555555555, 1.0, 0.9955947136563876</t>
+        </is>
+      </c>
+      <c r="CE102" t="n">
+        <v>0.996836584854206</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0.9955947136563876</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0.002000785099662565</v>
+      </c>
+      <c r="CH102" t="inlineStr">
+        <is>
+          <t>0.9965612327656124, 1.0, 0.9965808118160284, 0.9965671240247511, 0.9965671240247511, 1.0, 0.9965808118160284</t>
+        </is>
+      </c>
+      <c r="CI102" t="n">
+        <v>0.9975510149210244</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>0.9965808118160284</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0.001548888784658625</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0.9982654449878429</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>0.9975786924939467</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>0.001097039760045307</v>
+      </c>
+      <c r="CO102" t="inlineStr">
+        <is>
+          <t>0.9951456310679612, 1.0, 1.0, 0.9951690821256038, 0.9951690821256038, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CP102" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 0.9912280701754386, 1.0, 1.0, 1.0, 0.9912280701754386</t>
+        </is>
+      </c>
+      <c r="CQ102" t="n">
+        <v>0.9974937343358395</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>0.003962753960110764</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>0.997926256474167</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>0.002394563702285534</v>
+      </c>
+      <c r="CW102" t="inlineStr">
+        <is>
+          <t>1.0, 1.0, 0.9951456310679612, 1.0, 1.0, 1.0, 0.9951456310679612</t>
+        </is>
+      </c>
+      <c r="CX102" t="inlineStr">
+        <is>
+          <t>0.9911504424778761, 1.0, 1.0, 0.9911504424778761, 0.9911504424778761, 1.0, 1.0</t>
+        </is>
+      </c>
+      <c r="CY102" t="n">
+        <v>0.9962073324905182</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>0.004379395215091984</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>0.998613037447989</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>0.002192980346857405</v>
+      </c>
+      <c r="DE102" t="inlineStr">
+        <is>
+          <t>0.995575221238938, 1.0, 0.9975728155339806, 0.995575221238938, 0.995575221238938, 1.0, 0.9975728155339806</t>
+        </is>
+      </c>
+      <c r="DF102" t="n">
+        <v>0.9974101849692536</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>0.9975728155339806</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>0.00183491754827791</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>KNeighborsClassifier_no_fragmentation_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'base_estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.9027272727272728</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.8206911540969355</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.8363636363636364</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.897196261682243</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.9427609427609428</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.8369565217391305</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.9746835443037974</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.9005847953216375</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0.9915515038903728</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.9301978350130646</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0.9529381024271281</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0.9902439024390244</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0.9311926605504587</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0.9598108747044918</v>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>0.024509429931640625, 0.020848751068115234, 0.020676612854003906, 0.01972341537475586, 0.019952058792114258, 0.021252870559692383, 0.020036697387695312</t>
+        </is>
+      </c>
+      <c r="Z103" t="n">
+        <v>0.02099997656685965</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0.02067661285400391</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.001519553433003547</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>0.018678665161132812, 0.015993595123291016, 0.015009641647338867, 0.016558170318603516, 0.015002727508544922, 0.015459299087524414, 0.017819881439208984</t>
+        </is>
+      </c>
+      <c r="AD103" t="n">
+        <v>0.01636028289794922</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0.01599359512329102</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0.001317893547891996</v>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>0.8703703703703703, 0.7358490566037735, 0.9245283018867925, 0.8867924528301887, 0.8867924528301887, 0.8867924528301887, 0.8490566037735849</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>0.8487179487179488, 0.728937728937729, 0.9029304029304028, 0.9001831501831502, 0.8315018315018314, 0.8543956043956045, 0.8745421245421245</t>
+        </is>
+      </c>
+      <c r="AI103" t="n">
+        <v>0.8487441130298272</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0.8543956043956045</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.05468150893411447</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0.8628830987321555</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0.05593361086531986</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>0.7741935483870969, 0.588235294117647, 0.8571428571428571, 0.8125000000000001, 0.7692307692307692, 0.7857142857142857, 0.7647058823529412</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>0.9090909090909091, 0.8055555555555556, 0.9487179487179487, 0.9189189189189189, 0.9249999999999999, 0.9230769230769231, 0.8888888888888888</t>
+        </is>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0.9027498777498779</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0.9189189189189189</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0.04303126788446314</v>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>0.841642228739003, 0.6968954248366013, 0.9029304029304028, 0.8657094594594594, 0.8471153846153845, 0.8543956043956045, 0.826797385620915</t>
+        </is>
+      </c>
+      <c r="AU103" t="n">
+        <v>0.8336408415139099</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0.8471153846153845</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0.06006178621176272</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0.7645318052779425</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0.7741935483870969</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0.07793987774662568</v>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>0.75, 0.5, 0.8571428571428571, 0.7222222222222222, 0.8333333333333334, 0.7857142857142857, 0.65</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>0.9210526315789473, 0.8787878787878788, 0.9487179487179487, 0.9714285714285714, 0.9024390243902439, 0.9230769230769231, 0.9696969696969697</t>
+        </is>
+      </c>
+      <c r="BC103" t="n">
+        <v>0.9307428496682119</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0.03195744467231082</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>0.7283446712018141</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>0.1131929317366905</v>
+      </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>0.8, 0.7142857142857143, 0.8571428571428571, 0.9285714285714286, 0.7142857142857143, 0.7857142857142857, 0.9285714285714286</t>
+        </is>
+      </c>
+      <c r="BJ103" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.7435897435897436, 0.9487179487179487, 0.8717948717948718, 0.9487179487179487, 0.9230769230769231, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK103" t="n">
+        <v>0.879120879120879</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0.06950060791578855</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>0.8183673469387756</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0.08354893669574988</v>
+      </c>
+      <c r="BQ103" t="inlineStr">
+        <is>
+          <t>0.9034188034188034, 0.7701465201465201, 0.934981684981685, 0.9560439560439561, 0.9578754578754579, 0.8946886446886447, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="BR103" t="n">
+        <v>0.9094104308390023</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0.934981684981685</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>0.06137656826844985</v>
+      </c>
+      <c r="BU103" t="inlineStr">
+        <is>
+          <t>0.9433962264150944, 0.9404388714733543, 0.9341692789968652, 0.9373040752351097, 0.9373040752351097, 0.9435736677115988, 0.9467084639498433</t>
+        </is>
+      </c>
+      <c r="BV103" t="inlineStr">
+        <is>
+          <t>0.9424603174603174, 0.944419306184012, 0.9326546003016591, 0.9385369532428356, 0.9235545500251383, 0.9465560583207642, 0.944947209653092</t>
+        </is>
+      </c>
+      <c r="BW103" t="n">
+        <v>0.9390184278839743</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>0.9424603174603174</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>0.007679695435697343</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>0.9404135227167106</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0.9404388714733543</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>0.004085477281850636</v>
+      </c>
+      <c r="CC103" t="inlineStr">
+        <is>
+          <t>0.8977272727272727, 0.8950276243093922, 0.8826815642458101, 0.8888888888888888, 0.8837209302325582, 0.9, 0.903954802259887</t>
+        </is>
+      </c>
+      <c r="CD103" t="inlineStr">
+        <is>
+          <t>0.9608695652173912, 0.9584245076586433, 0.954248366013072, 0.9563318777292577, 0.9570815450643777, 0.9606986899563319, 0.963123644251627</t>
+        </is>
+      </c>
+      <c r="CE103" t="n">
+        <v>0.9586825994129572</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0.9584245076586433</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0.002838224405392204</v>
+      </c>
+      <c r="CH103" t="inlineStr">
+        <is>
+          <t>0.9292984189723319, 0.9267260659840177, 0.918464965129441, 0.9226103833090733, 0.9204012376484679, 0.9303493449781659, 0.933539223255757</t>
+        </is>
+      </c>
+      <c r="CI103" t="n">
+        <v>0.9259128056110363</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>0.9267260659840177</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0.005164751414568978</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0.8931430118091156</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0.8950276243093922</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0.007604466548574816</v>
+      </c>
+      <c r="CO103" t="inlineStr">
+        <is>
+          <t>0.8586956521739131, 0.84375, 0.8404255319148937, 0.8421052631578947, 0.8735632183908046, 0.8526315789473684, 0.8695652173913043</t>
+        </is>
+      </c>
+      <c r="CP103" t="inlineStr">
+        <is>
+          <t>0.9778761061946902, 0.9820627802690582, 0.9733333333333334, 0.9776785714285714, 0.9612068965517241, 0.9821428571428571, 0.9779735682819384</t>
+        </is>
+      </c>
+      <c r="CQ103" t="n">
+        <v>0.9760391590288817</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>0.9778761061946902</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>0.006661838371995908</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>0.8543909231394541</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>0.8526315789473684</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>0.01241347731753288</v>
+      </c>
+      <c r="CW103" t="inlineStr">
+        <is>
+          <t>0.9404761904761905, 0.9529411764705882, 0.9294117647058824, 0.9411764705882353, 0.8941176470588236, 0.9529411764705882, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX103" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.9358974358974359, 0.9358974358974359, 0.9358974358974359, 0.9529914529914529, 0.9401709401709402, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="CY103" t="n">
+        <v>0.9420024420024421</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>0.9401709401709402</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>0.006402984421063173</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>0.9360344137655063</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>0.01868980982523908</v>
+      </c>
+      <c r="DE103" t="inlineStr">
+        <is>
+          <t>0.9907407407407407, 0.9920563097033686, 0.9874057315233786, 0.9886877828054299, 0.9866767219708397, 0.9913021618903971, 0.9913021618903972</t>
+        </is>
+      </c>
+      <c r="DF103" t="n">
+        <v>0.9897388015035073</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>0.9907407407407407</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>0.001970754199009418</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SVC_splashing_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 26.972626232440984, 'class_weight': 'balanced', 'coef0': 0.08285683438096408, 'degree': 2, 'gamma': 'auto'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 26.972626232440984, 'class_weight': 'balanced', 'coef0': 0.08285683438096408, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.8896604938271604</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.8068924539512775</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.7450980392156864</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.9158249158249159</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.9417989417989417</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.9343832020997376</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0.9550843253968253</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.9085061550404792</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0.9111607142857143</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0.8952380952380953</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0.8826291079812207</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>0.04044198989868164, 0.03241443634033203, 0.05623126029968262, 0.03369283676147461, 0.03164029121398926, 0.03268027305603027, 0.03355598449707031</t>
+        </is>
+      </c>
+      <c r="Z104" t="n">
+        <v>0.03723672458103725</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.03355598449707031</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.008215915583920414</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>0.018276453018188477, 0.014851808547973633, 0.015522956848144531, 0.014258384704589844, 0.01596808433532715, 0.0160367488861084, 0.015537023544311523</t>
+        </is>
+      </c>
+      <c r="AD104" t="n">
+        <v>0.01577877998352051</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0.01553702354431152</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0.001173244839837054</v>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>0.9259259259259259, 0.7924528301886793, 0.9056603773584906, 0.8679245283018868, 0.9056603773584906, 0.8679245283018868, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>0.9067669172932331, 0.8023809523809524, 0.914860681114551, 0.8738390092879257, 0.903250773993808, 0.8738390092879257, 0.8738390092879257</t>
+        </is>
+      </c>
+      <c r="AI104" t="n">
+        <v>0.8783966218066173</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0.8738390092879257</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.03503656796221832</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0.8762104422481781</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.04040426667887082</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>0.9444444444444445, 0.8307692307692307, 0.923076923076923, 0.8923076923076922, 0.9253731343283583, 0.8923076923076922, 0.8923076923076922</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7317073170731708, 0.8780487804878049, 0.8292682926829269, 0.8717948717948718, 0.8292682926829269, 0.8292682926829269</t>
+        </is>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0.836892105184788</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>0.8292682926829269</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0.0490683892365447</v>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>0.9166666666666667, 0.7812382739212007, 0.900562851782364, 0.8607879924953096, 0.898584003061615, 0.8607879924953096, 0.8607879924953096</t>
+        </is>
+      </c>
+      <c r="AU104" t="n">
+        <v>0.8684879675596822</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0.8607879924953096</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0.04148344676142891</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0.9000838299345764</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0.8923076923076922</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0.03406299620932701</v>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.9, 0.967741935483871, 0.9354838709677419, 0.9393939393939394, 0.9354838709677419, 0.9354838709677419</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>0.9411764705882353, 0.6521739130434783, 0.8181818181818182, 0.7727272727272727, 0.85, 0.7727272727272727, 0.7727272727272727</t>
+        </is>
+      </c>
+      <c r="BC104" t="n">
+        <v>0.7971020028564785</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0.08175446042143104</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0.9332152009571365</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>0.0190987884856617</v>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.7714285714285715, 0.8823529411764706, 0.8529411764705882, 0.9117647058823529, 0.8529411764705882, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ104" t="inlineStr">
+        <is>
+          <t>0.8421052631578947, 0.8333333333333334, 0.9473684210526315, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632</t>
+        </is>
+      </c>
+      <c r="BK104" t="n">
+        <v>0.8859649122807017</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0.03539961627023943</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>0.870828331332533</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>0.05703279119049408</v>
+      </c>
+      <c r="BQ104" t="inlineStr">
+        <is>
+          <t>0.981954887218045, 0.8682539682539683, 0.9489164086687307, 0.9272445820433437, 0.978328173374613, 0.9272445820433437, 0.9164086687306501</t>
+        </is>
+      </c>
+      <c r="BR104" t="n">
+        <v>0.9354787529046708</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>0.9272445820433437</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>0.03624345735842283</v>
+      </c>
+      <c r="BU104" t="inlineStr">
+        <is>
+          <t>0.889937106918239, 0.9153605015673981, 0.9184952978056427, 0.8996865203761756, 0.9090909090909091, 0.9153605015673981, 0.9059561128526645</t>
+        </is>
+      </c>
+      <c r="BV104" t="inlineStr">
+        <is>
+          <t>0.896762357004101, 0.9166238767650834, 0.9189148552281123, 0.9023541541369533, 0.9096357075350117, 0.9184852650571356, 0.9132013059541197</t>
+        </is>
+      </c>
+      <c r="BW104" t="n">
+        <v>0.9108539316686454</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>0.9132013059541197</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>0.0078769186780503</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>0.9076981357397752</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>0.009400737020573018</v>
+      </c>
+      <c r="CC104" t="inlineStr">
+        <is>
+          <t>0.9109414758269719, 0.9326683291770573, 0.9356435643564357, 0.92, 0.9280397022332506, 0.9326683291770576, 0.9242424242424243</t>
+        </is>
+      </c>
+      <c r="CD104" t="inlineStr">
+        <is>
+          <t>0.8559670781893004, 0.8860759493670887, 0.888888888888889, 0.8655462184873949, 0.8765957446808511, 0.8860759493670886, 0.8760330578512397</t>
+        </is>
+      </c>
+      <c r="CE104" t="n">
+        <v>0.8764546981188361</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0.8765957446808511</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0.01120383368166361</v>
+      </c>
+      <c r="CH104" t="inlineStr">
+        <is>
+          <t>0.8834542770081362, 0.909372139272073, 0.9122662266226623, 0.8927731092436975, 0.9023177234570509, 0.909372139272073, 0.9001377410468321</t>
+        </is>
+      </c>
+      <c r="CI104" t="n">
+        <v>0.9013847651317892</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>0.9023177234570509</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0.009592340674305954</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0.9263148321447426</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0.9280397022332506</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0.008028932810974334</v>
+      </c>
+      <c r="CO104" t="inlineStr">
+        <is>
+          <t>0.9521276595744681, 0.9540816326530612, 0.9545454545454546, 0.9484536082474226, 0.949238578680203, 0.958974358974359, 0.9631578947368421</t>
+        </is>
+      </c>
+      <c r="CP104" t="inlineStr">
+        <is>
+          <t>0.8, 0.8536585365853658, 0.859504132231405, 0.824, 0.8442622950819673, 0.8467741935483871, 0.8217054263565892</t>
+        </is>
+      </c>
+      <c r="CQ104" t="n">
+        <v>0.8357006548291021</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>0.8442622950819673</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>0.01961167471487764</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>0.9543684553445443</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>0.9540816326530612</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>0.004853634948724548</v>
+      </c>
+      <c r="CW104" t="inlineStr">
+        <is>
+          <t>0.8731707317073171, 0.9121951219512195, 0.9174757281553398, 0.8932038834951457, 0.9077669902912622, 0.9077669902912622, 0.8883495145631068</t>
+        </is>
+      </c>
+      <c r="CX104" t="inlineStr">
+        <is>
+          <t>0.9203539823008849, 0.9210526315789473, 0.9203539823008849, 0.911504424778761, 0.911504424778761, 0.9292035398230089, 0.9380530973451328</t>
+        </is>
+      </c>
+      <c r="CY104" t="n">
+        <v>0.9217180118437688</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>0.9203539823008849</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>0.008747789541350907</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>0.8999898514935218</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>0.9077669902912622</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>0.01452340120028887</v>
+      </c>
+      <c r="DE104" t="inlineStr">
+        <is>
+          <t>0.9524498165335635, 0.9647411210954215, 0.958866741128963, 0.9633774379242203, 0.9531961508720681, 0.967007474868975, 0.9659979379671794</t>
+        </is>
+      </c>
+      <c r="DF104" t="n">
+        <v>0.9608052400557702</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>0.9633774379242203</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>0.005593469511598041</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SVC_no_fragmentation_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 27.620566418088167, 'class_weight': 'balanced', 'coef0': 0.48744430071806377, 'degree': 2, 'gamma': 'auto'}, 'base_estimator_params': {'probability': True, 'kernel': 'poly', 'C': 27.620566418088167, 'class_weight': 'balanced', 'coef0': 0.48744430071806377, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.9190909090909092</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.8636363636363638</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.9292929292929293</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0.9693996051561956</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.9118881118881119</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0.9235861107885264</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0.966824644549763</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0.9357798165137615</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0.951048951048951</v>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>0.0368349552154541, 0.030502796173095703, 0.03272080421447754, 0.031003713607788086, 0.03106212615966797, 0.03137636184692383, 0.03338742256164551</t>
+        </is>
+      </c>
+      <c r="Z105" t="n">
+        <v>0.03241259711129325</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.03137636184692383</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.002040041146043053</v>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>0.014758110046386719, 0.013398408889770508, 0.013259649276733398, 0.012997627258300781, 0.014047861099243164, 0.015001535415649414, 0.012931108474731445</t>
+        </is>
+      </c>
+      <c r="AD105" t="n">
+        <v>0.01377061435154506</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0.01339840888977051</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0.0007809409662593594</v>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>0.8888888888888888, 0.7924528301886793, 0.9622641509433962, 0.9245283018867925, 0.9245283018867925, 0.9056603773584906, 0.9245283018867925</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>0.9025641025641026, 0.7902930402930403, 0.9514652014652014, 0.9487179487179487, 0.9029304029304028, 0.8901098901098901, 0.9487179487179487</t>
+        </is>
+      </c>
+      <c r="AI105" t="n">
+        <v>0.9049712192569336</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0.9029304029304028</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0.05260519533712055</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0.9032644504342617</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>0.9245283018867925</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0.04975515940651736</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>0.8235294117647058, 0.6666666666666667, 0.9285714285714286, 0.8750000000000001, 0.8571428571428571, 0.8275862068965518, 0.8750000000000001</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>0.9189189189189189, 0.8493150684931507, 0.9743589743589743, 0.945945945945946, 0.9487179487179487, 0.935064935064935, 0.945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0.9311811053494028</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>0.9459459459459461</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0.03679162098531152</v>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>0.8712241653418124, 0.7579908675799087, 0.9514652014652014, 0.910472972972973, 0.9029304029304028, 0.8813255709807435, 0.910472972972973</t>
+        </is>
+      </c>
+      <c r="AU105" t="n">
+        <v>0.8836974506062879</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0.9029304029304028</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0.05651748829472441</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0.8362137958631728</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0.07649300163910447</v>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>0.7368421052631579, 0.5789473684210527, 0.9285714285714286, 0.7777777777777778, 0.8571428571428571, 0.8, 0.7777777777777778</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.9117647058823529, 0.9743589743589743, 1.0, 0.9487179487179487, 0.9473684210526315, 1.0</t>
+        </is>
+      </c>
+      <c r="BC105" t="n">
+        <v>0.9648055173486398</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0.02924924047139258</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>0.7795799021362931</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0.1005114744739972</v>
+      </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.7857142857142857, 0.9285714285714286, 1.0, 0.8571428571428571, 0.8571428571428571, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ105" t="inlineStr">
+        <is>
+          <t>0.8717948717948718, 0.7948717948717948, 0.9743589743589743, 0.8974358974358975, 0.9487179487179487, 0.9230769230769231, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="BK105" t="n">
+        <v>0.9010989010989012</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0.05383493940182809</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>0.9088435374149659</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0.073789928117601</v>
+      </c>
+      <c r="BQ105" t="inlineStr">
+        <is>
+          <t>0.9743589743589743, 0.9029304029304029, 0.9725274725274725, 0.9560439560439561, 0.9358974358974359, 0.9542124542124542, 0.9835164835164835</t>
+        </is>
+      </c>
+      <c r="BR105" t="n">
+        <v>0.9542124542124543</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>0.9560439560439561</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>0.02554741077704686</v>
+      </c>
+      <c r="BU105" t="inlineStr">
+        <is>
+          <t>0.9119496855345912, 0.9247648902821317, 0.8996865203761756, 0.9028213166144201, 0.9184952978056427, 0.9090909090909091, 0.9059561128526645</t>
+        </is>
+      </c>
+      <c r="BV105" t="inlineStr">
+        <is>
+          <t>0.924908424908425, 0.9262443438914028, 0.9166415284062343, 0.9150326797385621, 0.9182252388134741, 0.9267973856209151, 0.91342383107089</t>
+        </is>
+      </c>
+      <c r="BW105" t="n">
+        <v>0.9201819189214148</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>0.9182252388134741</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>0.005229130392284604</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>0.9103949617937906</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>0.008176291566357985</v>
+      </c>
+      <c r="CC105" t="inlineStr">
+        <is>
+          <t>0.8510638297872339, 0.868131868131868, 0.8350515463917525, 0.837696335078534, 0.8571428571428571, 0.8497409326424871, 0.8404255319148938</t>
+        </is>
+      </c>
+      <c r="CD105" t="inlineStr">
+        <is>
+          <t>0.9375, 0.9473684210526315, 0.9279279279279279, 0.9306487695749441, 0.9429824561403509, 0.9348314606741573, 0.9333333333333333</t>
+        </is>
+      </c>
+      <c r="CE105" t="n">
+        <v>0.9363703383861922</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0.9348314606741573</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0.006342106986593089</v>
+      </c>
+      <c r="CH105" t="inlineStr">
+        <is>
+          <t>0.894281914893617, 0.9077501445922498, 0.8814897371598402, 0.8841725523267391, 0.900062656641604, 0.8922861966583222, 0.8868794326241136</t>
+        </is>
+      </c>
+      <c r="CI105" t="n">
+        <v>0.8924175192709266</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>0.8922861966583222</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0.008578187011358099</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0.848464700155661</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>0.8497409326424871</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0.01089554794683732</v>
+      </c>
+      <c r="CO105" t="inlineStr">
+        <is>
+          <t>0.7692307692307693, 0.8144329896907216, 0.7431192660550459, 0.7547169811320755, 0.8041237113402062, 0.7592592592592593, 0.7669902912621359</t>
+        </is>
+      </c>
+      <c r="CP105" t="inlineStr">
+        <is>
+          <t>0.9813084112149533, 0.972972972972973, 0.9809523809523809, 0.9765258215962441, 0.9684684684684685, 0.985781990521327, 0.9722222222222222</t>
+        </is>
+      </c>
+      <c r="CQ105" t="n">
+        <v>0.9768903239926526</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>0.9765258215962441</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>0.005647741150517996</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>0.7731247525671734</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>0.7669902912621359</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>0.02435313941540409</v>
+      </c>
+      <c r="CW105" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9294117647058824, 0.9529411764705882, 0.9411764705882353, 0.9176470588235294, 0.9647058823529412, 0.9294117647058824</t>
+        </is>
+      </c>
+      <c r="CX105" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.9230769230769231, 0.8803418803418803, 0.8888888888888888, 0.9188034188034188, 0.8888888888888888, 0.8974358974358975</t>
+        </is>
+      </c>
+      <c r="CY105" t="n">
+        <v>0.8992673992673994</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>0.01477865499012237</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>0.9410964385754302</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>0.01534362094470151</v>
+      </c>
+      <c r="DE105" t="inlineStr">
+        <is>
+          <t>0.9712047212047212, 0.9768225238813475, 0.9673705379587731, 0.9739064856711916, 0.966365007541478, 0.9755153343388637, 0.9682755153343389</t>
+        </is>
+      </c>
+      <c r="DF105" t="n">
+        <v>0.9713514465615306</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>0.9712047212047212</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>0.003854384552734193</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4.xlsx
+++ b/results/metrics_modelling4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vulf/Git/Hub/Drop_wall_impact/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E75BC0-FE5C-6D41-A0F5-54B43863D988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41A0F1E-4A10-6649-89DA-597B4D155740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5596,6 +5596,9 @@
     <t>LogisticRegression_splashing_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.552828000398145, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.010000228881835938, 0.009027719497680664, 0.007972478866577148, 0.008032798767089844, 0.00700831413269043, 0.0070002079010009766, 0.0069963932037353516</t>
   </si>
   <si>
@@ -5665,6 +5668,9 @@
     <t>LogisticRegression_no_fragmentation_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 3.6236985622991797, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.00800013542175293, 0.0069997310638427734, 0.0069997310638427734, 0.006999969482421875, 0.007001161575317383, 0.007002353668212891, 0.008000850677490234</t>
   </si>
   <si>
@@ -5731,6 +5737,9 @@
     <t>KNeighborsClassifier_splashing_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'distance', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.010028839111328125, 0.006996870040893555, 0.006000995635986328, 0.006015300750732422, 0.006010293960571289, 0.0059702396392822266, 0.006994485855102539</t>
   </si>
   <si>
@@ -5788,6 +5797,9 @@
     <t>KNeighborsClassifier_no_fragmentation_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 5, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.008001327514648438, 0.00699925422668457, 0.004000425338745117, 0.00500178337097168, 0.005002498626708984, 0.006001710891723633, 0.004999876022338867</t>
   </si>
   <si>
@@ -5827,6 +5839,9 @@
     <t>SVC_splashing_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 18.041415988066607, 'class_weight': None, 'coef0': 0.06653734510998605, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.03385305404663086, 0.016930818557739258, 0.015964508056640625, 0.018526554107666016, 0.016786813735961914, 0.014027833938598633, 0.014509916305541992</t>
   </si>
   <si>
@@ -5896,6 +5911,9 @@
     <t>SVC_no_fragmentation_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 5.737910803667096, 'class_weight': None, 'coef0': 0.8535469624679377, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.012425422668457031, 0.009999275207519531, 0.010129451751708984, 0.010998725891113281, 0.011511564254760742, 0.011305809020996094, 0.011202335357666016</t>
   </si>
   <si>
@@ -5965,6 +5983,9 @@
     <t>LogisticRegression_splashing_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 0.47129737561107793, 'class_weight': None, 'penalty': 'l2'}, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.011999845504760742, 0.011874675750732422, 0.011998891830444336, 0.011457443237304688, 0.010410308837890625, 0.01091313362121582, 0.01103830337524414</t>
   </si>
   <si>
@@ -6031,6 +6052,9 @@
     <t>LogisticRegression_no_fragmentation_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'newton-cholesky', 'C': 6.5706235157060515, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.009731769561767578, 0.010012388229370117, 0.009104728698730469, 0.009039163589477539, 0.010002613067626953, 0.008647680282592773, 0.008929014205932617</t>
   </si>
   <si>
@@ -6100,6 +6124,9 @@
     <t>KNeighborsClassifier_splashing_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 2, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.011987924575805664, 0.009905338287353516, 0.008966207504272461, 0.009542465209960938, 0.009782791137695312, 0.009510040283203125, 0.009002685546875</t>
   </si>
   <si>
@@ -6139,6 +6166,9 @@
     <t>KNeighborsClassifier_no_fragmentation_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.010000467300415039, 0.008997917175292969, 0.008598804473876953, 0.007999181747436523, 0.009029865264892578, 0.007953166961669922, 0.0070002079010009766</t>
   </si>
   <si>
@@ -6208,6 +6238,9 @@
     <t>SVC_splashing_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 8.080278139769582, 'class_weight': 'balanced', 'coef0': 0.48875906950513137, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.019130468368530273, 0.017958402633666992, 0.01714777946472168, 0.0182952880859375, 0.0179290771484375, 0.01857900619506836, 0.016715526580810547</t>
   </si>
   <si>
@@ -6277,6 +6310,9 @@
     <t>SVC_no_fragmentation_smote_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 28.682610859801468, 'class_weight': None, 'coef0': 0.49963292619423594, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.022585391998291016, 0.019678592681884766, 0.018721342086791992, 0.019030094146728516, 0.021327733993530273, 0.01943683624267578, 0.018349647521972656</t>
   </si>
   <si>
@@ -6346,6 +6382,9 @@
     <t>LogisticRegression_splashing_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.15947545233607524, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.025205612182617188, 0.02387094497680664, 0.023152828216552734, 0.022998571395874023, 0.022031307220458984, 0.02233409881591797, 0.02214360237121582</t>
   </si>
   <si>
@@ -6415,6 +6454,9 @@
     <t>LogisticRegression_no_fragmentation_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'liblinear', 'C': 377.1313111077982, 'class_weight': None, 'penalty': 'l1'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.024035215377807617, 0.020569324493408203, 0.02002739906311035, 0.021613359451293945, 0.021079540252685547, 0.021424055099487305, 0.02055525779724121</t>
   </si>
   <si>
@@ -6451,6 +6493,9 @@
     <t>KNeighborsClassifier_splashing_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 1, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.026993751525878906, 0.020168304443359375, 0.019930124282836914, 0.02133655548095703, 0.020959138870239258, 0.021331071853637695, 0.02089977264404297</t>
   </si>
   <si>
@@ -6511,6 +6556,9 @@
     <t>KNeighborsClassifier_no_fragmentation_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.024509429931640625, 0.020848751068115234, 0.020676612854003906, 0.01972341537475586, 0.019952058792114258, 0.021252870559692383, 0.020036697387695312</t>
   </si>
   <si>
@@ -6580,6 +6628,9 @@
     <t>SVC_splashing_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 26.972626232440984, 'class_weight': 'balanced', 'coef0': 0.08285683438096408, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.04044198989868164, 0.03241443634033203, 0.05623126029968262, 0.03369283676147461, 0.03164029121398926, 0.03268027305603027, 0.03355598449707031</t>
   </si>
   <si>
@@ -6649,6 +6700,9 @@
     <t>SVC_no_fragmentation_smotenc_opt-model</t>
   </si>
   <si>
+    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 27.620566418088167, 'class_weight': 'balanced', 'coef0': 0.48744430071806377, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+  </si>
+  <si>
     <t>0.0368349552154541, 0.030502796173095703, 0.03272080421447754, 0.031003713607788086, 0.03106212615966797, 0.03137636184692383, 0.03338742256164551</t>
   </si>
   <si>
@@ -6713,60 +6767,6 @@
   </si>
   <si>
     <t>0.9712047212047212, 0.9768225238813475, 0.9673705379587731, 0.9739064856711916, 0.966365007541478, 0.9755153343388637, 0.9682755153343389</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.552828000398145, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 3.6236985622991797, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 27.620566418088167, 'class_weight': 'balanced', 'coef0': 0.48744430071806377, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 26.972626232440984, 'class_weight': 'balanced', 'coef0': 0.08285683438096408, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 1, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'liblinear', 'C': 377.1313111077982, 'class_weight': None, 'penalty': 'l1'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'sag', 'C': 0.15947545233607524, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 28.682610859801468, 'class_weight': None, 'coef0': 0.49963292619423594, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 8.080278139769582, 'class_weight': 'balanced', 'coef0': 0.48875906950513137, 'degree': 2, 'gamma': 'auto'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'uniform', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 2, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'newton-cholesky', 'C': 6.5706235157060515, 'class_weight': 'balanced', 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'LogisticRegression', 'estimator_params': {'fit_intercept': False, 'max_iter': 1000, 'solver': 'lbfgs', 'C': 0.47129737561107793, 'class_weight': None, 'penalty': 'l2'}, 'class_weight': None, 'penalty': 'l2'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 5.737910803667096, 'class_weight': None, 'coef0': 0.8535469624679377, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'SVC', 'estimator_params': {'probability': True, 'kernel': 'poly', 'C': 18.041415988066607, 'class_weight': None, 'coef0': 0.06653734510998605, 'degree': 2, 'gamma': 'scale'}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 3, 'weights': 'distance', 'p': 2}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
-  </si>
-  <si>
-    <t>{'estimator': 'KNeighborsClassifier', 'estimator_params': {'n_neighbors': 5, 'weights': 'distance', 'p': 1}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': False, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
   </si>
 </sst>
 </file>
@@ -36550,7 +36550,7 @@
         <v>1857</v>
       </c>
       <c r="D88" t="s">
-        <v>2231</v>
+        <v>1858</v>
       </c>
       <c r="E88">
         <v>0.78666666666666663</v>
@@ -36613,7 +36613,7 @@
         <v>0.79668049792531126</v>
       </c>
       <c r="Y88" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="Z88">
         <v>8.0054487500871938E-3</v>
@@ -36625,7 +36625,7 @@
         <v>1.0723139197588111E-3</v>
       </c>
       <c r="AC88" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="AD88">
         <v>1.646113395690918E-2</v>
@@ -36637,10 +36637,10 @@
         <v>1.56083659277844E-3</v>
       </c>
       <c r="AG88" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="AH88" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="AI88">
         <v>0.82886101809144708</v>
@@ -36661,10 +36661,10 @@
         <v>5.4442024745888183E-2</v>
       </c>
       <c r="AO88" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="AP88" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AQ88">
         <v>0.77339474320449408</v>
@@ -36676,7 +36676,7 @@
         <v>6.3445713556925173E-2</v>
       </c>
       <c r="AT88" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="AU88">
         <v>0.80948694899938711</v>
@@ -36697,10 +36697,10 @@
         <v>4.8832068757050838E-2</v>
       </c>
       <c r="BA88" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="BB88" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="BC88">
         <v>0.70034005114423548</v>
@@ -36721,10 +36721,10 @@
         <v>4.0507547092598691E-2</v>
       </c>
       <c r="BI88" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="BJ88" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="BK88">
         <v>0.87092731829573922</v>
@@ -36745,7 +36745,7 @@
         <v>7.554445485019097E-2</v>
       </c>
       <c r="BQ88" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="BR88">
         <v>0.89732243774702858</v>
@@ -36757,10 +36757,10 @@
         <v>4.6350320653201889E-2</v>
       </c>
       <c r="BU88" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="BV88" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="BW88">
         <v>0.83751604529398749</v>
@@ -36781,10 +36781,10 @@
         <v>9.8321672312090651E-3</v>
       </c>
       <c r="CC88" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="CD88" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="CE88">
         <v>0.78129343692151554</v>
@@ -36796,7 +36796,7 @@
         <v>9.4179777766895886E-3</v>
       </c>
       <c r="CH88" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="CI88">
         <v>0.81755999903193499</v>
@@ -36817,10 +36817,10 @@
         <v>9.6838309101750543E-3</v>
       </c>
       <c r="CO88" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="CP88" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="CQ88">
         <v>0.70202021846842677</v>
@@ -36841,10 +36841,10 @@
         <v>7.5910311155891466E-3</v>
       </c>
       <c r="CW88" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="CX88" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="CY88">
         <v>0.88130725042695235</v>
@@ -36865,7 +36865,7 @@
         <v>1.8071534642519649E-2</v>
       </c>
       <c r="DE88" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="DF88">
         <v>0.90969531996605446</v>
@@ -36885,10 +36885,10 @@
         <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="D89" t="s">
-        <v>2232</v>
+        <v>1882</v>
       </c>
       <c r="E89">
         <v>0.82666666666666666</v>
@@ -36951,7 +36951,7 @@
         <v>0.9033816425120772</v>
       </c>
       <c r="Y89" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="Z89">
         <v>7.2862761361258367E-3</v>
@@ -36963,7 +36963,7 @@
         <v>4.5171131619771589E-4</v>
       </c>
       <c r="AC89" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="AD89">
         <v>1.3425895145961221E-2</v>
@@ -36975,10 +36975,10 @@
         <v>4.9737836101214968E-4</v>
       </c>
       <c r="AG89" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="AH89" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="AI89">
         <v>0.8643642072213501</v>
@@ -36999,10 +36999,10 @@
         <v>5.8839094672646551E-2</v>
       </c>
       <c r="AO89" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="AP89" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="AQ89">
         <v>0.89660790605935159</v>
@@ -37014,7 +37014,7 @@
         <v>4.5344363618053538E-2</v>
       </c>
       <c r="AT89" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="AU89">
         <v>0.83279524954828321</v>
@@ -37035,10 +37035,10 @@
         <v>8.2792754002689539E-2</v>
       </c>
       <c r="BA89" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="BB89" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="BC89">
         <v>0.95093956879671171</v>
@@ -37062,7 +37062,7 @@
         <v>198</v>
       </c>
       <c r="BJ89" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="BK89">
         <v>0.84981684981684968</v>
@@ -37083,7 +37083,7 @@
         <v>9.1024373788722357E-2</v>
       </c>
       <c r="BQ89" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="BR89">
         <v>0.93521716378859232</v>
@@ -37095,10 +37095,10 @@
         <v>3.6492377948779603E-2</v>
       </c>
       <c r="BU89" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="BV89" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="BW89">
         <v>0.86560059921404453</v>
@@ -37119,10 +37119,10 @@
         <v>9.6149545162086767E-3</v>
       </c>
       <c r="CC89" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="CD89" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="CE89">
         <v>0.89966608584924734</v>
@@ -37134,7 +37134,7 @@
         <v>7.0531262209585126E-3</v>
       </c>
       <c r="CH89" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="CI89">
         <v>0.83463826574678879</v>
@@ -37155,10 +37155,10 @@
         <v>1.5189692595782581E-2</v>
       </c>
       <c r="CO89" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="CP89" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="CQ89">
         <v>0.95041134659786153</v>
@@ -37179,10 +37179,10 @@
         <v>1.575385788795243E-2</v>
       </c>
       <c r="CW89" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="CX89" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="CY89">
         <v>0.85409035409035394</v>
@@ -37203,7 +37203,7 @@
         <v>1.641310052344333E-2</v>
       </c>
       <c r="DE89" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="DF89">
         <v>0.93937797341158702</v>
@@ -37223,10 +37223,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="D90" t="s">
-        <v>2247</v>
+        <v>1905</v>
       </c>
       <c r="E90">
         <v>0.85333333333333339</v>
@@ -37289,7 +37289,7 @@
         <v>0.99526066350710907</v>
       </c>
       <c r="Y90" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="Z90">
         <v>6.8595749991280696E-3</v>
@@ -37301,7 +37301,7 @@
         <v>1.3650452150791559E-3</v>
       </c>
       <c r="AC90" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="AD90">
         <v>1.597057070050921E-2</v>
@@ -37313,10 +37313,10 @@
         <v>9.229586112470226E-4</v>
       </c>
       <c r="AG90" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="AH90" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="AI90">
         <v>0.88584591731429396</v>
@@ -37337,10 +37337,10 @@
         <v>3.1678857770437968E-2</v>
       </c>
       <c r="AO90" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="AP90" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="AQ90">
         <v>0.85138227503897768</v>
@@ -37352,7 +37352,7 @@
         <v>4.1561792280754919E-2</v>
       </c>
       <c r="AT90" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="AU90">
         <v>0.88342827512180488</v>
@@ -37373,10 +37373,10 @@
         <v>2.5532956825800021E-2</v>
       </c>
       <c r="BA90" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="BB90" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="BC90">
         <v>0.8441119031344595</v>
@@ -37397,10 +37397,10 @@
         <v>2.043371926778044E-2</v>
       </c>
       <c r="BI90" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="BJ90" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="BK90">
         <v>0.86340852130325807</v>
@@ -37421,7 +37421,7 @@
         <v>4.7036155944005412E-2</v>
       </c>
       <c r="BQ90" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="BR90">
         <v>0.92486924594399178</v>
@@ -37436,7 +37436,7 @@
         <v>369</v>
       </c>
       <c r="BV90" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="BW90">
         <v>0.99826460539223982</v>
@@ -37457,10 +37457,10 @@
         <v>1.417051170840857E-3</v>
       </c>
       <c r="CC90" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="CD90" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="CE90">
         <v>0.99685336689741977</v>
@@ -37472,7 +37472,7 @@
         <v>1.9901055130071761E-3</v>
       </c>
       <c r="CH90" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="CI90">
         <v>0.99755687288639661</v>
@@ -37496,7 +37496,7 @@
         <v>375</v>
       </c>
       <c r="CP90" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="CQ90">
         <v>0.99373433583959891</v>
@@ -37517,7 +37517,7 @@
         <v>0</v>
       </c>
       <c r="CW90" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="CX90" t="s">
         <v>375</v>
@@ -37561,10 +37561,10 @@
         <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="D91" t="s">
-        <v>2248</v>
+        <v>1925</v>
       </c>
       <c r="E91">
         <v>0.92</v>
@@ -37627,7 +37627,7 @@
         <v>1</v>
       </c>
       <c r="Y91" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
       <c r="Z91">
         <v>5.7152679988316116E-3</v>
@@ -37639,7 +37639,7 @@
         <v>1.277626694582705E-3</v>
       </c>
       <c r="AC91" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="AD91">
         <v>1.5026535306658061E-2</v>
@@ -37651,10 +37651,10 @@
         <v>2.1160577179123682E-3</v>
       </c>
       <c r="AG91" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="AH91" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="AI91">
         <v>0.82697540554683402</v>
@@ -37675,10 +37675,10 @@
         <v>3.1570371855296632E-2</v>
       </c>
       <c r="AO91" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="AP91" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="AQ91">
         <v>0.91459045625712299</v>
@@ -37690,7 +37690,7 @@
         <v>2.2537737450952271E-2</v>
       </c>
       <c r="AT91" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="AU91">
         <v>0.8334743445786138</v>
@@ -37711,10 +37711,10 @@
         <v>6.5039747346654866E-2</v>
       </c>
       <c r="BA91" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="BB91" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="BC91">
         <v>0.90530303691866132</v>
@@ -37735,10 +37735,10 @@
         <v>0.10228865129620759</v>
       </c>
       <c r="BI91" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="BJ91" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="BK91">
         <v>0.92673992673992667</v>
@@ -37759,7 +37759,7 @@
         <v>0.10400824410131369</v>
       </c>
       <c r="BQ91" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
       <c r="BR91">
         <v>0.93168498168498182</v>
@@ -37899,10 +37899,10 @@
         <v>113</v>
       </c>
       <c r="C92" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="D92" t="s">
-        <v>2246</v>
+        <v>1939</v>
       </c>
       <c r="E92">
         <v>0.84</v>
@@ -37965,7 +37965,7 @@
         <v>0.87081339712918659</v>
       </c>
       <c r="Y92" t="s">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="Z92">
         <v>1.8657071249825609E-2</v>
@@ -37977,7 +37977,7 @@
         <v>6.3616189333841767E-3</v>
       </c>
       <c r="AC92" t="s">
-        <v>1936</v>
+        <v>1941</v>
       </c>
       <c r="AD92">
         <v>1.7291375568934848E-2</v>
@@ -37989,10 +37989,10 @@
         <v>4.9319890074851968E-3</v>
       </c>
       <c r="AG92" t="s">
-        <v>1937</v>
+        <v>1942</v>
       </c>
       <c r="AH92" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="AI92">
         <v>0.86159551539914214</v>
@@ -38013,10 +38013,10 @@
         <v>3.6418220603683812E-2</v>
       </c>
       <c r="AO92" t="s">
-        <v>1939</v>
+        <v>1944</v>
       </c>
       <c r="AP92" t="s">
-        <v>1940</v>
+        <v>1945</v>
       </c>
       <c r="AQ92">
         <v>0.82329995593282934</v>
@@ -38028,7 +38028,7 @@
         <v>5.7501527766802042E-2</v>
       </c>
       <c r="AT92" t="s">
-        <v>1941</v>
+        <v>1946</v>
       </c>
       <c r="AU92">
         <v>0.8654576529983663</v>
@@ -38049,10 +38049,10 @@
         <v>2.7060612692675439E-2</v>
       </c>
       <c r="BA92" t="s">
-        <v>1942</v>
+        <v>1947</v>
       </c>
       <c r="BB92" t="s">
-        <v>1943</v>
+        <v>1948</v>
       </c>
       <c r="BC92">
         <v>0.85034734787056743</v>
@@ -38073,10 +38073,10 @@
         <v>3.7412677092296842E-2</v>
       </c>
       <c r="BI92" t="s">
-        <v>1944</v>
+        <v>1949</v>
       </c>
       <c r="BJ92" t="s">
-        <v>1945</v>
+        <v>1950</v>
       </c>
       <c r="BK92">
         <v>0.80242272347535504</v>
@@ -38097,7 +38097,7 @@
         <v>3.7275634884588717E-2</v>
       </c>
       <c r="BQ92" t="s">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="BR92">
         <v>0.93525831385185643</v>
@@ -38109,10 +38109,10 @@
         <v>3.5829968492735793E-2</v>
       </c>
       <c r="BU92" t="s">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="BV92" t="s">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="BW92">
         <v>0.90049037196752579</v>
@@ -38133,10 +38133,10 @@
         <v>1.023858807929395E-2</v>
       </c>
       <c r="CC92" t="s">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="CD92" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="CE92">
         <v>0.87315400977137847</v>
@@ -38148,7 +38148,7 @@
         <v>1.453673088192685E-2</v>
       </c>
       <c r="CH92" t="s">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="CI92">
         <v>0.90220448068119097</v>
@@ -38169,10 +38169,10 @@
         <v>7.9116326087036518E-3</v>
       </c>
       <c r="CO92" t="s">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="CP92" t="s">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="CQ92">
         <v>0.88163111580542775</v>
@@ -38193,10 +38193,10 @@
         <v>7.5736648416428838E-3</v>
       </c>
       <c r="CW92" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="CX92" t="s">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="CY92">
         <v>0.86487235788586503</v>
@@ -38217,7 +38217,7 @@
         <v>8.814516510296494E-3</v>
       </c>
       <c r="DE92" t="s">
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="DF92">
         <v>0.96498620518971279</v>
@@ -38237,10 +38237,10 @@
         <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="D93" t="s">
-        <v>2245</v>
+        <v>1963</v>
       </c>
       <c r="E93">
         <v>0.8666666666666667</v>
@@ -38303,7 +38303,7 @@
         <v>0.94883720930232562</v>
       </c>
       <c r="Y93" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
       <c r="Z93">
         <v>1.1081797736031671E-2</v>
@@ -38315,7 +38315,7 @@
         <v>7.6908632468164495E-4</v>
       </c>
       <c r="AC93" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="AD93">
         <v>1.463331495012556E-2</v>
@@ -38327,10 +38327,10 @@
         <v>1.312864857834909E-3</v>
       </c>
       <c r="AG93" t="s">
-        <v>1960</v>
+        <v>1966</v>
       </c>
       <c r="AH93" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="AI93">
         <v>0.88529565672422816</v>
@@ -38351,10 +38351,10 @@
         <v>5.2308260995201229E-2</v>
       </c>
       <c r="AO93" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="AP93" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="AQ93">
         <v>0.92857375031163947</v>
@@ -38366,7 +38366,7 @@
         <v>3.8092925665618102E-2</v>
       </c>
       <c r="AT93" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="AU93">
         <v>0.87404875049055364</v>
@@ -38387,10 +38387,10 @@
         <v>8.3157645302476865E-2</v>
       </c>
       <c r="BA93" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
       <c r="BB93" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="BC93">
         <v>0.94691772868464597</v>
@@ -38411,10 +38411,10 @@
         <v>0.1049407686566827</v>
       </c>
       <c r="BI93" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="BJ93" t="s">
-        <v>1968</v>
+        <v>1974</v>
       </c>
       <c r="BK93">
         <v>0.91208791208791218</v>
@@ -38435,7 +38435,7 @@
         <v>8.5438493789503467E-2</v>
       </c>
       <c r="BQ93" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="BR93">
         <v>0.95874760160474448</v>
@@ -38447,10 +38447,10 @@
         <v>1.9679551721959721E-2</v>
       </c>
       <c r="BU93" t="s">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="BV93" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="BW93">
         <v>0.90932398600465836</v>
@@ -38471,10 +38471,10 @@
         <v>5.9107130862048112E-3</v>
       </c>
       <c r="CC93" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="CD93" t="s">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="CE93">
         <v>0.94389976755300364</v>
@@ -38486,7 +38486,7 @@
         <v>4.2004318802550322E-3</v>
       </c>
       <c r="CH93" t="s">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="CI93">
         <v>0.89878501048976223</v>
@@ -38507,10 +38507,10 @@
         <v>1.042945052687042E-2</v>
       </c>
       <c r="CO93" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="CP93" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="CQ93">
         <v>0.95854807561982036</v>
@@ -38531,10 +38531,10 @@
         <v>1.740622108788583E-2</v>
       </c>
       <c r="CW93" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="CX93" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="CY93">
         <v>0.92979242979242982</v>
@@ -38555,7 +38555,7 @@
         <v>1.9955734046635809E-2</v>
       </c>
       <c r="DE93" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="DF93">
         <v>0.97052735624164199</v>
@@ -38575,10 +38575,10 @@
         <v>113</v>
       </c>
       <c r="C94" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="D94" t="s">
-        <v>2244</v>
+        <v>1987</v>
       </c>
       <c r="E94">
         <v>0.77333333333333332</v>
@@ -38641,7 +38641,7 @@
         <v>0.8</v>
       </c>
       <c r="Y94" t="s">
-        <v>1981</v>
+        <v>1988</v>
       </c>
       <c r="Z94">
         <v>1.1384657451084679E-2</v>
@@ -38653,7 +38653,7 @@
         <v>5.7231447484966586E-4</v>
       </c>
       <c r="AC94" t="s">
-        <v>1982</v>
+        <v>1989</v>
       </c>
       <c r="AD94">
         <v>1.5223673411778041E-2</v>
@@ -38665,10 +38665,10 @@
         <v>8.97125378465606E-4</v>
       </c>
       <c r="AG94" t="s">
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="AH94" t="s">
-        <v>1984</v>
+        <v>1991</v>
       </c>
       <c r="AI94">
         <v>0.82886101809144708</v>
@@ -38689,10 +38689,10 @@
         <v>4.8514438936045408E-2</v>
       </c>
       <c r="AO94" t="s">
-        <v>1985</v>
+        <v>1992</v>
       </c>
       <c r="AP94" t="s">
-        <v>1986</v>
+        <v>1993</v>
       </c>
       <c r="AQ94">
         <v>0.77317102279508287</v>
@@ -38704,7 +38704,7 @@
         <v>5.6521888218575553E-2</v>
       </c>
       <c r="AT94" t="s">
-        <v>1987</v>
+        <v>1994</v>
       </c>
       <c r="AU94">
         <v>0.80933611177901665</v>
@@ -38725,10 +38725,10 @@
         <v>4.4235689348156623E-2</v>
       </c>
       <c r="BA94" t="s">
-        <v>1988</v>
+        <v>1995</v>
       </c>
       <c r="BB94" t="s">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="BC94">
         <v>0.70081676654705927</v>
@@ -38752,7 +38752,7 @@
         <v>558</v>
       </c>
       <c r="BJ94" t="s">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="BK94">
         <v>0.87092731829573933</v>
@@ -38773,7 +38773,7 @@
         <v>7.554445485019097E-2</v>
       </c>
       <c r="BQ94" t="s">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="BR94">
         <v>0.897734532409455</v>
@@ -38785,10 +38785,10 @@
         <v>4.6250333929565193E-2</v>
       </c>
       <c r="BU94" t="s">
-        <v>1992</v>
+        <v>1999</v>
       </c>
       <c r="BV94" t="s">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="BW94">
         <v>0.83760621616320907</v>
@@ -38809,10 +38809,10 @@
         <v>8.5821525732836454E-3</v>
       </c>
       <c r="CC94" t="s">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="CD94" t="s">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="CE94">
         <v>0.78097349016625317</v>
@@ -38824,7 +38824,7 @@
         <v>6.7801624782986604E-3</v>
       </c>
       <c r="CH94" t="s">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="CI94">
         <v>0.81652679128772576</v>
@@ -38845,10 +38845,10 @@
         <v>9.0363374342491559E-3</v>
       </c>
       <c r="CO94" t="s">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="CP94" t="s">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="CQ94">
         <v>0.69847422693304684</v>
@@ -38869,10 +38869,10 @@
         <v>6.4336214947721578E-3</v>
       </c>
       <c r="CW94" t="s">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="CX94" t="s">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="CY94">
         <v>0.88634196109743379</v>
@@ -38893,7 +38893,7 @@
         <v>1.977086446669224E-2</v>
       </c>
       <c r="DE94" t="s">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="DF94">
         <v>0.91073181214768406</v>
@@ -38913,10 +38913,10 @@
         <v>138</v>
       </c>
       <c r="C95" t="s">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="D95" t="s">
-        <v>2243</v>
+        <v>2010</v>
       </c>
       <c r="E95">
         <v>0.82666666666666666</v>
@@ -38979,7 +38979,7 @@
         <v>0.875</v>
       </c>
       <c r="Y95" t="s">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="Z95">
         <v>9.3524796622140062E-3</v>
@@ -38991,7 +38991,7 @@
         <v>5.1236513894784745E-4</v>
       </c>
       <c r="AC95" t="s">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="AD95">
         <v>1.4224393027169361E-2</v>
@@ -39003,10 +39003,10 @@
         <v>1.1017711288096119E-3</v>
       </c>
       <c r="AG95" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="AH95" t="s">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="AI95">
         <v>0.85408163265306136</v>
@@ -39027,10 +39027,10 @@
         <v>5.3129038015935118E-2</v>
       </c>
       <c r="AO95" t="s">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="AP95" t="s">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="AQ95">
         <v>0.87642823047249596</v>
@@ -39042,7 +39042,7 @@
         <v>4.0658428646815868E-2</v>
       </c>
       <c r="AT95" t="s">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="AU95">
         <v>0.80956674230858228</v>
@@ -39063,10 +39063,10 @@
         <v>7.6574942173962199E-2</v>
       </c>
       <c r="BA95" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="BB95" t="s">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="BC95">
         <v>0.95672313157912237</v>
@@ -39087,10 +39087,10 @@
         <v>7.9321056760163183E-2</v>
       </c>
       <c r="BI95" t="s">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="BJ95" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="BK95">
         <v>0.80952380952380953</v>
@@ -39111,7 +39111,7 @@
         <v>8.4408584322427746E-2</v>
       </c>
       <c r="BQ95" t="s">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="BR95">
         <v>0.94681667538810399</v>
@@ -39123,10 +39123,10 @@
         <v>3.0782577013458021E-2</v>
       </c>
       <c r="BU95" t="s">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="BV95" t="s">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="BW95">
         <v>0.85722878895147814</v>
@@ -39147,10 +39147,10 @@
         <v>1.0847611032199609E-2</v>
       </c>
       <c r="CC95" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="CD95" t="s">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="CE95">
         <v>0.87979823730049567</v>
@@ -39162,7 +39162,7 @@
         <v>8.8166518431554951E-3</v>
       </c>
       <c r="CH95" t="s">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="CI95">
         <v>0.8130634152597308</v>
@@ -39183,10 +39183,10 @@
         <v>1.3372804051122169E-2</v>
       </c>
       <c r="CO95" t="s">
-        <v>2020</v>
+        <v>2028</v>
       </c>
       <c r="CP95" t="s">
-        <v>2021</v>
+        <v>2029</v>
       </c>
       <c r="CQ95">
         <v>0.95763568236948893</v>
@@ -39207,10 +39207,10 @@
         <v>1.9157236468690279E-2</v>
       </c>
       <c r="CW95" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="CX95" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="CY95">
         <v>0.81379731379731368</v>
@@ -39231,7 +39231,7 @@
         <v>1.075183998923873E-2</v>
       </c>
       <c r="DE95" t="s">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="DF95">
         <v>0.94716972258989074</v>
@@ -39251,10 +39251,10 @@
         <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="D96" t="s">
-        <v>2242</v>
+        <v>2034</v>
       </c>
       <c r="E96">
         <v>0.85333333333333339</v>
@@ -39317,7 +39317,7 @@
         <v>0.99526066350710907</v>
       </c>
       <c r="Y96" t="s">
-        <v>2026</v>
+        <v>2035</v>
       </c>
       <c r="Z96">
         <v>9.8139217921665734E-3</v>
@@ -39329,7 +39329,7 @@
         <v>9.4705337031672293E-4</v>
       </c>
       <c r="AC96" t="s">
-        <v>2027</v>
+        <v>2036</v>
       </c>
       <c r="AD96">
         <v>1.6008002417428151E-2</v>
@@ -39341,10 +39341,10 @@
         <v>1.4631953176020591E-3</v>
       </c>
       <c r="AG96" t="s">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="AH96" t="s">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="AI96">
         <v>0.88590594132389799</v>
@@ -39365,10 +39365,10 @@
         <v>3.6143803771930168E-2</v>
       </c>
       <c r="AO96" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="AP96" t="s">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="AQ96">
         <v>0.85135387326356138</v>
@@ -39380,7 +39380,7 @@
         <v>4.5773095695721321E-2</v>
       </c>
       <c r="AT96" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="AU96">
         <v>0.8833888866710965</v>
@@ -39401,10 +39401,10 @@
         <v>2.9806642222565741E-2</v>
       </c>
       <c r="BA96" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="BB96" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="BC96">
         <v>0.84717746747821931</v>
@@ -39425,10 +39425,10 @@
         <v>2.7877211900740991E-2</v>
       </c>
       <c r="BI96" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
       <c r="BJ96" t="s">
-        <v>2036</v>
+        <v>2045</v>
       </c>
       <c r="BK96">
         <v>0.86340852130325818</v>
@@ -39449,7 +39449,7 @@
         <v>5.5969162370913303E-2</v>
       </c>
       <c r="BQ96" t="s">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="BR96">
         <v>0.91902936613241792</v>
@@ -39464,7 +39464,7 @@
         <v>369</v>
       </c>
       <c r="BV96" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="BW96">
         <v>0.99826460539223982</v>
@@ -39485,10 +39485,10 @@
         <v>1.417051170840857E-3</v>
       </c>
       <c r="CC96" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="CD96" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="CE96">
         <v>0.99685336689741977</v>
@@ -39500,7 +39500,7 @@
         <v>1.9901055130071761E-3</v>
       </c>
       <c r="CH96" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="CI96">
         <v>0.99755687288639661</v>
@@ -39524,7 +39524,7 @@
         <v>375</v>
       </c>
       <c r="CP96" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="CQ96">
         <v>0.99373433583959891</v>
@@ -39545,7 +39545,7 @@
         <v>0</v>
       </c>
       <c r="CW96" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="CX96" t="s">
         <v>375</v>
@@ -39589,10 +39589,10 @@
         <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>2038</v>
+        <v>2047</v>
       </c>
       <c r="D97" t="s">
-        <v>2241</v>
+        <v>2048</v>
       </c>
       <c r="E97">
         <v>0.84</v>
@@ -39655,7 +39655,7 @@
         <v>0.95981087470449178</v>
       </c>
       <c r="Y97" t="s">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="Z97">
         <v>8.5113729749407094E-3</v>
@@ -39667,7 +39667,7 @@
         <v>8.9348110366789751E-4</v>
       </c>
       <c r="AC97" t="s">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="AD97">
         <v>1.6461508614676341E-2</v>
@@ -39679,10 +39679,10 @@
         <v>1.1809220954667899E-3</v>
       </c>
       <c r="AG97" t="s">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="AH97" t="s">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="AI97">
         <v>0.86187859759288321</v>
@@ -39703,10 +39703,10 @@
         <v>5.8686965356105063E-2</v>
       </c>
       <c r="AO97" t="s">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="AP97" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="AQ97">
         <v>0.9058525285642629</v>
@@ -39718,7 +39718,7 @@
         <v>4.4834732615850942E-2</v>
       </c>
       <c r="AT97" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="AU97">
         <v>0.84241653879667433</v>
@@ -39739,10 +39739,10 @@
         <v>8.2415499252061833E-2</v>
       </c>
       <c r="BA97" t="s">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="BB97" t="s">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="BC97">
         <v>0.94067831401975588</v>
@@ -39763,10 +39763,10 @@
         <v>0.11443901769543049</v>
       </c>
       <c r="BI97" t="s">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="BJ97" t="s">
-        <v>2049</v>
+        <v>2059</v>
       </c>
       <c r="BK97">
         <v>0.87545787545787535</v>
@@ -39787,7 +39787,7 @@
         <v>7.0970347514258389E-2</v>
       </c>
       <c r="BQ97" t="s">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="BR97">
         <v>0.91036106750392476</v>
@@ -39799,10 +39799,10 @@
         <v>5.3732196890561801E-2</v>
       </c>
       <c r="BU97" t="s">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="BV97" t="s">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="BW97">
         <v>0.95042247668298097</v>
@@ -39823,10 +39823,10 @@
         <v>5.241863005903344E-3</v>
       </c>
       <c r="CC97" t="s">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="CD97" t="s">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="CE97">
         <v>0.96187498057230314</v>
@@ -39838,7 +39838,7 @@
         <v>3.6640131249366221E-3</v>
       </c>
       <c r="CH97" t="s">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="CI97">
         <v>0.93267837381665519</v>
@@ -39859,10 +39859,10 @@
         <v>9.2535578013054828E-3</v>
       </c>
       <c r="CO97" t="s">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="CP97" t="s">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="CQ97">
         <v>0.98529986432933259</v>
@@ -39883,10 +39883,10 @@
         <v>1.0211061853907291E-2</v>
       </c>
       <c r="CW97" t="s">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="CX97" t="s">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="CY97">
         <v>0.93956043956043966</v>
@@ -39907,7 +39907,7 @@
         <v>1.36398536179124E-2</v>
       </c>
       <c r="DE97" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="DF97">
         <v>0.99214048867410221</v>
@@ -39927,10 +39927,10 @@
         <v>113</v>
       </c>
       <c r="C98" t="s">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="D98" t="s">
-        <v>2240</v>
+        <v>2072</v>
       </c>
       <c r="E98">
         <v>0.82666666666666666</v>
@@ -39993,7 +39993,7 @@
         <v>0.87037037037037035</v>
       </c>
       <c r="Y98" t="s">
-        <v>2062</v>
+        <v>2073</v>
       </c>
       <c r="Z98">
         <v>1.7965078353881839E-2</v>
@@ -40005,7 +40005,7 @@
         <v>7.6296203869359092E-4</v>
       </c>
       <c r="AC98" t="s">
-        <v>2063</v>
+        <v>2074</v>
       </c>
       <c r="AD98">
         <v>1.4922244208199639E-2</v>
@@ -40017,10 +40017,10 @@
         <v>5.4791746153441017E-4</v>
       </c>
       <c r="AG98" t="s">
-        <v>2064</v>
+        <v>2075</v>
       </c>
       <c r="AH98" t="s">
-        <v>2065</v>
+        <v>2076</v>
       </c>
       <c r="AI98">
         <v>0.87818776633460394</v>
@@ -40041,10 +40041,10 @@
         <v>4.8420056979197192E-2</v>
       </c>
       <c r="AO98" t="s">
-        <v>2066</v>
+        <v>2077</v>
       </c>
       <c r="AP98" t="s">
-        <v>2067</v>
+        <v>2078</v>
       </c>
       <c r="AQ98">
         <v>0.83685393197588309</v>
@@ -40056,7 +40056,7 @@
         <v>6.0923346791577723E-2</v>
       </c>
       <c r="AT98" t="s">
-        <v>2068</v>
+        <v>2079</v>
       </c>
       <c r="AU98">
         <v>0.86840731517387559</v>
@@ -40077,10 +40077,10 @@
         <v>4.0340855897196118E-2</v>
       </c>
       <c r="BA98" t="s">
-        <v>2069</v>
+        <v>2080</v>
       </c>
       <c r="BB98" t="s">
-        <v>2070</v>
+        <v>2081</v>
       </c>
       <c r="BC98">
         <v>0.79834988540870899</v>
@@ -40101,10 +40101,10 @@
         <v>3.0038471158665689E-2</v>
       </c>
       <c r="BI98" t="s">
-        <v>2071</v>
+        <v>2082</v>
       </c>
       <c r="BJ98" t="s">
-        <v>2072</v>
+        <v>2083</v>
       </c>
       <c r="BK98">
         <v>0.88554720133667486</v>
@@ -40125,7 +40125,7 @@
         <v>6.5125801472186981E-2</v>
       </c>
       <c r="BQ98" t="s">
-        <v>2073</v>
+        <v>2084</v>
       </c>
       <c r="BR98">
         <v>0.93420947326298953</v>
@@ -40137,10 +40137,10 @@
         <v>3.2692277747609987E-2</v>
       </c>
       <c r="BU98" t="s">
-        <v>2074</v>
+        <v>2085</v>
       </c>
       <c r="BV98" t="s">
-        <v>2075</v>
+        <v>2086</v>
       </c>
       <c r="BW98">
         <v>0.90295281885652279</v>
@@ -40161,10 +40161,10 @@
         <v>3.5749186921830499E-3</v>
       </c>
       <c r="CC98" t="s">
-        <v>2076</v>
+        <v>2087</v>
       </c>
       <c r="CD98" t="s">
-        <v>2077</v>
+        <v>2088</v>
       </c>
       <c r="CE98">
         <v>0.866330297705592</v>
@@ -40176,7 +40176,7 @@
         <v>5.723592902356963E-3</v>
       </c>
       <c r="CH98" t="s">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="CI98">
         <v>0.89327129289729701</v>
@@ -40197,10 +40197,10 @@
         <v>2.753989329424617E-3</v>
       </c>
       <c r="CO98" t="s">
-        <v>2079</v>
+        <v>2090</v>
       </c>
       <c r="CP98" t="s">
-        <v>2080</v>
+        <v>2091</v>
       </c>
       <c r="CQ98">
         <v>0.82464067370751004</v>
@@ -40221,10 +40221,10 @@
         <v>9.674706604636844E-3</v>
       </c>
       <c r="CW98" t="s">
-        <v>2081</v>
+        <v>2092</v>
       </c>
       <c r="CX98" t="s">
-        <v>2082</v>
+        <v>2093</v>
       </c>
       <c r="CY98">
         <v>0.91285736465056455</v>
@@ -40245,7 +40245,7 @@
         <v>8.6966904373310706E-3</v>
       </c>
       <c r="DE98" t="s">
-        <v>2083</v>
+        <v>2094</v>
       </c>
       <c r="DF98">
         <v>0.96051483720523034</v>
@@ -40265,10 +40265,10 @@
         <v>138</v>
       </c>
       <c r="C99" t="s">
-        <v>2084</v>
+        <v>2095</v>
       </c>
       <c r="D99" t="s">
-        <v>2239</v>
+        <v>2096</v>
       </c>
       <c r="E99">
         <v>0.8666666666666667</v>
@@ -40331,7 +40331,7 @@
         <v>0.94033412887828161</v>
       </c>
       <c r="Y99" t="s">
-        <v>2085</v>
+        <v>2097</v>
       </c>
       <c r="Z99">
         <v>1.9875662667410719E-2</v>
@@ -40343,7 +40343,7 @@
         <v>1.4171759515281201E-3</v>
       </c>
       <c r="AC99" t="s">
-        <v>2086</v>
+        <v>2098</v>
       </c>
       <c r="AD99">
         <v>1.385617256164551E-2</v>
@@ -40355,10 +40355,10 @@
         <v>6.5349001003401036E-4</v>
       </c>
       <c r="AG99" t="s">
-        <v>2087</v>
+        <v>2099</v>
       </c>
       <c r="AH99" t="s">
-        <v>2088</v>
+        <v>2100</v>
       </c>
       <c r="AI99">
         <v>0.90562532705389864</v>
@@ -40379,10 +40379,10 @@
         <v>2.746839050685379E-2</v>
       </c>
       <c r="AO99" t="s">
-        <v>2089</v>
+        <v>2101</v>
       </c>
       <c r="AP99" t="s">
-        <v>2090</v>
+        <v>2102</v>
       </c>
       <c r="AQ99">
         <v>0.92029803678361222</v>
@@ -40394,7 +40394,7 @@
         <v>2.1575555667991572E-2</v>
       </c>
       <c r="AT99" t="s">
-        <v>2091</v>
+        <v>2103</v>
       </c>
       <c r="AU99">
         <v>0.8704188154601934</v>
@@ -40415,10 +40415,10 @@
         <v>3.7250334936681527E-2</v>
       </c>
       <c r="BA99" t="s">
-        <v>2092</v>
+        <v>2104</v>
       </c>
       <c r="BB99" t="s">
-        <v>2093</v>
+        <v>2105</v>
       </c>
       <c r="BC99">
         <v>0.97590281608138751</v>
@@ -40439,10 +40439,10 @@
         <v>5.5678541153844498E-2</v>
       </c>
       <c r="BI99" t="s">
-        <v>2094</v>
+        <v>2106</v>
       </c>
       <c r="BJ99" t="s">
-        <v>2095</v>
+        <v>2107</v>
       </c>
       <c r="BK99">
         <v>0.8717948717948717</v>
@@ -40463,7 +40463,7 @@
         <v>4.5512186894361192E-2</v>
       </c>
       <c r="BQ99" t="s">
-        <v>2096</v>
+        <v>2108</v>
       </c>
       <c r="BR99">
         <v>0.9646781789638933</v>
@@ -40475,10 +40475,10 @@
         <v>2.1126770526620962E-2</v>
       </c>
       <c r="BU99" t="s">
-        <v>2097</v>
+        <v>2109</v>
       </c>
       <c r="BV99" t="s">
-        <v>2098</v>
+        <v>2110</v>
       </c>
       <c r="BW99">
         <v>0.92247668298088481</v>
@@ -40499,10 +40499,10 @@
         <v>7.0922984370790582E-3</v>
       </c>
       <c r="CC99" t="s">
-        <v>2099</v>
+        <v>2111</v>
       </c>
       <c r="CD99" t="s">
-        <v>2100</v>
+        <v>2112</v>
       </c>
       <c r="CE99">
         <v>0.93513441168012268</v>
@@ -40514,7 +40514,7 @@
         <v>5.4393329577296836E-3</v>
       </c>
       <c r="CH99" t="s">
-        <v>2101</v>
+        <v>2113</v>
       </c>
       <c r="CI99">
         <v>0.89148144436884802</v>
@@ -40535,10 +40535,10 @@
         <v>9.9619378088634074E-3</v>
       </c>
       <c r="CO99" t="s">
-        <v>2102</v>
+        <v>2114</v>
       </c>
       <c r="CP99" t="s">
-        <v>2103</v>
+        <v>2115</v>
       </c>
       <c r="CQ99">
         <v>0.98060667836513293</v>
@@ -40559,10 +40559,10 @@
         <v>1.6836285612491529E-2</v>
       </c>
       <c r="CW99" t="s">
-        <v>2104</v>
+        <v>2116</v>
       </c>
       <c r="CX99" t="s">
-        <v>2105</v>
+        <v>2117</v>
       </c>
       <c r="CY99">
         <v>0.89377289377289393</v>
@@ -40583,7 +40583,7 @@
         <v>9.7881474720958109E-3</v>
       </c>
       <c r="DE99" t="s">
-        <v>2106</v>
+        <v>2118</v>
       </c>
       <c r="DF99">
         <v>0.97186242018174795</v>
@@ -40603,10 +40603,10 @@
         <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>2107</v>
+        <v>2119</v>
       </c>
       <c r="D100" t="s">
-        <v>2238</v>
+        <v>2120</v>
       </c>
       <c r="E100">
         <v>0.77333333333333332</v>
@@ -40669,7 +40669,7 @@
         <v>0.78688524590163933</v>
       </c>
       <c r="Y100" t="s">
-        <v>2108</v>
+        <v>2121</v>
       </c>
       <c r="Z100">
         <v>2.3105280739920481E-2</v>
@@ -40681,7 +40681,7 @@
         <v>1.0477354835695481E-3</v>
       </c>
       <c r="AC100" t="s">
-        <v>2109</v>
+        <v>2122</v>
       </c>
       <c r="AD100">
         <v>1.5482766287667409E-2</v>
@@ -40693,10 +40693,10 @@
         <v>1.5003551197444911E-3</v>
       </c>
       <c r="AG100" t="s">
-        <v>2110</v>
+        <v>2123</v>
       </c>
       <c r="AH100" t="s">
-        <v>2111</v>
+        <v>2124</v>
       </c>
       <c r="AI100">
         <v>0.82454595873437087</v>
@@ -40717,10 +40717,10 @@
         <v>5.6949482866748793E-2</v>
       </c>
       <c r="AO100" t="s">
-        <v>2112</v>
+        <v>2125</v>
       </c>
       <c r="AP100" t="s">
-        <v>2113</v>
+        <v>2126</v>
       </c>
       <c r="AQ100">
         <v>0.76687574624640675</v>
@@ -40732,7 +40732,7 @@
         <v>6.8586074816066336E-2</v>
       </c>
       <c r="AT100" t="s">
-        <v>2114</v>
+        <v>2127</v>
       </c>
       <c r="AU100">
         <v>0.80183822529612747</v>
@@ -40753,10 +40753,10 @@
         <v>5.1109266237862452E-2</v>
       </c>
       <c r="BA100" t="s">
-        <v>2115</v>
+        <v>2128</v>
       </c>
       <c r="BB100" t="s">
-        <v>2116</v>
+        <v>2129</v>
       </c>
       <c r="BC100">
         <v>0.68691585629146934</v>
@@ -40777,10 +40777,10 @@
         <v>4.9811536920238438E-2</v>
       </c>
       <c r="BI100" t="s">
-        <v>2117</v>
+        <v>2130</v>
       </c>
       <c r="BJ100" t="s">
-        <v>2118</v>
+        <v>2131</v>
       </c>
       <c r="BK100">
         <v>0.87886382623224724</v>
@@ -40801,7 +40801,7 @@
         <v>8.2438470350551546E-2</v>
       </c>
       <c r="BQ100" t="s">
-        <v>2119</v>
+        <v>2132</v>
       </c>
       <c r="BR100">
         <v>0.89465961823325812</v>
@@ -40813,10 +40813,10 @@
         <v>4.8504592798555728E-2</v>
       </c>
       <c r="BU100" t="s">
-        <v>2120</v>
+        <v>2133</v>
       </c>
       <c r="BV100" t="s">
-        <v>2121</v>
+        <v>2134</v>
       </c>
       <c r="BW100">
         <v>0.84143153793528047</v>
@@ -40837,10 +40837,10 @@
         <v>1.1287634320127299E-2</v>
       </c>
       <c r="CC100" t="s">
-        <v>2122</v>
+        <v>2135</v>
       </c>
       <c r="CD100" t="s">
-        <v>2123</v>
+        <v>2136</v>
       </c>
       <c r="CE100">
         <v>0.78455461054019093</v>
@@ -40852,7 +40852,7 @@
         <v>1.002078727098015E-2</v>
       </c>
       <c r="CH100" t="s">
-        <v>2124</v>
+        <v>2137</v>
       </c>
       <c r="CI100">
         <v>0.81812100140322497</v>
@@ -40873,10 +40873,10 @@
         <v>1.1382181766083769E-2</v>
       </c>
       <c r="CO100" t="s">
-        <v>2125</v>
+        <v>2138</v>
       </c>
       <c r="CP100" t="s">
-        <v>2126</v>
+        <v>2139</v>
       </c>
       <c r="CQ100">
         <v>0.69565518878508315</v>
@@ -40897,10 +40897,10 @@
         <v>5.8367951465261997E-3</v>
       </c>
       <c r="CW100" t="s">
-        <v>2127</v>
+        <v>2140</v>
       </c>
       <c r="CX100" t="s">
-        <v>2128</v>
+        <v>2141</v>
       </c>
       <c r="CY100">
         <v>0.90023731896111969</v>
@@ -40921,7 +40921,7 @@
         <v>2.1644660979063569E-2</v>
       </c>
       <c r="DE100" t="s">
-        <v>2129</v>
+        <v>2142</v>
       </c>
       <c r="DF100">
         <v>0.90858423996449489</v>
@@ -40941,10 +40941,10 @@
         <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>2130</v>
+        <v>2143</v>
       </c>
       <c r="D101" t="s">
-        <v>2237</v>
+        <v>2144</v>
       </c>
       <c r="E101">
         <v>0.84</v>
@@ -41007,7 +41007,7 @@
         <v>0.87745098039215685</v>
       </c>
       <c r="Y101" t="s">
-        <v>2131</v>
+        <v>2145</v>
       </c>
       <c r="Z101">
         <v>2.1329164505004879E-2</v>
@@ -41019,7 +41019,7 @@
         <v>1.215711213782499E-3</v>
       </c>
       <c r="AC101" t="s">
-        <v>2132</v>
+        <v>2146</v>
       </c>
       <c r="AD101">
         <v>1.324030331202916E-2</v>
@@ -41151,10 +41151,10 @@
         <v>3.1019267646652839E-2</v>
       </c>
       <c r="BU101" t="s">
-        <v>2133</v>
+        <v>2147</v>
       </c>
       <c r="BV101" t="s">
-        <v>2134</v>
+        <v>2148</v>
       </c>
       <c r="BW101">
         <v>0.85572716265993554</v>
@@ -41175,10 +41175,10 @@
         <v>1.0682749221641899E-2</v>
       </c>
       <c r="CC101" t="s">
-        <v>2135</v>
+        <v>2149</v>
       </c>
       <c r="CD101" t="s">
-        <v>2136</v>
+        <v>2150</v>
       </c>
       <c r="CE101">
         <v>0.88741849171643838</v>
@@ -41190,7 +41190,7 @@
         <v>8.0051036466715596E-3</v>
       </c>
       <c r="CH101" t="s">
-        <v>2137</v>
+        <v>2151</v>
       </c>
       <c r="CI101">
         <v>0.81926716312307035</v>
@@ -41211,10 +41211,10 @@
         <v>1.628538920568498E-2</v>
       </c>
       <c r="CO101" t="s">
-        <v>2138</v>
+        <v>2152</v>
       </c>
       <c r="CP101" t="s">
-        <v>2139</v>
+        <v>2153</v>
       </c>
       <c r="CQ101">
         <v>0.94986102391262073</v>
@@ -41235,7 +41235,7 @@
         <v>1.7340165913896449E-2</v>
       </c>
       <c r="CW101" t="s">
-        <v>2140</v>
+        <v>2154</v>
       </c>
       <c r="CX101" t="s">
         <v>918</v>
@@ -41259,7 +41259,7 @@
         <v>1.6808794818811829E-2</v>
       </c>
       <c r="DE101" t="s">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="DF101">
         <v>0.94572110895640316</v>
@@ -41279,10 +41279,10 @@
         <v>113</v>
       </c>
       <c r="C102" t="s">
-        <v>2142</v>
+        <v>2156</v>
       </c>
       <c r="D102" t="s">
-        <v>2236</v>
+        <v>2157</v>
       </c>
       <c r="E102">
         <v>0.85333333333333339</v>
@@ -41345,7 +41345,7 @@
         <v>0.99526066350710907</v>
       </c>
       <c r="Y102" t="s">
-        <v>2143</v>
+        <v>2158</v>
       </c>
       <c r="Z102">
         <v>2.1659817014421739E-2</v>
@@ -41357,7 +41357,7 @@
         <v>2.234422033747832E-3</v>
       </c>
       <c r="AC102" t="s">
-        <v>2144</v>
+        <v>2159</v>
       </c>
       <c r="AD102">
         <v>1.7643928527832031E-2</v>
@@ -41369,10 +41369,10 @@
         <v>4.9283557665869941E-3</v>
       </c>
       <c r="AG102" t="s">
-        <v>2145</v>
+        <v>2160</v>
       </c>
       <c r="AH102" t="s">
-        <v>2146</v>
+        <v>2161</v>
       </c>
       <c r="AI102">
         <v>0.89342473831637914</v>
@@ -41393,10 +41393,10 @@
         <v>3.7689074138275193E-2</v>
       </c>
       <c r="AO102" t="s">
-        <v>2147</v>
+        <v>2162</v>
       </c>
       <c r="AP102" t="s">
-        <v>2148</v>
+        <v>2163</v>
       </c>
       <c r="AQ102">
         <v>0.85962454995529058</v>
@@ -41408,7 +41408,7 @@
         <v>4.8503776338968622E-2</v>
       </c>
       <c r="AT102" t="s">
-        <v>2149</v>
+        <v>2164</v>
       </c>
       <c r="AU102">
         <v>0.88949774169636009</v>
@@ -41429,10 +41429,10 @@
         <v>3.0871093784943279E-2</v>
       </c>
       <c r="BA102" t="s">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="BB102" t="s">
-        <v>2151</v>
+        <v>2166</v>
       </c>
       <c r="BC102">
         <v>0.84932569519035683</v>
@@ -41453,10 +41453,10 @@
         <v>3.0973415437552439E-2</v>
       </c>
       <c r="BI102" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
       <c r="BJ102" t="s">
-        <v>2152</v>
+        <v>2167</v>
       </c>
       <c r="BK102">
         <v>0.87844611528822047</v>
@@ -41477,7 +41477,7 @@
         <v>5.5969162370913303E-2</v>
       </c>
       <c r="BQ102" t="s">
-        <v>2153</v>
+        <v>2168</v>
       </c>
       <c r="BR102">
         <v>0.89342473831637914</v>
@@ -41492,7 +41492,7 @@
         <v>369</v>
       </c>
       <c r="BV102" t="s">
-        <v>2154</v>
+        <v>2169</v>
       </c>
       <c r="BW102">
         <v>0.9974101849692536</v>
@@ -41513,10 +41513,10 @@
         <v>1.417051170840857E-3</v>
       </c>
       <c r="CC102" t="s">
-        <v>2155</v>
+        <v>2170</v>
       </c>
       <c r="CD102" t="s">
-        <v>2156</v>
+        <v>2171</v>
       </c>
       <c r="CE102">
         <v>0.99683658485420601</v>
@@ -41528,7 +41528,7 @@
         <v>2.0007850996625648E-3</v>
       </c>
       <c r="CH102" t="s">
-        <v>2157</v>
+        <v>2172</v>
       </c>
       <c r="CI102">
         <v>0.99755101492102438</v>
@@ -41549,10 +41549,10 @@
         <v>1.097039760045307E-3</v>
       </c>
       <c r="CO102" t="s">
-        <v>2158</v>
+        <v>2173</v>
       </c>
       <c r="CP102" t="s">
-        <v>2159</v>
+        <v>2174</v>
       </c>
       <c r="CQ102">
         <v>0.99749373433583954</v>
@@ -41573,10 +41573,10 @@
         <v>2.3945637022855341E-3</v>
       </c>
       <c r="CW102" t="s">
-        <v>2160</v>
+        <v>2175</v>
       </c>
       <c r="CX102" t="s">
-        <v>2161</v>
+        <v>2176</v>
       </c>
       <c r="CY102">
         <v>0.99620733249051818</v>
@@ -41597,7 +41597,7 @@
         <v>2.192980346857405E-3</v>
       </c>
       <c r="DE102" t="s">
-        <v>2154</v>
+        <v>2169</v>
       </c>
       <c r="DF102">
         <v>0.9974101849692536</v>
@@ -41617,10 +41617,10 @@
         <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>2162</v>
+        <v>2177</v>
       </c>
       <c r="D103" t="s">
-        <v>2235</v>
+        <v>2178</v>
       </c>
       <c r="E103">
         <v>0.85333333333333339</v>
@@ -41683,7 +41683,7 @@
         <v>0.95981087470449178</v>
       </c>
       <c r="Y103" t="s">
-        <v>2163</v>
+        <v>2179</v>
       </c>
       <c r="Z103">
         <v>2.099997656685965E-2</v>
@@ -41695,7 +41695,7 @@
         <v>1.519553433003547E-3</v>
       </c>
       <c r="AC103" t="s">
-        <v>2164</v>
+        <v>2180</v>
       </c>
       <c r="AD103">
         <v>1.6360282897949219E-2</v>
@@ -41707,10 +41707,10 @@
         <v>1.317893547891996E-3</v>
       </c>
       <c r="AG103" t="s">
-        <v>2165</v>
+        <v>2181</v>
       </c>
       <c r="AH103" t="s">
-        <v>2166</v>
+        <v>2182</v>
       </c>
       <c r="AI103">
         <v>0.84874411302982722</v>
@@ -41731,10 +41731,10 @@
         <v>5.5933610865319859E-2</v>
       </c>
       <c r="AO103" t="s">
-        <v>2167</v>
+        <v>2183</v>
       </c>
       <c r="AP103" t="s">
-        <v>2168</v>
+        <v>2184</v>
       </c>
       <c r="AQ103">
         <v>0.90274987774987792</v>
@@ -41746,7 +41746,7 @@
         <v>4.303126788446314E-2</v>
       </c>
       <c r="AT103" t="s">
-        <v>2169</v>
+        <v>2185</v>
       </c>
       <c r="AU103">
         <v>0.83364084151390994</v>
@@ -41767,10 +41767,10 @@
         <v>7.7939877746625683E-2</v>
       </c>
       <c r="BA103" t="s">
-        <v>2170</v>
+        <v>2186</v>
       </c>
       <c r="BB103" t="s">
-        <v>2171</v>
+        <v>2187</v>
       </c>
       <c r="BC103">
         <v>0.93074284966821186</v>
@@ -41791,10 +41791,10 @@
         <v>0.1131929317366905</v>
       </c>
       <c r="BI103" t="s">
-        <v>2172</v>
+        <v>2188</v>
       </c>
       <c r="BJ103" t="s">
-        <v>2173</v>
+        <v>2189</v>
       </c>
       <c r="BK103">
         <v>0.879120879120879</v>
@@ -41815,7 +41815,7 @@
         <v>8.3548936695749879E-2</v>
       </c>
       <c r="BQ103" t="s">
-        <v>2174</v>
+        <v>2190</v>
       </c>
       <c r="BR103">
         <v>0.9094104308390023</v>
@@ -41827,10 +41827,10 @@
         <v>6.1376568268449852E-2</v>
       </c>
       <c r="BU103" t="s">
-        <v>2175</v>
+        <v>2191</v>
       </c>
       <c r="BV103" t="s">
-        <v>2176</v>
+        <v>2192</v>
       </c>
       <c r="BW103">
         <v>0.93901842788397427</v>
@@ -41851,10 +41851,10 @@
         <v>4.0854772818506363E-3</v>
       </c>
       <c r="CC103" t="s">
-        <v>2177</v>
+        <v>2193</v>
       </c>
       <c r="CD103" t="s">
-        <v>2178</v>
+        <v>2194</v>
       </c>
       <c r="CE103">
         <v>0.95868259941295719</v>
@@ -41866,7 +41866,7 @@
         <v>2.838224405392204E-3</v>
       </c>
       <c r="CH103" t="s">
-        <v>2179</v>
+        <v>2195</v>
       </c>
       <c r="CI103">
         <v>0.92591280561103628</v>
@@ -41887,10 +41887,10 @@
         <v>7.6044665485748156E-3</v>
       </c>
       <c r="CO103" t="s">
-        <v>2180</v>
+        <v>2196</v>
       </c>
       <c r="CP103" t="s">
-        <v>2181</v>
+        <v>2197</v>
       </c>
       <c r="CQ103">
         <v>0.97603915902888172</v>
@@ -41911,10 +41911,10 @@
         <v>1.2413477317532879E-2</v>
       </c>
       <c r="CW103" t="s">
-        <v>2182</v>
+        <v>2198</v>
       </c>
       <c r="CX103" t="s">
-        <v>2183</v>
+        <v>2199</v>
       </c>
       <c r="CY103">
         <v>0.9420024420024421</v>
@@ -41935,7 +41935,7 @@
         <v>1.868980982523908E-2</v>
       </c>
       <c r="DE103" t="s">
-        <v>2184</v>
+        <v>2200</v>
       </c>
       <c r="DF103">
         <v>0.98973880150350735</v>
@@ -41955,10 +41955,10 @@
         <v>113</v>
       </c>
       <c r="C104" t="s">
-        <v>2185</v>
+        <v>2201</v>
       </c>
       <c r="D104" t="s">
-        <v>2234</v>
+        <v>2202</v>
       </c>
       <c r="E104">
         <v>0.82666666666666666</v>
@@ -42021,7 +42021,7 @@
         <v>0.88262910798122074</v>
       </c>
       <c r="Y104" t="s">
-        <v>2186</v>
+        <v>2203</v>
       </c>
       <c r="Z104">
         <v>3.7236724581037252E-2</v>
@@ -42033,7 +42033,7 @@
         <v>8.2159155839204145E-3</v>
       </c>
       <c r="AC104" t="s">
-        <v>2187</v>
+        <v>2204</v>
       </c>
       <c r="AD104">
         <v>1.5778779983520511E-2</v>
@@ -42045,10 +42045,10 @@
         <v>1.173244839837054E-3</v>
       </c>
       <c r="AG104" t="s">
-        <v>2188</v>
+        <v>2205</v>
       </c>
       <c r="AH104" t="s">
-        <v>2189</v>
+        <v>2206</v>
       </c>
       <c r="AI104">
         <v>0.87839662180661726</v>
@@ -42069,10 +42069,10 @@
         <v>4.0404266678870822E-2</v>
       </c>
       <c r="AO104" t="s">
-        <v>2190</v>
+        <v>2207</v>
       </c>
       <c r="AP104" t="s">
-        <v>2191</v>
+        <v>2208</v>
       </c>
       <c r="AQ104">
         <v>0.83689210518478796</v>
@@ -42084,7 +42084,7 @@
         <v>4.9068389236544697E-2</v>
       </c>
       <c r="AT104" t="s">
-        <v>2192</v>
+        <v>2209</v>
       </c>
       <c r="AU104">
         <v>0.86848796755968216</v>
@@ -42105,10 +42105,10 @@
         <v>3.4062996209327012E-2</v>
       </c>
       <c r="BA104" t="s">
-        <v>2193</v>
+        <v>2210</v>
       </c>
       <c r="BB104" t="s">
-        <v>2194</v>
+        <v>2211</v>
       </c>
       <c r="BC104">
         <v>0.79710200285647848</v>
@@ -42129,10 +42129,10 @@
         <v>1.90987884856617E-2</v>
       </c>
       <c r="BI104" t="s">
-        <v>2195</v>
+        <v>2212</v>
       </c>
       <c r="BJ104" t="s">
-        <v>2196</v>
+        <v>2213</v>
       </c>
       <c r="BK104">
         <v>0.88596491228070173</v>
@@ -42153,7 +42153,7 @@
         <v>5.7032791190494078E-2</v>
       </c>
       <c r="BQ104" t="s">
-        <v>2197</v>
+        <v>2214</v>
       </c>
       <c r="BR104">
         <v>0.93547875290467075</v>
@@ -42165,10 +42165,10 @@
         <v>3.6243457358422833E-2</v>
       </c>
       <c r="BU104" t="s">
-        <v>2198</v>
+        <v>2215</v>
       </c>
       <c r="BV104" t="s">
-        <v>2199</v>
+        <v>2216</v>
       </c>
       <c r="BW104">
         <v>0.91085393166864537</v>
@@ -42189,10 +42189,10 @@
         <v>9.4007370205730183E-3</v>
       </c>
       <c r="CC104" t="s">
-        <v>2200</v>
+        <v>2217</v>
       </c>
       <c r="CD104" t="s">
-        <v>2201</v>
+        <v>2218</v>
       </c>
       <c r="CE104">
         <v>0.87645469811883614</v>
@@ -42204,7 +42204,7 @@
         <v>1.1203833681663611E-2</v>
       </c>
       <c r="CH104" t="s">
-        <v>2202</v>
+        <v>2219</v>
       </c>
       <c r="CI104">
         <v>0.90138476513178922</v>
@@ -42225,10 +42225,10 @@
         <v>8.0289328109743336E-3</v>
       </c>
       <c r="CO104" t="s">
-        <v>2203</v>
+        <v>2220</v>
       </c>
       <c r="CP104" t="s">
-        <v>2204</v>
+        <v>2221</v>
       </c>
       <c r="CQ104">
         <v>0.83570065482910205</v>
@@ -42249,10 +42249,10 @@
         <v>4.8536349487245476E-3</v>
       </c>
       <c r="CW104" t="s">
-        <v>2205</v>
+        <v>2222</v>
       </c>
       <c r="CX104" t="s">
-        <v>2206</v>
+        <v>2223</v>
       </c>
       <c r="CY104">
         <v>0.92171801184376878</v>
@@ -42273,7 +42273,7 @@
         <v>1.4523401200288871E-2</v>
       </c>
       <c r="DE104" t="s">
-        <v>2207</v>
+        <v>2224</v>
       </c>
       <c r="DF104">
         <v>0.96080524005577017</v>
@@ -42293,10 +42293,10 @@
         <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>2208</v>
+        <v>2225</v>
       </c>
       <c r="D105" t="s">
-        <v>2233</v>
+        <v>2226</v>
       </c>
       <c r="E105">
         <v>0.89333333333333331</v>
@@ -42359,7 +42359,7 @@
         <v>0.95104895104895104</v>
       </c>
       <c r="Y105" t="s">
-        <v>2209</v>
+        <v>2227</v>
       </c>
       <c r="Z105">
         <v>3.2412597111293247E-2</v>
@@ -42371,7 +42371,7 @@
         <v>2.0400411460430529E-3</v>
       </c>
       <c r="AC105" t="s">
-        <v>2210</v>
+        <v>2228</v>
       </c>
       <c r="AD105">
         <v>1.3770614351545059E-2</v>
@@ -42383,10 +42383,10 @@
         <v>7.8094096625935935E-4</v>
       </c>
       <c r="AG105" t="s">
-        <v>2211</v>
+        <v>2229</v>
       </c>
       <c r="AH105" t="s">
-        <v>2212</v>
+        <v>2230</v>
       </c>
       <c r="AI105">
         <v>0.90497121925693358</v>
@@ -42407,10 +42407,10 @@
         <v>4.9755159406517362E-2</v>
       </c>
       <c r="AO105" t="s">
-        <v>2213</v>
+        <v>2231</v>
       </c>
       <c r="AP105" t="s">
-        <v>2214</v>
+        <v>2232</v>
       </c>
       <c r="AQ105">
         <v>0.93118110534940279</v>
@@ -42422,7 +42422,7 @@
         <v>3.6791620985311517E-2</v>
       </c>
       <c r="AT105" t="s">
-        <v>2215</v>
+        <v>2233</v>
       </c>
       <c r="AU105">
         <v>0.8836974506062879</v>
@@ -42443,10 +42443,10 @@
         <v>7.6493001639104469E-2</v>
       </c>
       <c r="BA105" t="s">
-        <v>2216</v>
+        <v>2234</v>
       </c>
       <c r="BB105" t="s">
-        <v>2217</v>
+        <v>2235</v>
       </c>
       <c r="BC105">
         <v>0.96480551734863984</v>
@@ -42467,10 +42467,10 @@
         <v>0.10051147447399721</v>
       </c>
       <c r="BI105" t="s">
-        <v>2218</v>
+        <v>2236</v>
       </c>
       <c r="BJ105" t="s">
-        <v>2219</v>
+        <v>2237</v>
       </c>
       <c r="BK105">
         <v>0.90109890109890123</v>
@@ -42491,7 +42491,7 @@
         <v>7.3789928117601003E-2</v>
       </c>
       <c r="BQ105" t="s">
-        <v>2220</v>
+        <v>2238</v>
       </c>
       <c r="BR105">
         <v>0.95421245421245426</v>
@@ -42503,10 +42503,10 @@
         <v>2.554741077704686E-2</v>
       </c>
       <c r="BU105" t="s">
-        <v>2221</v>
+        <v>2239</v>
       </c>
       <c r="BV105" t="s">
-        <v>2222</v>
+        <v>2240</v>
       </c>
       <c r="BW105">
         <v>0.92018191892141477</v>
@@ -42527,10 +42527,10 @@
         <v>8.1762915663579853E-3</v>
       </c>
       <c r="CC105" t="s">
-        <v>2223</v>
+        <v>2241</v>
       </c>
       <c r="CD105" t="s">
-        <v>2224</v>
+        <v>2242</v>
       </c>
       <c r="CE105">
         <v>0.93637033838619221</v>
@@ -42542,7 +42542,7 @@
         <v>6.3421069865930886E-3</v>
       </c>
       <c r="CH105" t="s">
-        <v>2225</v>
+        <v>2243</v>
       </c>
       <c r="CI105">
         <v>0.89241751927092661</v>
@@ -42563,10 +42563,10 @@
         <v>1.0895547946837321E-2</v>
       </c>
       <c r="CO105" t="s">
-        <v>2226</v>
+        <v>2244</v>
       </c>
       <c r="CP105" t="s">
-        <v>2227</v>
+        <v>2245</v>
       </c>
       <c r="CQ105">
         <v>0.97689032399265263</v>
@@ -42587,10 +42587,10 @@
         <v>2.4353139415404089E-2</v>
       </c>
       <c r="CW105" t="s">
-        <v>2228</v>
+        <v>2246</v>
       </c>
       <c r="CX105" t="s">
-        <v>2229</v>
+        <v>2247</v>
       </c>
       <c r="CY105">
         <v>0.8992673992673994</v>
@@ -42611,7 +42611,7 @@
         <v>1.534362094470151E-2</v>
       </c>
       <c r="DE105" t="s">
-        <v>2230</v>
+        <v>2248</v>
       </c>
       <c r="DF105">
         <v>0.97135144656153061</v>
